--- a/INDUSTRIAL.xlsx
+++ b/INDUSTRIAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GUDESCHA\Downloads\Dashaboard em HTML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338D6E7E-A27E-4713-A730-AB56A8AB5280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36787315-9C33-42DF-BEB1-D38F331D260E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F2E2EF4D-F0CD-41CA-9DD0-62727A1AD53A}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1716" uniqueCount="755">
   <si>
     <t>Fornecedor</t>
   </si>
@@ -153,9 +153,6 @@
     <t>B66385</t>
   </si>
   <si>
-    <t>B73206</t>
-  </si>
-  <si>
     <t>B71659</t>
   </si>
   <si>
@@ -618,24 +615,6 @@
     <t>01.03</t>
   </si>
   <si>
-    <t>SKFAPE202609091312050130</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85833511PO</t>
-  </si>
-  <si>
-    <t>2026-09-09 13:12:05.367</t>
-  </si>
-  <si>
-    <t>8170.00</t>
-  </si>
-  <si>
-    <t>32182612000139&amp;NA&amp;9012</t>
-  </si>
-  <si>
-    <t>EP1765298</t>
-  </si>
-  <si>
     <t>SKFAPE202606172025160726</t>
   </si>
   <si>
@@ -768,9 +747,6 @@
     <t>0FFICE TOTAL SP</t>
   </si>
   <si>
-    <t>MARIA I. BATTISTON PEGADA</t>
-  </si>
-  <si>
     <t>SKFAPM202609291235330281</t>
   </si>
   <si>
@@ -1035,9 +1011,6 @@
     <t>B73269</t>
   </si>
   <si>
-    <t xml:space="preserve">RODRIGO BERTOLINO JOSE </t>
-  </si>
-  <si>
     <t>EP1771835</t>
   </si>
   <si>
@@ -1335,9 +1308,6 @@
     <t>B73235</t>
   </si>
   <si>
-    <t>AREA 19 TELECOMUNICAÇOES LTDA</t>
-  </si>
-  <si>
     <t>EP1658693</t>
   </si>
   <si>
@@ -1363,6 +1333,981 @@
   </si>
   <si>
     <t>2026-09-30 17:42:07.57</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051221090991</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855781PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:21:09.467</t>
+  </si>
+  <si>
+    <t>8521.46</t>
+  </si>
+  <si>
+    <t>62173620009306&amp;NA&amp;</t>
+  </si>
+  <si>
+    <t>B71225</t>
+  </si>
+  <si>
+    <t>SERASA S.A.</t>
+  </si>
+  <si>
+    <t>EP1759507</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051221280992</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855782PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:21:28.837</t>
+  </si>
+  <si>
+    <t>3315.00</t>
+  </si>
+  <si>
+    <t>31199199000152&amp;NA&amp;9001</t>
+  </si>
+  <si>
+    <t>04.01</t>
+  </si>
+  <si>
+    <t>B71492</t>
+  </si>
+  <si>
+    <t>PRAM SERVIÇOS MEDICO</t>
+  </si>
+  <si>
+    <t>EP1735635</t>
+  </si>
+  <si>
+    <t>Kamila Vieira</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051221480993</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855783PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:21:48.293</t>
+  </si>
+  <si>
+    <t>18221.90</t>
+  </si>
+  <si>
+    <t>48109110000112&amp;16/11/2026&amp;9002</t>
+  </si>
+  <si>
+    <t>17.14</t>
+  </si>
+  <si>
+    <t>EP1799619</t>
+  </si>
+  <si>
+    <t>Joyce Santos</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051222280995</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855785PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:22:28.153</t>
+  </si>
+  <si>
+    <t>1820.12</t>
+  </si>
+  <si>
+    <t>EP1799620</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051215360971</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855757PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:15:36.97</t>
+  </si>
+  <si>
+    <t>23000.00</t>
+  </si>
+  <si>
+    <t>20329532000184&amp;NA</t>
+  </si>
+  <si>
+    <t>B73254</t>
+  </si>
+  <si>
+    <t>ALEXANDRE DE ALMEIDA CHIA</t>
+  </si>
+  <si>
+    <t>EP1665486</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051215550972</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855758PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:15:56.047</t>
+  </si>
+  <si>
+    <t>484.87</t>
+  </si>
+  <si>
+    <t>10552544000110&amp;NA</t>
+  </si>
+  <si>
+    <t>B71369</t>
+  </si>
+  <si>
+    <t>BANCODOC GESTAO DE INFORMACOES</t>
+  </si>
+  <si>
+    <t>EP1660608</t>
+  </si>
+  <si>
+    <t>Paula Carvalho</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051216150973</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855759PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:16:15.537</t>
+  </si>
+  <si>
+    <t>976.95</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051216340974</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855760PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:16:34.967</t>
+  </si>
+  <si>
+    <t>2739.41</t>
+  </si>
+  <si>
+    <t>11440691000160&amp;NA</t>
+  </si>
+  <si>
+    <t>B72540</t>
+  </si>
+  <si>
+    <t>DYNAMICCA SOLUCOES E SERVICOS</t>
+  </si>
+  <si>
+    <t>EP1663776</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051216540975</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855761PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:16:54.37</t>
+  </si>
+  <si>
+    <t>950.00</t>
+  </si>
+  <si>
+    <t>19037313000142&amp;05/11/2026</t>
+  </si>
+  <si>
+    <t>B70258</t>
+  </si>
+  <si>
+    <t>KERO TELECOM COM E SERV LTDA M</t>
+  </si>
+  <si>
+    <t>EP1660609</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051211260956</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855740PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:11:26.213</t>
+  </si>
+  <si>
+    <t>2650.00</t>
+  </si>
+  <si>
+    <t>09397942000120&amp;NA</t>
+  </si>
+  <si>
+    <t>14.02</t>
+  </si>
+  <si>
+    <t>B67053</t>
+  </si>
+  <si>
+    <t>SYLAMAG INFORMATICA COM E SER</t>
+  </si>
+  <si>
+    <t>EP1664305</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051211450957</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855741PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:11:45.537</t>
+  </si>
+  <si>
+    <t>492.26</t>
+  </si>
+  <si>
+    <t>07424616000139&amp;29/12/2026</t>
+  </si>
+  <si>
+    <t>14.05</t>
+  </si>
+  <si>
+    <t>B70228</t>
+  </si>
+  <si>
+    <t>USINAGEM E FERR LUZ &amp; LUZ LTDA</t>
+  </si>
+  <si>
+    <t>EP1805460</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051212050958</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855742PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:12:06.077</t>
+  </si>
+  <si>
+    <t>2784.07</t>
+  </si>
+  <si>
+    <t>06999230000192&amp;18/10/2026</t>
+  </si>
+  <si>
+    <t>B72298</t>
+  </si>
+  <si>
+    <t>FAIR SERVICES - SERV TECNICOS</t>
+  </si>
+  <si>
+    <t>EP1802943</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051212240959</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855743PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:12:25.187</t>
+  </si>
+  <si>
+    <t>587.86</t>
+  </si>
+  <si>
+    <t>EP1350362</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051214120966</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855752PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:14:12.923</t>
+  </si>
+  <si>
+    <t>6144.00</t>
+  </si>
+  <si>
+    <t>68290055000117&amp;NA</t>
+  </si>
+  <si>
+    <t>B66713</t>
+  </si>
+  <si>
+    <t>ADUANEIRAS INFORMATICA LTDA</t>
+  </si>
+  <si>
+    <t>EP1801868</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051214320967</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855753PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:14:33.187</t>
+  </si>
+  <si>
+    <t>5822.99</t>
+  </si>
+  <si>
+    <t>19660635000143&amp;NA</t>
+  </si>
+  <si>
+    <t>17.02</t>
+  </si>
+  <si>
+    <t>B70582</t>
+  </si>
+  <si>
+    <t>DKT SER ESP DE AP ADM LTDA ME</t>
+  </si>
+  <si>
+    <t>EP1660456</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051214530968</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855754PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:14:53.583</t>
+  </si>
+  <si>
+    <t>5400.00</t>
+  </si>
+  <si>
+    <t>EP1802978</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051215130969</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855755PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:15:13.203</t>
+  </si>
+  <si>
+    <t>12769.32</t>
+  </si>
+  <si>
+    <t>20482549000177&amp;NA</t>
+  </si>
+  <si>
+    <t>B71715</t>
+  </si>
+  <si>
+    <t>I4D SOLUCOES EM TECNOLOGIA</t>
+  </si>
+  <si>
+    <t>EP1724299</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051216580976</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855762PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:16:58.643</t>
+  </si>
+  <si>
+    <t>24302.00</t>
+  </si>
+  <si>
+    <t>EP1801883</t>
+  </si>
+  <si>
+    <t>Allana Fernandes</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051217180977</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855763PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:17:18.717</t>
+  </si>
+  <si>
+    <t>38731.89</t>
+  </si>
+  <si>
+    <t>02389406000133&amp;05/11/2026</t>
+  </si>
+  <si>
+    <t>B95802</t>
+  </si>
+  <si>
+    <t>S2M CONSULTORIA E SISTEMAS LTD</t>
+  </si>
+  <si>
+    <t>EP1654371</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051217380978</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855764PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:17:38.367</t>
+  </si>
+  <si>
+    <t>5631.00</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051217570979</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855765PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:17:57.613</t>
+  </si>
+  <si>
+    <t>1575.00</t>
+  </si>
+  <si>
+    <t>05538148000106&amp;28/10/2026</t>
+  </si>
+  <si>
+    <t>B70590</t>
+  </si>
+  <si>
+    <t>PROAQT EMPREENDIMENTOS TEC LTD</t>
+  </si>
+  <si>
+    <t>EP1795365</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051219440986</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855772PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:19:44.853</t>
+  </si>
+  <si>
+    <t>39922.05</t>
+  </si>
+  <si>
+    <t>08219049000141&amp;NA</t>
+  </si>
+  <si>
+    <t>B73409</t>
+  </si>
+  <si>
+    <t>GHT PORTELA ASSESSORIA EM</t>
+  </si>
+  <si>
+    <t>EP1801283</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051220290989</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855775PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:20:29.903</t>
+  </si>
+  <si>
+    <t>16042.72</t>
+  </si>
+  <si>
+    <t>00092302000137&amp;05/11/2026&amp;9001</t>
+  </si>
+  <si>
+    <t>B61171</t>
+  </si>
+  <si>
+    <t>CARREIRA, MULLER &amp; ASSOCIADOS</t>
+  </si>
+  <si>
+    <t>EP1804330</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051220490990</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855780PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:20:49.337</t>
+  </si>
+  <si>
+    <t>2270.00</t>
+  </si>
+  <si>
+    <t>16549592000135&amp;NA&amp;9001</t>
+  </si>
+  <si>
+    <t>04.21</t>
+  </si>
+  <si>
+    <t>B73371</t>
+  </si>
+  <si>
+    <t>TRANSHELP - SERV AMBULAN</t>
+  </si>
+  <si>
+    <t>EP1769937</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051222320996</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855786PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:22:32.56</t>
+  </si>
+  <si>
+    <t>1478.13</t>
+  </si>
+  <si>
+    <t>05538148000106&amp;NA&amp;&amp;7502</t>
+  </si>
+  <si>
+    <t>EP1774329</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051222510997</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855787PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:22:51.98</t>
+  </si>
+  <si>
+    <t>2716.00</t>
+  </si>
+  <si>
+    <t>59576215000106&amp;22/10/2026&amp;9001</t>
+  </si>
+  <si>
+    <t>B62705</t>
+  </si>
+  <si>
+    <t>A2 SERVICOS AMBIENTAIS  LTDA</t>
+  </si>
+  <si>
+    <t>EP1792302</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051225190107</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855796PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:25:19.22</t>
+  </si>
+  <si>
+    <t>26584.71</t>
+  </si>
+  <si>
+    <t>12237752000150&amp;21/08/2026&amp;5005</t>
+  </si>
+  <si>
+    <t>B73051</t>
+  </si>
+  <si>
+    <t>RODL &amp; PARTNER CONSUL LTDA</t>
+  </si>
+  <si>
+    <t>EP1780835</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051225570109</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855798PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:25:58.007</t>
+  </si>
+  <si>
+    <t>17069.99</t>
+  </si>
+  <si>
+    <t>03506307000157&amp;22/10/2026&amp;9001</t>
+  </si>
+  <si>
+    <t>B70837</t>
+  </si>
+  <si>
+    <t>TICKET SOLUCOES HDFGT SA</t>
+  </si>
+  <si>
+    <t>EP1769947</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051226030110</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855799PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:26:03.807</t>
+  </si>
+  <si>
+    <t>6686.50</t>
+  </si>
+  <si>
+    <t>11314113000188&amp;18/11/2026&amp;5005</t>
+  </si>
+  <si>
+    <t>B69098</t>
+  </si>
+  <si>
+    <t>BP DOS SANTOS</t>
+  </si>
+  <si>
+    <t>EP1802975</t>
+  </si>
+  <si>
+    <t>RODRIGO BERTOLINO JOSE</t>
+  </si>
+  <si>
+    <t>SKFAPE202609081425380594</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85832640PO</t>
+  </si>
+  <si>
+    <t>2026-09-08 14:25:38.987</t>
+  </si>
+  <si>
+    <t>22865.14</t>
+  </si>
+  <si>
+    <t>41420915000133&amp;NA</t>
+  </si>
+  <si>
+    <t>B73291</t>
+  </si>
+  <si>
+    <t>QUATRO PONTO ZERO - RH LT</t>
+  </si>
+  <si>
+    <t>EP1702648</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051223350101</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855790PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:23:36.05</t>
+  </si>
+  <si>
+    <t>7704.80</t>
+  </si>
+  <si>
+    <t>33040981000150&amp;</t>
+  </si>
+  <si>
+    <t>B71171</t>
+  </si>
+  <si>
+    <t>AIG SEGUROS BRASIL S.A.</t>
+  </si>
+  <si>
+    <t>EP1805915</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051223550102</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855791PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:23:55.517</t>
+  </si>
+  <si>
+    <t>198612.03</t>
+  </si>
+  <si>
+    <t>EP1805916</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051212290960</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855744PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:12:29.603</t>
+  </si>
+  <si>
+    <t>7304.80</t>
+  </si>
+  <si>
+    <t>15664649000184&amp;31/10/2026</t>
+  </si>
+  <si>
+    <t>B72251</t>
+  </si>
+  <si>
+    <t>GPBR PARTICIPACOES LTDA</t>
+  </si>
+  <si>
+    <t>EP1787936</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051212480961</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855745PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:12:48.913</t>
+  </si>
+  <si>
+    <t>4944.60</t>
+  </si>
+  <si>
+    <t>20482549000177&amp;30/10/2026</t>
+  </si>
+  <si>
+    <t>EP1721631</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051213080962</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855748PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:13:08.65</t>
+  </si>
+  <si>
+    <t>7887.75</t>
+  </si>
+  <si>
+    <t>22183303000120&amp;01/12/2026</t>
+  </si>
+  <si>
+    <t>B71527</t>
+  </si>
+  <si>
+    <t>LUPEON SERVICOS E TECNOLOGIA</t>
+  </si>
+  <si>
+    <t>EP1696558</t>
+  </si>
+  <si>
+    <t>Samily Donato</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051218170980</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855766PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:18:17.747</t>
+  </si>
+  <si>
+    <t>805.00</t>
+  </si>
+  <si>
+    <t>EP1660610</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051218410982</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855768PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:18:41.59</t>
+  </si>
+  <si>
+    <t>930.00</t>
+  </si>
+  <si>
+    <t>19037313000142&amp;19/11/2026</t>
+  </si>
+  <si>
+    <t>EP1683421</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051219000983</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855769PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:19:01.04</t>
+  </si>
+  <si>
+    <t>546.00</t>
+  </si>
+  <si>
+    <t>22226517000136&amp;NA</t>
+  </si>
+  <si>
+    <t>24.01</t>
+  </si>
+  <si>
+    <t>B72133</t>
+  </si>
+  <si>
+    <t>MAURO FIORAVANTI TASCHETTO</t>
+  </si>
+  <si>
+    <t>EP1799056</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051219210984</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855770PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:19:21.19</t>
+  </si>
+  <si>
+    <t>17623.41</t>
+  </si>
+  <si>
+    <t>02833315000579&amp;02/11/2026</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051210260953</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855737PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:10:26.983</t>
+  </si>
+  <si>
+    <t>11782.00</t>
+  </si>
+  <si>
+    <t>45662885000122&amp;NA</t>
+  </si>
+  <si>
+    <t>B72620</t>
+  </si>
+  <si>
+    <t>LEONARDO TAVARES DA SILVA DE O</t>
+  </si>
+  <si>
+    <t>EP1802970</t>
+  </si>
+  <si>
+    <t>Anderson R Doimo</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051210460954</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855738PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:10:46.36</t>
+  </si>
+  <si>
+    <t>1126.20</t>
+  </si>
+  <si>
+    <t>13965130000100&amp;NA</t>
+  </si>
+  <si>
+    <t>B71576</t>
+  </si>
+  <si>
+    <t>ENERGY &amp; TELL SOL Q REDUZ CUST</t>
+  </si>
+  <si>
+    <t>EP1753516</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051211060955</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855739PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:11:06.96</t>
+  </si>
+  <si>
+    <t>EP1735901</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051219250985</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855771PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:19:25.46</t>
+  </si>
+  <si>
+    <t>2958.63</t>
+  </si>
+  <si>
+    <t>11314113000188&amp;18/11/2026</t>
+  </si>
+  <si>
+    <t>EP1800415</t>
+  </si>
+  <si>
+    <t>AREA 19 TELECOMUNICAÇOES</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051213480964</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855750PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:13:48.977</t>
+  </si>
+  <si>
+    <t>2800.00</t>
+  </si>
+  <si>
+    <t>59576215000106&amp;22/10/2026</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051213530965</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855751PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:13:53.277</t>
+  </si>
+  <si>
+    <t>15.93</t>
   </si>
 </sst>
 </file>
@@ -1740,7 +2685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{442415D8-C6A7-43A8-8242-0B2814FB2593}">
-  <dimension ref="A1:U94"/>
+  <dimension ref="A1:U108"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.36328125" bestFit="1" customWidth="1"/>
@@ -1767,497 +2712,500 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" t="s">
         <v>40</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>41</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>42</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>43</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>44</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>45</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>46</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>47</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>48</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>49</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>50</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>51</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>52</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>53</v>
-      </c>
-      <c r="O1" t="s">
-        <v>54</v>
       </c>
       <c r="P1" t="s">
         <v>0</v>
       </c>
       <c r="Q1" t="s">
+        <v>54</v>
+      </c>
+      <c r="R1" t="s">
         <v>55</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>56</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>57</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>58</v>
-      </c>
-      <c r="U1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>242</v>
+        <v>430</v>
       </c>
       <c r="B2" t="s">
-        <v>242</v>
+        <v>431</v>
       </c>
       <c r="C2" t="s">
-        <v>243</v>
+        <v>432</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>244</v>
+        <v>433</v>
       </c>
       <c r="G2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H2" t="s">
-        <v>245</v>
+        <v>60</v>
+      </c>
+      <c r="H2">
+        <v>1329151</v>
       </c>
       <c r="I2" s="1">
-        <v>46241</v>
+        <v>46296</v>
       </c>
       <c r="J2">
-        <v>750</v>
-      </c>
-      <c r="K2">
-        <v>45815647000100</v>
+        <v>9079.8799999999992</v>
+      </c>
+      <c r="K2" t="s">
+        <v>434</v>
       </c>
       <c r="L2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M2" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="O2" t="s">
-        <v>246</v>
+        <v>435</v>
       </c>
       <c r="P2" t="s">
-        <v>247</v>
+        <v>436</v>
       </c>
       <c r="Q2" t="s">
-        <v>248</v>
+        <v>437</v>
       </c>
       <c r="R2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T2" t="s">
-        <v>12</v>
+        <v>413</v>
       </c>
       <c r="U2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>266</v>
+        <v>438</v>
       </c>
       <c r="B3" t="s">
-        <v>267</v>
+        <v>439</v>
       </c>
       <c r="C3" t="s">
-        <v>268</v>
+        <v>440</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>83</v>
+        <v>441</v>
       </c>
       <c r="G3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>757</v>
+        <v>220</v>
       </c>
       <c r="I3" s="1">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="J3">
-        <v>500</v>
+        <v>3400</v>
       </c>
       <c r="K3" t="s">
-        <v>269</v>
+        <v>442</v>
       </c>
       <c r="L3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M3" t="s">
-        <v>85</v>
+        <v>443</v>
       </c>
       <c r="O3" t="s">
-        <v>11</v>
+        <v>444</v>
       </c>
       <c r="P3" t="s">
-        <v>256</v>
+        <v>445</v>
       </c>
       <c r="Q3" t="s">
-        <v>86</v>
+        <v>446</v>
       </c>
       <c r="R3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T3" t="s">
-        <v>29</v>
+        <v>447</v>
       </c>
       <c r="U3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>270</v>
+        <v>448</v>
       </c>
       <c r="B4" t="s">
-        <v>271</v>
+        <v>449</v>
       </c>
       <c r="C4" t="s">
-        <v>272</v>
+        <v>450</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>451</v>
       </c>
       <c r="G4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H4">
-        <v>755</v>
+        <v>177670</v>
       </c>
       <c r="I4" s="1">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="J4">
-        <v>500</v>
+        <v>19415.98</v>
       </c>
       <c r="K4" t="s">
-        <v>269</v>
+        <v>452</v>
       </c>
       <c r="L4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M4" t="s">
-        <v>85</v>
+        <v>453</v>
       </c>
       <c r="O4" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="P4" t="s">
         <v>256</v>
       </c>
       <c r="Q4" t="s">
-        <v>86</v>
+        <v>454</v>
       </c>
       <c r="R4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T4" t="s">
-        <v>29</v>
+        <v>455</v>
       </c>
       <c r="U4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>273</v>
+        <v>456</v>
       </c>
       <c r="B5" t="s">
-        <v>274</v>
+        <v>457</v>
       </c>
       <c r="C5" t="s">
-        <v>275</v>
+        <v>458</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>83</v>
+        <v>459</v>
       </c>
       <c r="G5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H5">
-        <v>754</v>
+        <v>177671</v>
       </c>
       <c r="I5" s="1">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="J5">
-        <v>500</v>
+        <v>1939.39</v>
       </c>
       <c r="K5" t="s">
-        <v>269</v>
+        <v>452</v>
       </c>
       <c r="L5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M5" t="s">
-        <v>85</v>
+        <v>453</v>
       </c>
       <c r="O5" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="P5" t="s">
         <v>256</v>
       </c>
       <c r="Q5" t="s">
-        <v>86</v>
+        <v>460</v>
       </c>
       <c r="R5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T5" t="s">
-        <v>29</v>
+        <v>455</v>
       </c>
       <c r="U5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>276</v>
+        <v>461</v>
       </c>
       <c r="B6" t="s">
-        <v>277</v>
+        <v>462</v>
       </c>
       <c r="C6" t="s">
-        <v>278</v>
+        <v>463</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
-        <v>279</v>
+        <v>464</v>
       </c>
       <c r="G6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H6">
-        <v>752</v>
+        <v>39</v>
       </c>
       <c r="I6" s="1">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="J6" s="2">
-        <v>18357.18</v>
+        <v>23000</v>
       </c>
       <c r="K6" t="s">
-        <v>280</v>
+        <v>465</v>
       </c>
       <c r="L6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M6" t="s">
-        <v>281</v>
+        <v>443</v>
       </c>
       <c r="O6" t="s">
-        <v>282</v>
+        <v>466</v>
       </c>
       <c r="P6" t="s">
-        <v>283</v>
+        <v>467</v>
       </c>
       <c r="Q6" t="s">
-        <v>284</v>
+        <v>468</v>
       </c>
       <c r="R6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T6" t="s">
-        <v>285</v>
+        <v>12</v>
       </c>
       <c r="U6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>286</v>
+        <v>469</v>
       </c>
       <c r="B7" t="s">
-        <v>287</v>
+        <v>470</v>
       </c>
       <c r="C7" t="s">
-        <v>288</v>
+        <v>471</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
-        <v>289</v>
+        <v>472</v>
       </c>
       <c r="G7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H7">
-        <v>260283</v>
+        <v>61032</v>
       </c>
       <c r="I7" s="1">
-        <v>46248</v>
+        <v>46296</v>
       </c>
       <c r="J7" s="2">
-        <v>2983.75</v>
+        <v>484.87</v>
       </c>
       <c r="K7" t="s">
-        <v>290</v>
+        <v>473</v>
       </c>
       <c r="L7" t="s">
-        <v>63</v>
+        <v>62</v>
+      </c>
+      <c r="M7" t="s">
+        <v>162</v>
       </c>
       <c r="O7" t="s">
-        <v>291</v>
+        <v>474</v>
       </c>
       <c r="P7" t="s">
-        <v>292</v>
+        <v>475</v>
       </c>
       <c r="Q7" t="s">
-        <v>137</v>
+        <v>476</v>
       </c>
       <c r="R7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T7" t="s">
-        <v>293</v>
+        <v>477</v>
       </c>
       <c r="U7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>294</v>
+        <v>234</v>
       </c>
       <c r="B8" t="s">
-        <v>295</v>
+        <v>234</v>
       </c>
       <c r="C8" t="s">
-        <v>296</v>
+        <v>235</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>297</v>
+        <v>236</v>
       </c>
       <c r="G8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H8">
-        <v>751</v>
+        <v>60</v>
+      </c>
+      <c r="H8" t="s">
+        <v>237</v>
       </c>
       <c r="I8" s="1">
-        <v>46294</v>
+        <v>46241</v>
       </c>
       <c r="J8" s="2">
-        <v>5856.07</v>
-      </c>
-      <c r="K8" t="s">
-        <v>280</v>
+        <v>750</v>
+      </c>
+      <c r="K8">
+        <v>45815647000100</v>
       </c>
       <c r="L8" t="s">
+        <v>62</v>
+      </c>
+      <c r="M8" t="s">
         <v>63</v>
       </c>
-      <c r="M8" t="s">
-        <v>281</v>
-      </c>
       <c r="O8" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="P8" t="s">
-        <v>283</v>
+        <v>239</v>
       </c>
       <c r="Q8" t="s">
-        <v>284</v>
+        <v>240</v>
       </c>
       <c r="R8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T8" t="s">
-        <v>285</v>
+        <v>12</v>
       </c>
       <c r="U8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" t="s">
         <v>69</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>70</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" t="s">
         <v>71</v>
       </c>
-      <c r="D9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" t="s">
-        <v>72</v>
-      </c>
       <c r="G9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H9">
         <v>201</v>
@@ -2269,3095 +3217,3089 @@
         <v>45439</v>
       </c>
       <c r="K9" t="s">
+        <v>72</v>
+      </c>
+      <c r="L9" t="s">
+        <v>62</v>
+      </c>
+      <c r="M9" t="s">
         <v>73</v>
-      </c>
-      <c r="L9" t="s">
-        <v>63</v>
-      </c>
-      <c r="M9" t="s">
-        <v>74</v>
       </c>
       <c r="O9" t="s">
         <v>21</v>
       </c>
       <c r="P9" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="Q9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T9" t="s">
         <v>10</v>
       </c>
       <c r="U9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>107</v>
+        <v>258</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>259</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>260</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="G10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H10">
-        <v>373798</v>
+        <v>757</v>
       </c>
       <c r="I10" s="1">
-        <v>46195</v>
+        <v>46294</v>
       </c>
       <c r="J10" s="2">
-        <v>5136.25</v>
+        <v>500</v>
       </c>
       <c r="K10" t="s">
-        <v>111</v>
+        <v>261</v>
       </c>
       <c r="L10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M10" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="O10" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="P10" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="Q10" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="R10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T10" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="U10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>113</v>
+        <v>262</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="G11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H11">
-        <v>97322</v>
+        <v>755</v>
       </c>
       <c r="I11" s="1">
-        <v>46143</v>
+        <v>46294</v>
       </c>
       <c r="J11" s="2">
-        <v>1678.6</v>
+        <v>500</v>
       </c>
       <c r="K11" t="s">
-        <v>117</v>
+        <v>261</v>
       </c>
       <c r="L11" t="s">
-        <v>63</v>
+        <v>62</v>
+      </c>
+      <c r="M11" t="s">
+        <v>84</v>
       </c>
       <c r="O11" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P11" t="s">
-        <v>5</v>
+        <v>248</v>
       </c>
       <c r="Q11" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="R11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S11" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="T11" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="U11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>120</v>
+        <v>265</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>266</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>267</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="G12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H12">
-        <v>156553</v>
+        <v>754</v>
       </c>
       <c r="I12" s="1">
-        <v>46174</v>
+        <v>46294</v>
       </c>
       <c r="J12" s="2">
-        <v>1928</v>
+        <v>500</v>
       </c>
       <c r="K12" t="s">
-        <v>124</v>
+        <v>261</v>
       </c>
       <c r="L12" t="s">
-        <v>63</v>
+        <v>62</v>
+      </c>
+      <c r="M12" t="s">
+        <v>84</v>
       </c>
       <c r="O12" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P12" t="s">
-        <v>5</v>
+        <v>248</v>
       </c>
       <c r="Q12" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="R12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S12" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="T12" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="U12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>125</v>
+        <v>268</v>
       </c>
       <c r="B13" t="s">
-        <v>126</v>
+        <v>269</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>270</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>128</v>
+        <v>271</v>
       </c>
       <c r="G13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H13">
-        <v>12958</v>
+        <v>752</v>
       </c>
       <c r="I13" s="1">
-        <v>46244</v>
+        <v>46294</v>
       </c>
       <c r="J13" s="2">
-        <v>746101.35</v>
+        <v>18357.18</v>
       </c>
       <c r="K13" t="s">
-        <v>129</v>
+        <v>272</v>
       </c>
       <c r="L13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M13" t="s">
-        <v>130</v>
+        <v>273</v>
       </c>
       <c r="O13" t="s">
-        <v>9</v>
+        <v>274</v>
       </c>
       <c r="P13" t="s">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="Q13" t="s">
-        <v>131</v>
+        <v>276</v>
       </c>
       <c r="R13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T13" t="s">
-        <v>16</v>
+        <v>277</v>
       </c>
       <c r="U13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>132</v>
+        <v>278</v>
       </c>
       <c r="B14" t="s">
-        <v>133</v>
+        <v>279</v>
       </c>
       <c r="C14" t="s">
-        <v>134</v>
+        <v>280</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14" t="s">
-        <v>135</v>
+        <v>281</v>
       </c>
       <c r="G14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H14">
-        <v>37941</v>
+        <v>260283</v>
       </c>
       <c r="I14" s="1">
-        <v>46120</v>
+        <v>46248</v>
       </c>
       <c r="J14" s="2">
-        <v>1314.09</v>
+        <v>2983.75</v>
       </c>
       <c r="K14" t="s">
+        <v>282</v>
+      </c>
+      <c r="L14" t="s">
+        <v>62</v>
+      </c>
+      <c r="O14" t="s">
+        <v>283</v>
+      </c>
+      <c r="P14" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q14" t="s">
         <v>136</v>
       </c>
-      <c r="L14" t="s">
-        <v>63</v>
-      </c>
-      <c r="O14" t="s">
-        <v>4</v>
-      </c>
-      <c r="P14" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>137</v>
-      </c>
       <c r="R14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S14" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="T14" t="s">
-        <v>3</v>
+        <v>285</v>
       </c>
       <c r="U14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>478</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>479</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>480</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>79</v>
+        <v>481</v>
       </c>
       <c r="G15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H15">
-        <v>157417</v>
+        <v>61031</v>
       </c>
       <c r="I15" s="1">
-        <v>46283</v>
+        <v>46296</v>
       </c>
       <c r="J15" s="2">
-        <v>199</v>
+        <v>976.95</v>
       </c>
       <c r="K15" t="s">
-        <v>80</v>
+        <v>473</v>
       </c>
       <c r="L15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M15" t="s">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="O15" t="s">
-        <v>37</v>
+        <v>474</v>
       </c>
       <c r="P15" t="s">
-        <v>240</v>
+        <v>475</v>
       </c>
       <c r="Q15" t="s">
-        <v>82</v>
+        <v>476</v>
       </c>
       <c r="R15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T15" t="s">
-        <v>27</v>
+        <v>477</v>
       </c>
       <c r="U15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>482</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>483</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>484</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
-        <v>90</v>
+        <v>485</v>
       </c>
       <c r="G16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H16">
-        <v>143685</v>
+        <v>21027</v>
       </c>
       <c r="I16" s="1">
-        <v>46220</v>
+        <v>46296</v>
       </c>
       <c r="J16" s="2">
-        <v>560.28</v>
+        <v>2918.92</v>
       </c>
       <c r="K16" t="s">
-        <v>91</v>
+        <v>486</v>
       </c>
       <c r="L16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M16" t="s">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="O16" t="s">
-        <v>13</v>
+        <v>487</v>
       </c>
       <c r="P16" t="s">
-        <v>251</v>
+        <v>488</v>
       </c>
       <c r="Q16" t="s">
-        <v>92</v>
+        <v>489</v>
       </c>
       <c r="R16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T16" t="s">
-        <v>1</v>
+        <v>413</v>
       </c>
       <c r="U16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>298</v>
+        <v>490</v>
       </c>
       <c r="B17" t="s">
-        <v>299</v>
+        <v>491</v>
       </c>
       <c r="C17" t="s">
-        <v>300</v>
+        <v>492</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" t="s">
-        <v>301</v>
+        <v>493</v>
       </c>
       <c r="G17" t="s">
-        <v>61</v>
-      </c>
-      <c r="H17" t="s">
-        <v>302</v>
+        <v>60</v>
+      </c>
+      <c r="H17">
+        <v>22573</v>
       </c>
       <c r="I17" s="1">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="J17" s="2">
-        <v>341619.74</v>
+        <v>950</v>
       </c>
       <c r="K17" t="s">
-        <v>303</v>
+        <v>494</v>
       </c>
       <c r="L17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O17" t="s">
-        <v>282</v>
+        <v>495</v>
       </c>
       <c r="P17" t="s">
-        <v>283</v>
+        <v>496</v>
       </c>
       <c r="Q17" t="s">
-        <v>284</v>
+        <v>497</v>
       </c>
       <c r="R17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T17" t="s">
-        <v>285</v>
+        <v>477</v>
       </c>
       <c r="U17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="G18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H18">
-        <v>21941</v>
+        <v>157417</v>
       </c>
       <c r="I18" s="1">
-        <v>46247</v>
+        <v>46283</v>
       </c>
       <c r="J18" s="2">
-        <v>7881.75</v>
+        <v>199</v>
       </c>
       <c r="K18" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M18" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="O18" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="P18" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="Q18" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="R18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T18" t="s">
-        <v>293</v>
+        <v>27</v>
       </c>
       <c r="U18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H19">
-        <v>5053</v>
+        <v>143685</v>
       </c>
       <c r="I19" s="1">
-        <v>46251</v>
+        <v>46220</v>
       </c>
       <c r="J19" s="2">
-        <v>719</v>
+        <v>560.28</v>
       </c>
       <c r="K19" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="L19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M19" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="O19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P19" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="Q19" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="R19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T19" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="U19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>152</v>
+        <v>290</v>
       </c>
       <c r="B20" t="s">
-        <v>153</v>
+        <v>291</v>
       </c>
       <c r="C20" t="s">
-        <v>154</v>
+        <v>292</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E20" t="s">
-        <v>155</v>
+        <v>293</v>
       </c>
       <c r="G20" t="s">
-        <v>61</v>
-      </c>
-      <c r="H20">
-        <v>237</v>
+        <v>60</v>
+      </c>
+      <c r="H20" t="s">
+        <v>294</v>
       </c>
       <c r="I20" s="1">
-        <v>46282</v>
+        <v>46294</v>
       </c>
       <c r="J20" s="2">
-        <v>35467.589999999997</v>
-      </c>
-      <c r="K20">
-        <v>51990695000137</v>
+        <v>341619.74</v>
+      </c>
+      <c r="K20" t="s">
+        <v>295</v>
       </c>
       <c r="L20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O20" t="s">
-        <v>38</v>
+        <v>274</v>
       </c>
       <c r="P20" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="Q20" t="s">
-        <v>156</v>
+        <v>276</v>
       </c>
       <c r="R20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T20" t="s">
-        <v>31</v>
+        <v>277</v>
       </c>
       <c r="U20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>157</v>
+        <v>286</v>
       </c>
       <c r="B21" t="s">
-        <v>158</v>
+        <v>287</v>
       </c>
       <c r="C21" t="s">
-        <v>159</v>
+        <v>288</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E21" t="s">
-        <v>160</v>
+        <v>289</v>
       </c>
       <c r="G21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H21">
-        <v>3841</v>
+        <v>751</v>
       </c>
       <c r="I21" s="1">
-        <v>46276</v>
+        <v>46294</v>
       </c>
       <c r="J21" s="2">
-        <v>1470</v>
+        <v>5856.07</v>
       </c>
       <c r="K21" t="s">
-        <v>161</v>
+        <v>272</v>
       </c>
       <c r="L21" t="s">
-        <v>63</v>
+        <v>62</v>
+      </c>
+      <c r="M21" t="s">
+        <v>273</v>
       </c>
       <c r="O21" t="s">
-        <v>35</v>
+        <v>274</v>
       </c>
       <c r="P21" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="Q21" t="s">
-        <v>162</v>
+        <v>276</v>
       </c>
       <c r="R21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T21" t="s">
-        <v>33</v>
+        <v>277</v>
       </c>
       <c r="U21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>304</v>
+        <v>353</v>
       </c>
       <c r="B22" t="s">
-        <v>305</v>
+        <v>354</v>
       </c>
       <c r="C22" t="s">
-        <v>306</v>
+        <v>355</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" t="s">
-        <v>307</v>
+        <v>82</v>
       </c>
       <c r="G22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H22">
-        <v>756</v>
+        <v>774</v>
       </c>
       <c r="I22" s="1">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="J22" s="2">
-        <v>41919.46</v>
+        <v>500</v>
       </c>
       <c r="K22" t="s">
-        <v>308</v>
+        <v>261</v>
       </c>
       <c r="L22" t="s">
-        <v>63</v>
+        <v>62</v>
+      </c>
+      <c r="M22" t="s">
+        <v>84</v>
       </c>
       <c r="O22" t="s">
-        <v>309</v>
+        <v>11</v>
       </c>
       <c r="P22" t="s">
-        <v>310</v>
+        <v>248</v>
       </c>
       <c r="Q22" t="s">
-        <v>311</v>
+        <v>85</v>
       </c>
       <c r="R22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T22" t="s">
-        <v>312</v>
+        <v>29</v>
       </c>
       <c r="U22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>313</v>
+        <v>356</v>
       </c>
       <c r="B23" t="s">
-        <v>314</v>
+        <v>357</v>
       </c>
       <c r="C23" t="s">
-        <v>315</v>
+        <v>358</v>
       </c>
       <c r="D23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E23" t="s">
-        <v>316</v>
+        <v>82</v>
       </c>
       <c r="G23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H23">
-        <v>571</v>
+        <v>773</v>
       </c>
       <c r="I23" s="1">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="J23" s="2">
-        <v>3628</v>
+        <v>500</v>
       </c>
       <c r="K23" t="s">
-        <v>317</v>
+        <v>261</v>
       </c>
       <c r="L23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M23" t="s">
-        <v>318</v>
+        <v>84</v>
       </c>
       <c r="O23" t="s">
-        <v>319</v>
+        <v>11</v>
       </c>
       <c r="P23" t="s">
-        <v>320</v>
+        <v>248</v>
       </c>
       <c r="Q23" t="s">
-        <v>321</v>
+        <v>85</v>
       </c>
       <c r="R23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T23" t="s">
-        <v>322</v>
+        <v>29</v>
       </c>
       <c r="U23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
       <c r="B24" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="C24" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="D24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24" t="s">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="G24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H24">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="I24" s="1">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="J24" s="2">
-        <v>1700</v>
+        <v>500</v>
       </c>
       <c r="K24" t="s">
-        <v>327</v>
+        <v>261</v>
       </c>
       <c r="L24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M24" t="s">
-        <v>328</v>
+        <v>84</v>
       </c>
       <c r="O24" t="s">
-        <v>329</v>
+        <v>11</v>
       </c>
       <c r="P24" t="s">
-        <v>330</v>
+        <v>248</v>
       </c>
       <c r="Q24" t="s">
-        <v>331</v>
+        <v>85</v>
       </c>
       <c r="R24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T24" t="s">
-        <v>312</v>
+        <v>29</v>
       </c>
       <c r="U24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>332</v>
+        <v>498</v>
       </c>
       <c r="B25" t="s">
-        <v>333</v>
+        <v>499</v>
       </c>
       <c r="C25" t="s">
-        <v>334</v>
+        <v>500</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E25" t="s">
-        <v>175</v>
+        <v>501</v>
       </c>
       <c r="G25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H25">
-        <v>251785</v>
+        <v>3243</v>
       </c>
       <c r="I25" s="1">
         <v>46296</v>
       </c>
       <c r="J25" s="2">
-        <v>69505.789999999994</v>
+        <v>2650</v>
       </c>
       <c r="K25" t="s">
-        <v>335</v>
+        <v>502</v>
       </c>
       <c r="L25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M25" t="s">
-        <v>163</v>
+        <v>503</v>
       </c>
       <c r="O25" t="s">
-        <v>19</v>
+        <v>504</v>
       </c>
       <c r="P25" t="s">
-        <v>250</v>
+        <v>505</v>
       </c>
       <c r="Q25" t="s">
-        <v>177</v>
+        <v>506</v>
       </c>
       <c r="R25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T25" t="s">
-        <v>3</v>
+        <v>304</v>
       </c>
       <c r="U25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>336</v>
+        <v>507</v>
       </c>
       <c r="B26" t="s">
-        <v>337</v>
+        <v>508</v>
       </c>
       <c r="C26" t="s">
-        <v>338</v>
+        <v>509</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E26" t="s">
-        <v>339</v>
+        <v>510</v>
       </c>
       <c r="G26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H26">
-        <v>1657</v>
+        <v>882</v>
       </c>
       <c r="I26" s="1">
         <v>46296</v>
       </c>
       <c r="J26" s="2">
-        <v>9909.09</v>
+        <v>492.26</v>
       </c>
       <c r="K26" t="s">
-        <v>340</v>
+        <v>511</v>
       </c>
       <c r="L26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M26" t="s">
-        <v>341</v>
+        <v>512</v>
       </c>
       <c r="O26" t="s">
-        <v>342</v>
+        <v>513</v>
       </c>
       <c r="P26" t="s">
-        <v>343</v>
+        <v>514</v>
       </c>
       <c r="Q26" t="s">
-        <v>344</v>
+        <v>515</v>
       </c>
       <c r="R26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T26" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="U26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>345</v>
+        <v>516</v>
       </c>
       <c r="B27" t="s">
-        <v>346</v>
+        <v>517</v>
       </c>
       <c r="C27" t="s">
-        <v>347</v>
+        <v>518</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E27" t="s">
-        <v>348</v>
+        <v>519</v>
       </c>
       <c r="G27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H27">
-        <v>1658</v>
+        <v>16607</v>
       </c>
       <c r="I27" s="1">
         <v>46296</v>
       </c>
       <c r="J27" s="2">
-        <v>9000</v>
+        <v>2965.55</v>
       </c>
       <c r="K27" t="s">
-        <v>340</v>
+        <v>520</v>
       </c>
       <c r="L27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M27" t="s">
-        <v>341</v>
+        <v>84</v>
       </c>
       <c r="O27" t="s">
-        <v>342</v>
+        <v>521</v>
       </c>
       <c r="P27" t="s">
-        <v>343</v>
+        <v>522</v>
       </c>
       <c r="Q27" t="s">
-        <v>344</v>
+        <v>523</v>
       </c>
       <c r="R27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T27" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="U27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>349</v>
+        <v>524</v>
       </c>
       <c r="B28" t="s">
-        <v>350</v>
+        <v>525</v>
       </c>
       <c r="C28" t="s">
-        <v>351</v>
+        <v>526</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E28" t="s">
-        <v>352</v>
+        <v>527</v>
       </c>
       <c r="G28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H28">
-        <v>10017</v>
+        <v>60201</v>
       </c>
       <c r="I28" s="1">
         <v>46296</v>
       </c>
       <c r="J28" s="2">
-        <v>247890.09</v>
+        <v>587.86</v>
       </c>
       <c r="K28" t="s">
-        <v>353</v>
+        <v>473</v>
       </c>
       <c r="L28" t="s">
-        <v>63</v>
+        <v>62</v>
+      </c>
+      <c r="M28" t="s">
+        <v>162</v>
       </c>
       <c r="O28" t="s">
-        <v>354</v>
+        <v>474</v>
       </c>
       <c r="P28" t="s">
-        <v>355</v>
+        <v>475</v>
       </c>
       <c r="Q28" t="s">
-        <v>356</v>
+        <v>528</v>
       </c>
       <c r="R28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T28" t="s">
-        <v>312</v>
+        <v>477</v>
       </c>
       <c r="U28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>357</v>
+        <v>529</v>
       </c>
       <c r="B29" t="s">
-        <v>358</v>
+        <v>530</v>
       </c>
       <c r="C29" t="s">
-        <v>359</v>
+        <v>531</v>
       </c>
       <c r="D29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E29" t="s">
-        <v>360</v>
+        <v>532</v>
       </c>
       <c r="G29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H29">
-        <v>1006</v>
+        <v>31567</v>
       </c>
       <c r="I29" s="1">
         <v>46296</v>
       </c>
       <c r="J29" s="2">
-        <v>28450.799999999999</v>
+        <v>6144</v>
       </c>
       <c r="K29" t="s">
-        <v>353</v>
+        <v>533</v>
       </c>
       <c r="L29" t="s">
-        <v>63</v>
+        <v>62</v>
+      </c>
+      <c r="M29" t="s">
+        <v>104</v>
       </c>
       <c r="O29" t="s">
-        <v>354</v>
+        <v>534</v>
       </c>
       <c r="P29" t="s">
-        <v>355</v>
+        <v>535</v>
       </c>
       <c r="Q29" t="s">
-        <v>361</v>
+        <v>536</v>
       </c>
       <c r="R29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T29" t="s">
-        <v>293</v>
+        <v>413</v>
       </c>
       <c r="U29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>164</v>
+        <v>537</v>
       </c>
       <c r="B30" t="s">
-        <v>165</v>
+        <v>538</v>
       </c>
       <c r="C30" t="s">
-        <v>166</v>
+        <v>539</v>
       </c>
       <c r="D30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E30" t="s">
-        <v>167</v>
+        <v>540</v>
       </c>
       <c r="G30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H30">
-        <v>12908</v>
+        <v>2802</v>
       </c>
       <c r="I30" s="1">
-        <v>46205</v>
+        <v>46296</v>
       </c>
       <c r="J30">
-        <v>643664.51</v>
+        <v>5822.99</v>
       </c>
       <c r="K30" t="s">
-        <v>168</v>
+        <v>541</v>
       </c>
       <c r="L30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M30" t="s">
-        <v>130</v>
+        <v>542</v>
       </c>
       <c r="O30" t="s">
-        <v>9</v>
+        <v>543</v>
       </c>
       <c r="P30" t="s">
-        <v>249</v>
+        <v>544</v>
       </c>
       <c r="Q30" t="s">
-        <v>131</v>
+        <v>545</v>
       </c>
       <c r="R30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S30" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="T30" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="U30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>185</v>
+        <v>546</v>
       </c>
       <c r="B31" t="s">
-        <v>186</v>
+        <v>547</v>
       </c>
       <c r="C31" t="s">
-        <v>187</v>
+        <v>548</v>
       </c>
       <c r="D31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E31" t="s">
-        <v>188</v>
+        <v>549</v>
       </c>
       <c r="G31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H31">
-        <v>13020</v>
+        <v>2800</v>
       </c>
       <c r="I31" s="1">
-        <v>46268</v>
+        <v>46296</v>
       </c>
       <c r="J31">
-        <v>330986.02</v>
+        <v>5400</v>
       </c>
       <c r="K31" t="s">
-        <v>189</v>
+        <v>541</v>
       </c>
       <c r="L31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M31" t="s">
-        <v>190</v>
+        <v>542</v>
       </c>
       <c r="O31" t="s">
-        <v>9</v>
+        <v>543</v>
       </c>
       <c r="P31" t="s">
-        <v>249</v>
+        <v>544</v>
       </c>
       <c r="Q31" t="s">
-        <v>131</v>
+        <v>550</v>
       </c>
       <c r="R31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T31" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="U31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>191</v>
+        <v>551</v>
       </c>
       <c r="B32" t="s">
-        <v>192</v>
+        <v>552</v>
       </c>
       <c r="C32" t="s">
-        <v>193</v>
+        <v>553</v>
       </c>
       <c r="D32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E32" t="s">
-        <v>194</v>
+        <v>554</v>
       </c>
       <c r="G32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H32">
-        <v>105</v>
+        <v>2041</v>
       </c>
       <c r="I32" s="1">
-        <v>46205</v>
+        <v>46296</v>
       </c>
       <c r="J32" s="2">
-        <v>8170</v>
+        <v>12769.32</v>
       </c>
       <c r="K32" t="s">
-        <v>195</v>
+        <v>555</v>
       </c>
       <c r="L32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M32" t="s">
-        <v>85</v>
+        <v>162</v>
       </c>
       <c r="O32" t="s">
-        <v>36</v>
+        <v>556</v>
       </c>
       <c r="P32" t="s">
-        <v>241</v>
+        <v>557</v>
       </c>
       <c r="Q32" t="s">
-        <v>196</v>
+        <v>558</v>
       </c>
       <c r="R32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S32" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="T32" t="s">
-        <v>23</v>
+        <v>477</v>
       </c>
       <c r="U32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>362</v>
+        <v>559</v>
       </c>
       <c r="B33" t="s">
-        <v>363</v>
+        <v>560</v>
       </c>
       <c r="C33" t="s">
-        <v>364</v>
+        <v>561</v>
       </c>
       <c r="D33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E33" t="s">
-        <v>83</v>
+        <v>562</v>
       </c>
       <c r="G33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H33">
-        <v>774</v>
+        <v>10858</v>
       </c>
       <c r="I33" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="J33" s="2">
-        <v>500</v>
+        <v>24302</v>
       </c>
       <c r="K33" t="s">
-        <v>269</v>
+        <v>181</v>
       </c>
       <c r="L33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M33" t="s">
-        <v>85</v>
+        <v>182</v>
       </c>
       <c r="O33" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="P33" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="Q33" t="s">
-        <v>86</v>
+        <v>563</v>
       </c>
       <c r="R33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T33" t="s">
-        <v>29</v>
+        <v>564</v>
       </c>
       <c r="U33" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>365</v>
+        <v>565</v>
       </c>
       <c r="B34" t="s">
-        <v>366</v>
+        <v>566</v>
       </c>
       <c r="C34" t="s">
-        <v>367</v>
+        <v>567</v>
       </c>
       <c r="D34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E34" t="s">
-        <v>83</v>
+        <v>568</v>
       </c>
       <c r="G34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H34">
-        <v>773</v>
+        <v>1246</v>
       </c>
       <c r="I34" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="J34" s="2">
-        <v>500</v>
+        <v>41270</v>
       </c>
       <c r="K34" t="s">
-        <v>269</v>
+        <v>569</v>
       </c>
       <c r="L34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M34" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="O34" t="s">
-        <v>11</v>
+        <v>570</v>
       </c>
       <c r="P34" t="s">
-        <v>256</v>
+        <v>571</v>
       </c>
       <c r="Q34" t="s">
-        <v>86</v>
+        <v>572</v>
       </c>
       <c r="R34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S34" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T34" t="s">
-        <v>29</v>
+        <v>413</v>
       </c>
       <c r="U34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>368</v>
+        <v>573</v>
       </c>
       <c r="B35" t="s">
-        <v>369</v>
+        <v>574</v>
       </c>
       <c r="C35" t="s">
-        <v>370</v>
+        <v>575</v>
       </c>
       <c r="D35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E35" t="s">
-        <v>83</v>
+        <v>576</v>
       </c>
       <c r="G35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H35">
-        <v>772</v>
+        <v>1232</v>
       </c>
       <c r="I35" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="J35">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="K35" t="s">
-        <v>269</v>
+        <v>569</v>
       </c>
       <c r="L35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M35" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="O35" t="s">
-        <v>11</v>
+        <v>570</v>
       </c>
       <c r="P35" t="s">
-        <v>256</v>
+        <v>571</v>
       </c>
       <c r="Q35" t="s">
-        <v>86</v>
+        <v>572</v>
       </c>
       <c r="R35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T35" t="s">
-        <v>29</v>
+        <v>413</v>
       </c>
       <c r="U35" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>178</v>
+        <v>577</v>
       </c>
       <c r="B36" t="s">
-        <v>179</v>
+        <v>578</v>
       </c>
       <c r="C36" t="s">
-        <v>180</v>
+        <v>579</v>
       </c>
       <c r="D36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E36" t="s">
-        <v>181</v>
+        <v>580</v>
       </c>
       <c r="G36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H36">
-        <v>10760</v>
+        <v>39807</v>
       </c>
       <c r="I36" s="1">
-        <v>46276</v>
+        <v>46296</v>
       </c>
       <c r="J36">
-        <v>3770.93</v>
+        <v>1575</v>
       </c>
       <c r="K36" t="s">
-        <v>182</v>
+        <v>581</v>
       </c>
       <c r="L36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M36" t="s">
-        <v>183</v>
+        <v>73</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>34</v>
+        <v>582</v>
       </c>
       <c r="P36" t="s">
-        <v>254</v>
+        <v>583</v>
       </c>
       <c r="Q36" t="s">
-        <v>184</v>
+        <v>584</v>
       </c>
       <c r="R36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T36" t="s">
-        <v>22</v>
+        <v>314</v>
       </c>
       <c r="U36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>169</v>
+        <v>585</v>
       </c>
       <c r="B37" t="s">
-        <v>170</v>
+        <v>586</v>
       </c>
       <c r="C37" t="s">
-        <v>171</v>
+        <v>587</v>
       </c>
       <c r="D37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E37" t="s">
-        <v>83</v>
+        <v>588</v>
       </c>
       <c r="G37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H37">
-        <v>460</v>
+        <v>1</v>
       </c>
       <c r="I37" s="1">
-        <v>46262</v>
+        <v>46296</v>
       </c>
       <c r="J37">
-        <v>500</v>
+        <v>40530</v>
       </c>
       <c r="K37" t="s">
-        <v>84</v>
+        <v>589</v>
       </c>
       <c r="L37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M37" t="s">
-        <v>85</v>
+        <v>542</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>11</v>
+        <v>590</v>
       </c>
       <c r="P37" t="s">
-        <v>256</v>
+        <v>591</v>
       </c>
       <c r="Q37" t="s">
-        <v>86</v>
+        <v>592</v>
       </c>
       <c r="R37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T37" t="s">
-        <v>18</v>
+        <v>285</v>
       </c>
       <c r="U37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>208</v>
+        <v>593</v>
       </c>
       <c r="B38" t="s">
-        <v>209</v>
+        <v>594</v>
       </c>
       <c r="C38" t="s">
-        <v>210</v>
+        <v>595</v>
       </c>
       <c r="D38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E38" t="s">
-        <v>211</v>
+        <v>596</v>
       </c>
       <c r="G38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H38">
-        <v>176266</v>
+        <v>2307</v>
       </c>
       <c r="I38" s="1">
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="J38">
-        <v>270515.57</v>
+        <v>17094</v>
       </c>
       <c r="K38" t="s">
-        <v>212</v>
+        <v>597</v>
       </c>
       <c r="L38" t="s">
-        <v>63</v>
+        <v>62</v>
+      </c>
+      <c r="M38" t="s">
+        <v>84</v>
       </c>
       <c r="O38" t="s">
-        <v>24</v>
+        <v>598</v>
       </c>
       <c r="P38" t="s">
-        <v>257</v>
+        <v>599</v>
       </c>
       <c r="Q38" t="s">
-        <v>213</v>
+        <v>600</v>
       </c>
       <c r="R38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T38" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="U38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>371</v>
+        <v>601</v>
       </c>
       <c r="B39" t="s">
-        <v>372</v>
+        <v>602</v>
       </c>
       <c r="C39" t="s">
-        <v>373</v>
+        <v>603</v>
       </c>
       <c r="D39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E39" t="s">
-        <v>83</v>
+        <v>604</v>
       </c>
       <c r="G39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H39">
-        <v>760</v>
+        <v>2145</v>
       </c>
       <c r="I39" s="1">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="J39">
-        <v>500</v>
+        <v>2270</v>
       </c>
       <c r="K39" t="s">
-        <v>269</v>
+        <v>605</v>
       </c>
       <c r="L39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M39" t="s">
-        <v>85</v>
+        <v>606</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>11</v>
+        <v>607</v>
       </c>
       <c r="P39" t="s">
-        <v>256</v>
+        <v>608</v>
       </c>
       <c r="Q39" t="s">
-        <v>86</v>
+        <v>609</v>
       </c>
       <c r="R39" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T39" t="s">
-        <v>29</v>
+        <v>447</v>
       </c>
       <c r="U39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>374</v>
+        <v>610</v>
       </c>
       <c r="B40" t="s">
-        <v>375</v>
+        <v>611</v>
       </c>
       <c r="C40" t="s">
-        <v>376</v>
+        <v>612</v>
       </c>
       <c r="D40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E40" t="s">
-        <v>83</v>
+        <v>613</v>
       </c>
       <c r="G40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H40">
-        <v>759</v>
+        <v>39808</v>
       </c>
       <c r="I40" s="1">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="J40">
-        <v>500</v>
+        <v>1575</v>
       </c>
       <c r="K40" t="s">
-        <v>269</v>
+        <v>614</v>
       </c>
       <c r="L40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M40" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="O40" t="s">
-        <v>11</v>
+        <v>582</v>
       </c>
       <c r="P40" t="s">
-        <v>256</v>
+        <v>583</v>
       </c>
       <c r="Q40" t="s">
-        <v>86</v>
+        <v>615</v>
       </c>
       <c r="R40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T40" t="s">
-        <v>29</v>
+        <v>314</v>
       </c>
       <c r="U40" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>377</v>
+        <v>616</v>
       </c>
       <c r="B41" t="s">
-        <v>378</v>
+        <v>617</v>
       </c>
       <c r="C41" t="s">
-        <v>379</v>
+        <v>618</v>
       </c>
       <c r="D41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E41" t="s">
-        <v>83</v>
+        <v>619</v>
       </c>
       <c r="G41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H41">
-        <v>758</v>
+        <v>21395</v>
       </c>
       <c r="I41" s="1">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="J41" s="2">
-        <v>500</v>
+        <v>2800</v>
       </c>
       <c r="K41" t="s">
-        <v>269</v>
+        <v>620</v>
       </c>
       <c r="L41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M41" t="s">
-        <v>85</v>
+        <v>332</v>
       </c>
       <c r="O41" t="s">
-        <v>11</v>
+        <v>621</v>
       </c>
       <c r="P41" t="s">
-        <v>256</v>
+        <v>622</v>
       </c>
       <c r="Q41" t="s">
-        <v>86</v>
+        <v>623</v>
       </c>
       <c r="R41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S41" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T41" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="U41" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>380</v>
+        <v>624</v>
       </c>
       <c r="B42" t="s">
-        <v>381</v>
+        <v>625</v>
       </c>
       <c r="C42" t="s">
-        <v>382</v>
+        <v>626</v>
       </c>
       <c r="D42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E42" t="s">
-        <v>83</v>
+        <v>627</v>
       </c>
       <c r="G42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H42">
-        <v>756</v>
+        <v>131</v>
       </c>
       <c r="I42" s="1">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="J42" s="2">
-        <v>500</v>
+        <v>26584.71</v>
       </c>
       <c r="K42" t="s">
-        <v>269</v>
+        <v>628</v>
       </c>
       <c r="L42" t="s">
-        <v>63</v>
-      </c>
-      <c r="M42" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="O42" t="s">
-        <v>11</v>
+        <v>629</v>
       </c>
       <c r="P42" t="s">
-        <v>256</v>
+        <v>630</v>
       </c>
       <c r="Q42" t="s">
-        <v>86</v>
+        <v>631</v>
       </c>
       <c r="R42" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T42" t="s">
-        <v>29</v>
+        <v>285</v>
       </c>
       <c r="U42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>383</v>
+        <v>632</v>
       </c>
       <c r="B43" t="s">
-        <v>384</v>
+        <v>633</v>
       </c>
       <c r="C43" t="s">
-        <v>385</v>
+        <v>634</v>
       </c>
       <c r="D43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E43" t="s">
-        <v>386</v>
+        <v>635</v>
       </c>
       <c r="G43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H43">
-        <v>750</v>
+        <v>53916126</v>
       </c>
       <c r="I43" s="1">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="J43" s="2">
-        <v>22920.95</v>
+        <v>17069.990000000002</v>
       </c>
       <c r="K43" t="s">
-        <v>280</v>
+        <v>636</v>
       </c>
       <c r="L43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M43" t="s">
-        <v>281</v>
+        <v>182</v>
       </c>
       <c r="O43" t="s">
-        <v>282</v>
+        <v>637</v>
       </c>
       <c r="P43" t="s">
-        <v>283</v>
+        <v>638</v>
       </c>
       <c r="Q43" t="s">
-        <v>284</v>
+        <v>639</v>
       </c>
       <c r="R43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T43" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="U43" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>235</v>
+        <v>640</v>
       </c>
       <c r="B44" t="s">
-        <v>236</v>
+        <v>641</v>
       </c>
       <c r="C44" t="s">
-        <v>237</v>
+        <v>642</v>
       </c>
       <c r="D44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E44" t="s">
-        <v>83</v>
+        <v>643</v>
       </c>
       <c r="G44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H44">
-        <v>464</v>
+        <v>40</v>
       </c>
       <c r="I44" s="1">
-        <v>46265</v>
+        <v>46297</v>
       </c>
       <c r="J44" s="2">
-        <v>500</v>
+        <v>6686.5</v>
       </c>
       <c r="K44" t="s">
-        <v>84</v>
+        <v>644</v>
       </c>
       <c r="L44" t="s">
+        <v>62</v>
+      </c>
+      <c r="M44" t="s">
         <v>63</v>
       </c>
-      <c r="M44" t="s">
-        <v>85</v>
-      </c>
       <c r="O44" t="s">
-        <v>11</v>
+        <v>645</v>
       </c>
       <c r="P44" t="s">
-        <v>256</v>
+        <v>646</v>
       </c>
       <c r="Q44" t="s">
-        <v>86</v>
+        <v>647</v>
       </c>
       <c r="R44" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T44" t="s">
-        <v>18</v>
+        <v>285</v>
       </c>
       <c r="U44" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>172</v>
+        <v>92</v>
       </c>
       <c r="B45" t="s">
-        <v>173</v>
+        <v>93</v>
       </c>
       <c r="C45" t="s">
-        <v>174</v>
+        <v>94</v>
       </c>
       <c r="D45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E45" t="s">
-        <v>175</v>
+        <v>95</v>
       </c>
       <c r="G45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H45">
-        <v>251216</v>
+        <v>21941</v>
       </c>
       <c r="I45" s="1">
-        <v>46283</v>
+        <v>46247</v>
       </c>
       <c r="J45" s="2">
-        <v>69505.789999999994</v>
+        <v>7881.75</v>
       </c>
       <c r="K45" t="s">
-        <v>176</v>
+        <v>96</v>
       </c>
       <c r="L45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M45" t="s">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="O45" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P45" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="Q45" t="s">
-        <v>177</v>
+        <v>98</v>
       </c>
       <c r="R45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S45" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T45" t="s">
-        <v>3</v>
+        <v>285</v>
       </c>
       <c r="U45" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>387</v>
+        <v>106</v>
       </c>
       <c r="B46" t="s">
-        <v>388</v>
+        <v>107</v>
       </c>
       <c r="C46" t="s">
-        <v>389</v>
+        <v>108</v>
       </c>
       <c r="D46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="G46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H46">
-        <v>766</v>
+        <v>373798</v>
       </c>
       <c r="I46" s="1">
-        <v>46294</v>
+        <v>46195</v>
       </c>
       <c r="J46">
-        <v>500</v>
+        <v>5136.25</v>
       </c>
       <c r="K46" t="s">
-        <v>269</v>
+        <v>110</v>
       </c>
       <c r="L46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M46" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="O46" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P46" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="Q46" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="R46" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T46" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="U46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>390</v>
+        <v>112</v>
       </c>
       <c r="B47" t="s">
-        <v>391</v>
+        <v>113</v>
       </c>
       <c r="C47" t="s">
-        <v>392</v>
+        <v>114</v>
       </c>
       <c r="D47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E47" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="G47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H47">
-        <v>763</v>
+        <v>97322</v>
       </c>
       <c r="I47" s="1">
-        <v>46294</v>
+        <v>46143</v>
       </c>
       <c r="J47">
-        <v>500</v>
+        <v>1678.6</v>
       </c>
       <c r="K47" t="s">
-        <v>269</v>
+        <v>116</v>
       </c>
       <c r="L47" t="s">
-        <v>63</v>
-      </c>
-      <c r="M47" t="s">
-        <v>281</v>
+        <v>62</v>
       </c>
       <c r="O47" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P47" t="s">
-        <v>256</v>
+        <v>5</v>
       </c>
       <c r="Q47" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="R47" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S47" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="T47" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="U47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>393</v>
+        <v>119</v>
       </c>
       <c r="B48" t="s">
-        <v>394</v>
+        <v>120</v>
       </c>
       <c r="C48" t="s">
-        <v>395</v>
+        <v>121</v>
       </c>
       <c r="D48" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E48" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="G48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H48">
-        <v>765</v>
+        <v>156553</v>
       </c>
       <c r="I48" s="1">
-        <v>46294</v>
+        <v>46174</v>
       </c>
       <c r="J48">
-        <v>500</v>
+        <v>1928</v>
       </c>
       <c r="K48" t="s">
-        <v>269</v>
+        <v>123</v>
       </c>
       <c r="L48" t="s">
-        <v>63</v>
-      </c>
-      <c r="M48" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="O48" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P48" t="s">
-        <v>256</v>
+        <v>5</v>
       </c>
       <c r="Q48" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="R48" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S48" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="T48" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="U48" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>396</v>
+        <v>124</v>
       </c>
       <c r="B49" t="s">
-        <v>397</v>
+        <v>125</v>
       </c>
       <c r="C49" t="s">
-        <v>398</v>
+        <v>126</v>
       </c>
       <c r="D49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E49" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="G49" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H49">
-        <v>764</v>
+        <v>12958</v>
       </c>
       <c r="I49" s="1">
-        <v>46294</v>
+        <v>46244</v>
       </c>
       <c r="J49" s="2">
-        <v>500</v>
+        <v>746101.35</v>
       </c>
       <c r="K49" t="s">
-        <v>269</v>
+        <v>128</v>
       </c>
       <c r="L49" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M49" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="O49" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P49" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="Q49" t="s">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="R49" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T49" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="U49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>399</v>
+        <v>296</v>
       </c>
       <c r="B50" t="s">
-        <v>400</v>
+        <v>297</v>
       </c>
       <c r="C50" t="s">
-        <v>401</v>
+        <v>298</v>
       </c>
       <c r="D50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E50" t="s">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="G50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H50">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="I50" s="1">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="J50">
-        <v>500</v>
+        <v>41919.46</v>
       </c>
       <c r="K50" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="L50" t="s">
-        <v>63</v>
-      </c>
-      <c r="M50" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="O50" t="s">
-        <v>11</v>
+        <v>301</v>
       </c>
       <c r="P50" t="s">
-        <v>256</v>
+        <v>302</v>
       </c>
       <c r="Q50" t="s">
-        <v>86</v>
+        <v>303</v>
       </c>
       <c r="R50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T50" t="s">
-        <v>29</v>
+        <v>304</v>
       </c>
       <c r="U50" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>138</v>
+        <v>305</v>
       </c>
       <c r="B51" t="s">
-        <v>139</v>
+        <v>306</v>
       </c>
       <c r="C51" t="s">
-        <v>140</v>
+        <v>307</v>
       </c>
       <c r="D51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E51" t="s">
-        <v>141</v>
+        <v>308</v>
       </c>
       <c r="G51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H51">
-        <v>32</v>
+        <v>571</v>
       </c>
       <c r="I51" s="1">
-        <v>46269</v>
+        <v>46296</v>
       </c>
       <c r="J51" s="2">
-        <v>25800</v>
+        <v>3628</v>
       </c>
       <c r="K51" t="s">
-        <v>142</v>
+        <v>309</v>
       </c>
       <c r="L51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M51" t="s">
-        <v>143</v>
+        <v>310</v>
       </c>
       <c r="O51" t="s">
-        <v>28</v>
+        <v>311</v>
       </c>
       <c r="P51" t="s">
-        <v>261</v>
+        <v>312</v>
       </c>
       <c r="Q51" t="s">
-        <v>144</v>
+        <v>313</v>
       </c>
       <c r="R51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T51" t="s">
-        <v>22</v>
+        <v>314</v>
       </c>
       <c r="U51" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>145</v>
+        <v>99</v>
       </c>
       <c r="B52" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="C52" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="D52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E52" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="G52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H52">
-        <v>798</v>
+        <v>5053</v>
       </c>
       <c r="I52" s="1">
-        <v>46269</v>
+        <v>46251</v>
       </c>
       <c r="J52">
-        <v>2890</v>
+        <v>719</v>
       </c>
       <c r="K52" t="s">
-        <v>149</v>
+        <v>103</v>
       </c>
       <c r="L52" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M52" t="s">
-        <v>150</v>
+        <v>104</v>
       </c>
       <c r="O52" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="P52" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="Q52" t="s">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="R52" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S52" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T52" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="U52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>214</v>
+        <v>151</v>
       </c>
       <c r="B53" t="s">
-        <v>215</v>
+        <v>152</v>
       </c>
       <c r="C53" t="s">
-        <v>216</v>
+        <v>153</v>
       </c>
       <c r="D53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E53" t="s">
-        <v>217</v>
+        <v>154</v>
       </c>
       <c r="G53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H53">
-        <v>21985</v>
+        <v>237</v>
       </c>
       <c r="I53" s="1">
-        <v>46262</v>
+        <v>46282</v>
       </c>
       <c r="J53" s="2">
-        <v>969.98</v>
-      </c>
-      <c r="K53" t="s">
-        <v>97</v>
+        <v>35467.589999999997</v>
+      </c>
+      <c r="K53">
+        <v>51990695000137</v>
       </c>
       <c r="L53" t="s">
-        <v>63</v>
-      </c>
-      <c r="M53" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="O53" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="P53" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="Q53" t="s">
-        <v>239</v>
+        <v>155</v>
       </c>
       <c r="R53" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S53" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T53" t="s">
-        <v>293</v>
+        <v>31</v>
       </c>
       <c r="U53" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>218</v>
+        <v>156</v>
       </c>
       <c r="B54" t="s">
-        <v>219</v>
+        <v>157</v>
       </c>
       <c r="C54" t="s">
-        <v>220</v>
+        <v>158</v>
       </c>
       <c r="D54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E54" t="s">
-        <v>221</v>
+        <v>159</v>
       </c>
       <c r="G54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H54">
-        <v>2808</v>
+        <v>3841</v>
       </c>
       <c r="I54" s="1">
-        <v>46267</v>
+        <v>46276</v>
       </c>
       <c r="J54">
-        <v>15900</v>
+        <v>1470</v>
       </c>
       <c r="K54" t="s">
-        <v>222</v>
+        <v>160</v>
       </c>
       <c r="L54" t="s">
-        <v>63</v>
-      </c>
-      <c r="M54" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O54" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P54" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Q54" t="s">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c r="R54" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S54" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T54" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="U54" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>402</v>
+        <v>137</v>
       </c>
       <c r="B55" t="s">
-        <v>403</v>
+        <v>138</v>
       </c>
       <c r="C55" t="s">
-        <v>404</v>
+        <v>139</v>
       </c>
       <c r="D55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E55" t="s">
-        <v>348</v>
+        <v>140</v>
       </c>
       <c r="G55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H55">
-        <v>1656</v>
+        <v>32</v>
       </c>
       <c r="I55" s="1">
-        <v>46296</v>
+        <v>46269</v>
       </c>
       <c r="J55" s="2">
-        <v>9000</v>
+        <v>25800</v>
       </c>
       <c r="K55" t="s">
-        <v>405</v>
+        <v>141</v>
       </c>
       <c r="L55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M55" t="s">
-        <v>341</v>
+        <v>142</v>
       </c>
       <c r="O55" t="s">
-        <v>342</v>
+        <v>28</v>
       </c>
       <c r="P55" t="s">
-        <v>343</v>
+        <v>253</v>
       </c>
       <c r="Q55" t="s">
-        <v>344</v>
+        <v>143</v>
       </c>
       <c r="R55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T55" t="s">
-        <v>293</v>
+        <v>22</v>
       </c>
       <c r="U55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>406</v>
+        <v>144</v>
       </c>
       <c r="B56" t="s">
-        <v>407</v>
+        <v>145</v>
       </c>
       <c r="C56" t="s">
-        <v>408</v>
+        <v>146</v>
       </c>
       <c r="D56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E56" t="s">
-        <v>409</v>
+        <v>147</v>
       </c>
       <c r="G56" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H56">
-        <v>2564</v>
+        <v>798</v>
       </c>
       <c r="I56" s="1">
-        <v>46296</v>
+        <v>46269</v>
       </c>
       <c r="J56" s="2">
-        <v>1300</v>
+        <v>2890</v>
       </c>
       <c r="K56" t="s">
-        <v>410</v>
+        <v>148</v>
       </c>
       <c r="L56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M56" t="s">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="O56" t="s">
-        <v>411</v>
+        <v>26</v>
       </c>
       <c r="P56" t="s">
-        <v>412</v>
+        <v>255</v>
       </c>
       <c r="Q56" t="s">
-        <v>413</v>
+        <v>150</v>
       </c>
       <c r="R56" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T56" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="U56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>414</v>
+        <v>340</v>
       </c>
       <c r="B57" t="s">
-        <v>415</v>
+        <v>341</v>
       </c>
       <c r="C57" t="s">
-        <v>416</v>
+        <v>342</v>
       </c>
       <c r="D57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E57" t="s">
-        <v>417</v>
+        <v>343</v>
       </c>
       <c r="G57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H57">
-        <v>6025</v>
+        <v>10017</v>
       </c>
       <c r="I57" s="1">
         <v>46296</v>
       </c>
       <c r="J57" s="2">
-        <v>9204</v>
+        <v>247890.09</v>
       </c>
       <c r="K57" t="s">
-        <v>418</v>
+        <v>344</v>
       </c>
       <c r="L57" t="s">
-        <v>63</v>
-      </c>
-      <c r="M57" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="O57" t="s">
-        <v>419</v>
+        <v>345</v>
       </c>
       <c r="P57" t="s">
-        <v>420</v>
+        <v>346</v>
       </c>
       <c r="Q57" t="s">
-        <v>421</v>
+        <v>347</v>
       </c>
       <c r="R57" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S57" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T57" t="s">
-        <v>422</v>
+        <v>304</v>
       </c>
       <c r="U57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>423</v>
+        <v>348</v>
       </c>
       <c r="B58" t="s">
-        <v>424</v>
+        <v>349</v>
       </c>
       <c r="C58" t="s">
-        <v>425</v>
+        <v>350</v>
       </c>
       <c r="D58" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E58" t="s">
-        <v>426</v>
+        <v>351</v>
       </c>
       <c r="G58" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H58">
-        <v>10823</v>
+        <v>1006</v>
       </c>
       <c r="I58" s="1">
         <v>46296</v>
       </c>
       <c r="J58" s="2">
-        <v>19950</v>
+        <v>28450.799999999999</v>
       </c>
       <c r="K58" t="s">
-        <v>427</v>
+        <v>344</v>
       </c>
       <c r="L58" t="s">
-        <v>63</v>
-      </c>
-      <c r="M58" t="s">
-        <v>428</v>
+        <v>62</v>
       </c>
       <c r="O58" t="s">
-        <v>429</v>
+        <v>345</v>
       </c>
       <c r="P58" t="s">
-        <v>430</v>
+        <v>346</v>
       </c>
       <c r="Q58" t="s">
-        <v>431</v>
+        <v>352</v>
       </c>
       <c r="R58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S58" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T58" t="s">
-        <v>312</v>
+        <v>285</v>
       </c>
       <c r="U58" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>432</v>
+        <v>131</v>
       </c>
       <c r="B59" t="s">
-        <v>433</v>
+        <v>132</v>
       </c>
       <c r="C59" t="s">
-        <v>434</v>
+        <v>133</v>
       </c>
       <c r="D59" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E59" t="s">
-        <v>435</v>
+        <v>134</v>
       </c>
       <c r="G59" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H59">
-        <v>342</v>
+        <v>37941</v>
       </c>
       <c r="I59" s="1">
-        <v>46296</v>
+        <v>46120</v>
       </c>
       <c r="J59" s="2">
-        <v>1270.83</v>
+        <v>1314.09</v>
       </c>
       <c r="K59" t="s">
-        <v>436</v>
+        <v>135</v>
       </c>
       <c r="L59" t="s">
-        <v>63</v>
-      </c>
-      <c r="M59" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="O59" t="s">
-        <v>342</v>
+        <v>4</v>
       </c>
       <c r="P59" t="s">
-        <v>343</v>
+        <v>5</v>
       </c>
       <c r="Q59" t="s">
-        <v>344</v>
+        <v>136</v>
       </c>
       <c r="R59" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S59" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="T59" t="s">
-        <v>293</v>
+        <v>3</v>
       </c>
       <c r="U59" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>224</v>
+        <v>362</v>
       </c>
       <c r="B60" t="s">
-        <v>225</v>
+        <v>363</v>
       </c>
       <c r="C60" t="s">
-        <v>226</v>
+        <v>364</v>
       </c>
       <c r="D60" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E60" t="s">
-        <v>227</v>
+        <v>82</v>
       </c>
       <c r="G60" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H60">
-        <v>26491</v>
+        <v>760</v>
       </c>
       <c r="I60" s="1">
-        <v>46267</v>
+        <v>46294</v>
       </c>
       <c r="J60" s="2">
-        <v>22510.52</v>
+        <v>500</v>
       </c>
       <c r="K60" t="s">
-        <v>62</v>
+        <v>261</v>
       </c>
       <c r="L60" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M60" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="O60" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="P60" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="Q60" t="s">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="R60" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S60" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T60" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="U60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>229</v>
+        <v>365</v>
       </c>
       <c r="B61" t="s">
-        <v>230</v>
+        <v>366</v>
       </c>
       <c r="C61" t="s">
-        <v>231</v>
+        <v>367</v>
       </c>
       <c r="D61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E61" t="s">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="G61" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H61">
-        <v>427</v>
+        <v>759</v>
       </c>
       <c r="I61" s="1">
-        <v>46281</v>
+        <v>46294</v>
       </c>
       <c r="J61" s="2">
-        <v>3200</v>
+        <v>500</v>
       </c>
       <c r="K61" t="s">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="L61" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M61" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="O61" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="P61" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="Q61" t="s">
-        <v>234</v>
+        <v>85</v>
       </c>
       <c r="R61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S61" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T61" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="U61" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>437</v>
+        <v>368</v>
       </c>
       <c r="B62" t="s">
-        <v>438</v>
+        <v>369</v>
       </c>
       <c r="C62" t="s">
-        <v>439</v>
+        <v>370</v>
       </c>
       <c r="D62" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E62" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G62" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H62">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="I62" s="1">
         <v>46294</v>
@@ -5366,255 +6308,2734 @@
         <v>500</v>
       </c>
       <c r="K62" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="L62" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M62" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O62" t="s">
         <v>11</v>
       </c>
       <c r="P62" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="Q62" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R62" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T62" t="s">
         <v>29</v>
       </c>
       <c r="U62" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>197</v>
+        <v>371</v>
       </c>
       <c r="B63" t="s">
-        <v>198</v>
+        <v>372</v>
       </c>
       <c r="C63" t="s">
-        <v>199</v>
+        <v>373</v>
       </c>
       <c r="D63" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E63" t="s">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="G63" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H63">
-        <v>203</v>
+        <v>756</v>
       </c>
       <c r="I63" s="1">
-        <v>46189</v>
+        <v>46294</v>
       </c>
       <c r="J63" s="2">
-        <v>5280</v>
+        <v>500</v>
       </c>
       <c r="K63" t="s">
-        <v>201</v>
+        <v>261</v>
       </c>
       <c r="L63" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M63" t="s">
+        <v>84</v>
+      </c>
+      <c r="O63" t="s">
+        <v>11</v>
+      </c>
+      <c r="P63" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q63" t="s">
         <v>85</v>
       </c>
-      <c r="O63" t="s">
-        <v>7</v>
-      </c>
-      <c r="P63" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>202</v>
-      </c>
       <c r="R63" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S63" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T63" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="U63" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
+        <v>374</v>
+      </c>
+      <c r="B64" t="s">
+        <v>375</v>
+      </c>
+      <c r="C64" t="s">
+        <v>376</v>
+      </c>
+      <c r="D64" t="s">
+        <v>59</v>
+      </c>
+      <c r="E64" t="s">
+        <v>377</v>
+      </c>
+      <c r="G64" t="s">
+        <v>60</v>
+      </c>
+      <c r="H64">
+        <v>750</v>
+      </c>
+      <c r="I64" s="1">
+        <v>46294</v>
+      </c>
+      <c r="J64" s="2">
+        <v>22920.95</v>
+      </c>
+      <c r="K64" t="s">
+        <v>272</v>
+      </c>
+      <c r="L64" t="s">
+        <v>62</v>
+      </c>
+      <c r="M64" t="s">
+        <v>273</v>
+      </c>
+      <c r="O64" t="s">
+        <v>274</v>
+      </c>
+      <c r="P64" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>276</v>
+      </c>
+      <c r="R64" t="s">
+        <v>64</v>
+      </c>
+      <c r="S64" t="s">
+        <v>65</v>
+      </c>
+      <c r="T64" t="s">
+        <v>277</v>
+      </c>
+      <c r="U64" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>315</v>
+      </c>
+      <c r="B65" t="s">
+        <v>316</v>
+      </c>
+      <c r="C65" t="s">
+        <v>317</v>
+      </c>
+      <c r="D65" t="s">
+        <v>59</v>
+      </c>
+      <c r="E65" t="s">
+        <v>318</v>
+      </c>
+      <c r="G65" t="s">
+        <v>60</v>
+      </c>
+      <c r="H65">
+        <v>16</v>
+      </c>
+      <c r="I65" s="1">
+        <v>46296</v>
+      </c>
+      <c r="J65" s="2">
+        <v>1700</v>
+      </c>
+      <c r="K65" t="s">
+        <v>319</v>
+      </c>
+      <c r="L65" t="s">
+        <v>62</v>
+      </c>
+      <c r="M65" t="s">
+        <v>320</v>
+      </c>
+      <c r="O65" t="s">
+        <v>321</v>
+      </c>
+      <c r="P65" t="s">
+        <v>648</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>322</v>
+      </c>
+      <c r="R65" t="s">
+        <v>64</v>
+      </c>
+      <c r="S65" t="s">
+        <v>65</v>
+      </c>
+      <c r="T65" t="s">
+        <v>304</v>
+      </c>
+      <c r="U65" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>323</v>
+      </c>
+      <c r="B66" t="s">
+        <v>324</v>
+      </c>
+      <c r="C66" t="s">
+        <v>325</v>
+      </c>
+      <c r="D66" t="s">
+        <v>59</v>
+      </c>
+      <c r="E66" t="s">
+        <v>174</v>
+      </c>
+      <c r="G66" t="s">
+        <v>60</v>
+      </c>
+      <c r="H66">
+        <v>251785</v>
+      </c>
+      <c r="I66" s="1">
+        <v>46296</v>
+      </c>
+      <c r="J66" s="2">
+        <v>69505.789999999994</v>
+      </c>
+      <c r="K66" t="s">
+        <v>326</v>
+      </c>
+      <c r="L66" t="s">
+        <v>62</v>
+      </c>
+      <c r="M66" t="s">
+        <v>162</v>
+      </c>
+      <c r="O66" t="s">
+        <v>19</v>
+      </c>
+      <c r="P66" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>176</v>
+      </c>
+      <c r="R66" t="s">
+        <v>64</v>
+      </c>
+      <c r="S66" t="s">
+        <v>65</v>
+      </c>
+      <c r="T66" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>327</v>
+      </c>
+      <c r="B67" t="s">
+        <v>328</v>
+      </c>
+      <c r="C67" t="s">
+        <v>329</v>
+      </c>
+      <c r="D67" t="s">
+        <v>59</v>
+      </c>
+      <c r="E67" t="s">
+        <v>330</v>
+      </c>
+      <c r="G67" t="s">
+        <v>60</v>
+      </c>
+      <c r="H67">
+        <v>1657</v>
+      </c>
+      <c r="I67" s="1">
+        <v>46296</v>
+      </c>
+      <c r="J67" s="2">
+        <v>9909.09</v>
+      </c>
+      <c r="K67" t="s">
+        <v>331</v>
+      </c>
+      <c r="L67" t="s">
+        <v>62</v>
+      </c>
+      <c r="M67" t="s">
+        <v>332</v>
+      </c>
+      <c r="O67" t="s">
+        <v>333</v>
+      </c>
+      <c r="P67" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>335</v>
+      </c>
+      <c r="R67" t="s">
+        <v>64</v>
+      </c>
+      <c r="S67" t="s">
+        <v>65</v>
+      </c>
+      <c r="T67" t="s">
+        <v>285</v>
+      </c>
+      <c r="U67" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>336</v>
+      </c>
+      <c r="B68" t="s">
+        <v>337</v>
+      </c>
+      <c r="C68" t="s">
+        <v>338</v>
+      </c>
+      <c r="D68" t="s">
+        <v>59</v>
+      </c>
+      <c r="E68" t="s">
+        <v>339</v>
+      </c>
+      <c r="G68" t="s">
+        <v>60</v>
+      </c>
+      <c r="H68">
+        <v>1658</v>
+      </c>
+      <c r="I68" s="1">
+        <v>46296</v>
+      </c>
+      <c r="J68">
+        <v>9000</v>
+      </c>
+      <c r="K68" t="s">
+        <v>331</v>
+      </c>
+      <c r="L68" t="s">
+        <v>62</v>
+      </c>
+      <c r="M68" t="s">
+        <v>332</v>
+      </c>
+      <c r="O68" t="s">
+        <v>333</v>
+      </c>
+      <c r="P68" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>335</v>
+      </c>
+      <c r="R68" t="s">
+        <v>64</v>
+      </c>
+      <c r="S68" t="s">
+        <v>65</v>
+      </c>
+      <c r="T68" t="s">
+        <v>285</v>
+      </c>
+      <c r="U68" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>201</v>
+      </c>
+      <c r="B69" t="s">
+        <v>202</v>
+      </c>
+      <c r="C69" t="s">
         <v>203</v>
       </c>
-      <c r="B64" t="s">
+      <c r="D69" t="s">
+        <v>59</v>
+      </c>
+      <c r="E69" t="s">
         <v>204</v>
       </c>
-      <c r="C64" t="s">
+      <c r="G69" t="s">
+        <v>60</v>
+      </c>
+      <c r="H69">
+        <v>176266</v>
+      </c>
+      <c r="I69" s="1">
+        <v>46266</v>
+      </c>
+      <c r="J69">
+        <v>270515.57</v>
+      </c>
+      <c r="K69" t="s">
         <v>205</v>
       </c>
-      <c r="D64" t="s">
-        <v>60</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="L69" t="s">
+        <v>62</v>
+      </c>
+      <c r="O69" t="s">
+        <v>24</v>
+      </c>
+      <c r="P69" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q69" t="s">
         <v>206</v>
       </c>
-      <c r="G64" t="s">
+      <c r="R69" t="s">
+        <v>64</v>
+      </c>
+      <c r="S69" t="s">
+        <v>65</v>
+      </c>
+      <c r="T69" t="s">
+        <v>29</v>
+      </c>
+      <c r="U69" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>649</v>
+      </c>
+      <c r="B70" t="s">
+        <v>650</v>
+      </c>
+      <c r="C70" t="s">
+        <v>651</v>
+      </c>
+      <c r="D70" t="s">
+        <v>59</v>
+      </c>
+      <c r="E70" t="s">
+        <v>652</v>
+      </c>
+      <c r="G70" t="s">
+        <v>60</v>
+      </c>
+      <c r="H70">
+        <v>176</v>
+      </c>
+      <c r="I70" s="1">
+        <v>46273</v>
+      </c>
+      <c r="J70">
+        <v>22865.14</v>
+      </c>
+      <c r="K70" t="s">
+        <v>653</v>
+      </c>
+      <c r="L70" t="s">
+        <v>62</v>
+      </c>
+      <c r="M70" t="s">
+        <v>63</v>
+      </c>
+      <c r="O70" t="s">
+        <v>654</v>
+      </c>
+      <c r="P70" t="s">
+        <v>655</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>656</v>
+      </c>
+      <c r="R70" t="s">
+        <v>64</v>
+      </c>
+      <c r="S70" t="s">
+        <v>65</v>
+      </c>
+      <c r="T70" t="s">
+        <v>12</v>
+      </c>
+      <c r="U70" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>177</v>
+      </c>
+      <c r="B71" t="s">
+        <v>178</v>
+      </c>
+      <c r="C71" t="s">
+        <v>179</v>
+      </c>
+      <c r="D71" t="s">
+        <v>59</v>
+      </c>
+      <c r="E71" t="s">
+        <v>180</v>
+      </c>
+      <c r="G71" t="s">
+        <v>60</v>
+      </c>
+      <c r="H71">
+        <v>10760</v>
+      </c>
+      <c r="I71" s="1">
+        <v>46276</v>
+      </c>
+      <c r="J71" s="2">
+        <v>3770.93</v>
+      </c>
+      <c r="K71" t="s">
+        <v>181</v>
+      </c>
+      <c r="L71" t="s">
+        <v>62</v>
+      </c>
+      <c r="M71" t="s">
+        <v>182</v>
+      </c>
+      <c r="O71" t="s">
+        <v>34</v>
+      </c>
+      <c r="P71" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>183</v>
+      </c>
+      <c r="R71" t="s">
+        <v>64</v>
+      </c>
+      <c r="S71" t="s">
+        <v>65</v>
+      </c>
+      <c r="T71" t="s">
+        <v>22</v>
+      </c>
+      <c r="U71" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>184</v>
+      </c>
+      <c r="B72" t="s">
+        <v>185</v>
+      </c>
+      <c r="C72" t="s">
+        <v>186</v>
+      </c>
+      <c r="D72" t="s">
+        <v>59</v>
+      </c>
+      <c r="E72" t="s">
+        <v>187</v>
+      </c>
+      <c r="G72" t="s">
+        <v>60</v>
+      </c>
+      <c r="H72">
+        <v>13020</v>
+      </c>
+      <c r="I72" s="1">
+        <v>46268</v>
+      </c>
+      <c r="J72">
+        <v>330986.02</v>
+      </c>
+      <c r="K72" t="s">
+        <v>188</v>
+      </c>
+      <c r="L72" t="s">
+        <v>62</v>
+      </c>
+      <c r="M72" t="s">
+        <v>189</v>
+      </c>
+      <c r="O72" t="s">
+        <v>9</v>
+      </c>
+      <c r="P72" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>130</v>
+      </c>
+      <c r="R72" t="s">
+        <v>64</v>
+      </c>
+      <c r="S72" t="s">
+        <v>65</v>
+      </c>
+      <c r="T72" t="s">
+        <v>16</v>
+      </c>
+      <c r="U72" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>171</v>
+      </c>
+      <c r="B73" t="s">
+        <v>172</v>
+      </c>
+      <c r="C73" t="s">
+        <v>173</v>
+      </c>
+      <c r="D73" t="s">
+        <v>59</v>
+      </c>
+      <c r="E73" t="s">
+        <v>174</v>
+      </c>
+      <c r="G73" t="s">
+        <v>60</v>
+      </c>
+      <c r="H73">
+        <v>251216</v>
+      </c>
+      <c r="I73" s="1">
+        <v>46283</v>
+      </c>
+      <c r="J73">
+        <v>69505.789999999994</v>
+      </c>
+      <c r="K73" t="s">
+        <v>175</v>
+      </c>
+      <c r="L73" t="s">
+        <v>62</v>
+      </c>
+      <c r="M73" t="s">
+        <v>162</v>
+      </c>
+      <c r="O73" t="s">
+        <v>19</v>
+      </c>
+      <c r="P73" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>176</v>
+      </c>
+      <c r="R73" t="s">
+        <v>64</v>
+      </c>
+      <c r="S73" t="s">
+        <v>65</v>
+      </c>
+      <c r="T73" t="s">
+        <v>3</v>
+      </c>
+      <c r="U73" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>378</v>
+      </c>
+      <c r="B74" t="s">
+        <v>379</v>
+      </c>
+      <c r="C74" t="s">
+        <v>380</v>
+      </c>
+      <c r="D74" t="s">
+        <v>59</v>
+      </c>
+      <c r="E74" t="s">
+        <v>82</v>
+      </c>
+      <c r="G74" t="s">
+        <v>60</v>
+      </c>
+      <c r="H74">
+        <v>766</v>
+      </c>
+      <c r="I74" s="1">
+        <v>46294</v>
+      </c>
+      <c r="J74">
+        <v>500</v>
+      </c>
+      <c r="K74" t="s">
+        <v>261</v>
+      </c>
+      <c r="L74" t="s">
+        <v>62</v>
+      </c>
+      <c r="M74" t="s">
+        <v>84</v>
+      </c>
+      <c r="O74" t="s">
+        <v>11</v>
+      </c>
+      <c r="P74" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>85</v>
+      </c>
+      <c r="R74" t="s">
+        <v>64</v>
+      </c>
+      <c r="S74" t="s">
+        <v>65</v>
+      </c>
+      <c r="T74" t="s">
+        <v>29</v>
+      </c>
+      <c r="U74" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>381</v>
+      </c>
+      <c r="B75" t="s">
+        <v>382</v>
+      </c>
+      <c r="C75" t="s">
+        <v>383</v>
+      </c>
+      <c r="D75" t="s">
+        <v>59</v>
+      </c>
+      <c r="E75" t="s">
+        <v>82</v>
+      </c>
+      <c r="G75" t="s">
+        <v>60</v>
+      </c>
+      <c r="H75">
+        <v>763</v>
+      </c>
+      <c r="I75" s="1">
+        <v>46294</v>
+      </c>
+      <c r="J75">
+        <v>500</v>
+      </c>
+      <c r="K75" t="s">
+        <v>261</v>
+      </c>
+      <c r="L75" t="s">
+        <v>62</v>
+      </c>
+      <c r="M75" t="s">
+        <v>273</v>
+      </c>
+      <c r="O75" t="s">
+        <v>11</v>
+      </c>
+      <c r="P75" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>85</v>
+      </c>
+      <c r="R75" t="s">
+        <v>64</v>
+      </c>
+      <c r="S75" t="s">
+        <v>65</v>
+      </c>
+      <c r="T75" t="s">
+        <v>29</v>
+      </c>
+      <c r="U75" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>384</v>
+      </c>
+      <c r="B76" t="s">
+        <v>385</v>
+      </c>
+      <c r="C76" t="s">
+        <v>386</v>
+      </c>
+      <c r="D76" t="s">
+        <v>59</v>
+      </c>
+      <c r="E76" t="s">
+        <v>82</v>
+      </c>
+      <c r="G76" t="s">
+        <v>60</v>
+      </c>
+      <c r="H76">
+        <v>765</v>
+      </c>
+      <c r="I76" s="1">
+        <v>46294</v>
+      </c>
+      <c r="J76">
+        <v>500</v>
+      </c>
+      <c r="K76" t="s">
+        <v>261</v>
+      </c>
+      <c r="L76" t="s">
+        <v>62</v>
+      </c>
+      <c r="M76" t="s">
+        <v>84</v>
+      </c>
+      <c r="O76" t="s">
+        <v>11</v>
+      </c>
+      <c r="P76" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>85</v>
+      </c>
+      <c r="R76" t="s">
+        <v>64</v>
+      </c>
+      <c r="S76" t="s">
+        <v>65</v>
+      </c>
+      <c r="T76" t="s">
+        <v>29</v>
+      </c>
+      <c r="U76" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>207</v>
+      </c>
+      <c r="B77" t="s">
+        <v>208</v>
+      </c>
+      <c r="C77" t="s">
+        <v>209</v>
+      </c>
+      <c r="D77" t="s">
+        <v>59</v>
+      </c>
+      <c r="E77" t="s">
+        <v>210</v>
+      </c>
+      <c r="G77" t="s">
+        <v>60</v>
+      </c>
+      <c r="H77">
+        <v>21985</v>
+      </c>
+      <c r="I77" s="1">
+        <v>46262</v>
+      </c>
+      <c r="J77">
+        <v>969.98</v>
+      </c>
+      <c r="K77" t="s">
+        <v>96</v>
+      </c>
+      <c r="L77" t="s">
+        <v>62</v>
+      </c>
+      <c r="M77" t="s">
+        <v>97</v>
+      </c>
+      <c r="O77" t="s">
+        <v>17</v>
+      </c>
+      <c r="P77" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>232</v>
+      </c>
+      <c r="R77" t="s">
+        <v>64</v>
+      </c>
+      <c r="S77" t="s">
+        <v>65</v>
+      </c>
+      <c r="T77" t="s">
+        <v>285</v>
+      </c>
+      <c r="U77" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>657</v>
+      </c>
+      <c r="B78" t="s">
+        <v>658</v>
+      </c>
+      <c r="C78" t="s">
+        <v>659</v>
+      </c>
+      <c r="D78" t="s">
+        <v>59</v>
+      </c>
+      <c r="E78" t="s">
+        <v>660</v>
+      </c>
+      <c r="G78" t="s">
+        <v>60</v>
+      </c>
+      <c r="H78">
+        <v>17158443</v>
+      </c>
+      <c r="I78" s="1">
+        <v>46290</v>
+      </c>
+      <c r="J78">
+        <v>7704.8</v>
+      </c>
+      <c r="K78" t="s">
+        <v>661</v>
+      </c>
+      <c r="L78" t="s">
+        <v>62</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="P78" t="s">
+        <v>663</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>664</v>
+      </c>
+      <c r="R78" t="s">
+        <v>64</v>
+      </c>
+      <c r="S78" t="s">
+        <v>65</v>
+      </c>
+      <c r="T78" t="s">
+        <v>29</v>
+      </c>
+      <c r="U78" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>665</v>
+      </c>
+      <c r="B79" t="s">
+        <v>666</v>
+      </c>
+      <c r="C79" t="s">
+        <v>667</v>
+      </c>
+      <c r="D79" t="s">
+        <v>59</v>
+      </c>
+      <c r="E79" t="s">
+        <v>668</v>
+      </c>
+      <c r="G79" t="s">
+        <v>60</v>
+      </c>
+      <c r="H79">
+        <v>17158451</v>
+      </c>
+      <c r="I79" s="1">
+        <v>46290</v>
+      </c>
+      <c r="J79">
+        <v>198612.03</v>
+      </c>
+      <c r="K79" t="s">
+        <v>661</v>
+      </c>
+      <c r="L79" t="s">
+        <v>62</v>
+      </c>
+      <c r="O79" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="P79" t="s">
+        <v>663</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>669</v>
+      </c>
+      <c r="R79" t="s">
+        <v>64</v>
+      </c>
+      <c r="S79" t="s">
+        <v>65</v>
+      </c>
+      <c r="T79" t="s">
+        <v>29</v>
+      </c>
+      <c r="U79" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>670</v>
+      </c>
+      <c r="B80" t="s">
+        <v>671</v>
+      </c>
+      <c r="C80" t="s">
+        <v>672</v>
+      </c>
+      <c r="D80" t="s">
+        <v>59</v>
+      </c>
+      <c r="E80" t="s">
+        <v>673</v>
+      </c>
+      <c r="G80" t="s">
+        <v>60</v>
+      </c>
+      <c r="H80">
+        <v>1276715</v>
+      </c>
+      <c r="I80" s="1">
+        <v>46296</v>
+      </c>
+      <c r="J80">
+        <v>7304.8</v>
+      </c>
+      <c r="K80" t="s">
+        <v>674</v>
+      </c>
+      <c r="L80" t="s">
+        <v>62</v>
+      </c>
+      <c r="M80" t="s">
+        <v>104</v>
+      </c>
+      <c r="O80" t="s">
+        <v>675</v>
+      </c>
+      <c r="P80" t="s">
+        <v>676</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>677</v>
+      </c>
+      <c r="R80" t="s">
+        <v>64</v>
+      </c>
+      <c r="S80" t="s">
+        <v>65</v>
+      </c>
+      <c r="T80" t="s">
+        <v>447</v>
+      </c>
+      <c r="U80" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>678</v>
+      </c>
+      <c r="B81" t="s">
+        <v>679</v>
+      </c>
+      <c r="C81" t="s">
+        <v>680</v>
+      </c>
+      <c r="D81" t="s">
+        <v>59</v>
+      </c>
+      <c r="E81" t="s">
+        <v>681</v>
+      </c>
+      <c r="G81" t="s">
+        <v>60</v>
+      </c>
+      <c r="H81">
+        <v>2042</v>
+      </c>
+      <c r="I81" s="1">
+        <v>46296</v>
+      </c>
+      <c r="J81" s="2">
+        <v>4944.6000000000004</v>
+      </c>
+      <c r="K81" t="s">
+        <v>682</v>
+      </c>
+      <c r="L81" t="s">
+        <v>62</v>
+      </c>
+      <c r="M81" t="s">
+        <v>162</v>
+      </c>
+      <c r="O81" t="s">
+        <v>556</v>
+      </c>
+      <c r="P81" t="s">
+        <v>557</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>683</v>
+      </c>
+      <c r="R81" t="s">
+        <v>64</v>
+      </c>
+      <c r="S81" t="s">
+        <v>65</v>
+      </c>
+      <c r="T81" t="s">
+        <v>477</v>
+      </c>
+      <c r="U81" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>684</v>
+      </c>
+      <c r="B82" t="s">
+        <v>685</v>
+      </c>
+      <c r="C82" t="s">
+        <v>686</v>
+      </c>
+      <c r="D82" t="s">
+        <v>59</v>
+      </c>
+      <c r="E82" t="s">
+        <v>687</v>
+      </c>
+      <c r="G82" t="s">
+        <v>60</v>
+      </c>
+      <c r="H82">
+        <v>5881</v>
+      </c>
+      <c r="I82" s="1">
+        <v>46296</v>
+      </c>
+      <c r="J82" s="2">
+        <v>7887.75</v>
+      </c>
+      <c r="K82" t="s">
+        <v>688</v>
+      </c>
+      <c r="L82" t="s">
+        <v>62</v>
+      </c>
+      <c r="M82" t="s">
+        <v>104</v>
+      </c>
+      <c r="O82" t="s">
+        <v>689</v>
+      </c>
+      <c r="P82" t="s">
+        <v>690</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>691</v>
+      </c>
+      <c r="R82" t="s">
+        <v>64</v>
+      </c>
+      <c r="S82" t="s">
+        <v>65</v>
+      </c>
+      <c r="T82" t="s">
+        <v>692</v>
+      </c>
+      <c r="U82" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>163</v>
+      </c>
+      <c r="B83" t="s">
+        <v>164</v>
+      </c>
+      <c r="C83" t="s">
+        <v>165</v>
+      </c>
+      <c r="D83" t="s">
+        <v>59</v>
+      </c>
+      <c r="E83" t="s">
+        <v>166</v>
+      </c>
+      <c r="G83" t="s">
+        <v>60</v>
+      </c>
+      <c r="H83">
+        <v>12908</v>
+      </c>
+      <c r="I83" s="1">
+        <v>46205</v>
+      </c>
+      <c r="J83" s="2">
+        <v>643664.51</v>
+      </c>
+      <c r="K83" t="s">
+        <v>167</v>
+      </c>
+      <c r="L83" t="s">
+        <v>62</v>
+      </c>
+      <c r="M83" t="s">
+        <v>129</v>
+      </c>
+      <c r="O83" t="s">
+        <v>9</v>
+      </c>
+      <c r="P83" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>130</v>
+      </c>
+      <c r="R83" t="s">
+        <v>64</v>
+      </c>
+      <c r="S83" t="s">
+        <v>118</v>
+      </c>
+      <c r="T83" t="s">
+        <v>16</v>
+      </c>
+      <c r="U83" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>211</v>
+      </c>
+      <c r="B84" t="s">
+        <v>212</v>
+      </c>
+      <c r="C84" t="s">
+        <v>213</v>
+      </c>
+      <c r="D84" t="s">
+        <v>59</v>
+      </c>
+      <c r="E84" t="s">
+        <v>214</v>
+      </c>
+      <c r="G84" t="s">
+        <v>60</v>
+      </c>
+      <c r="H84">
+        <v>2808</v>
+      </c>
+      <c r="I84" s="1">
+        <v>46267</v>
+      </c>
+      <c r="J84" s="2">
+        <v>15900</v>
+      </c>
+      <c r="K84" t="s">
+        <v>215</v>
+      </c>
+      <c r="L84" t="s">
+        <v>62</v>
+      </c>
+      <c r="M84" t="s">
+        <v>63</v>
+      </c>
+      <c r="O84" t="s">
+        <v>32</v>
+      </c>
+      <c r="P84" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>216</v>
+      </c>
+      <c r="R84" t="s">
+        <v>64</v>
+      </c>
+      <c r="S84" t="s">
+        <v>65</v>
+      </c>
+      <c r="T84" t="s">
+        <v>25</v>
+      </c>
+      <c r="U84" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>693</v>
+      </c>
+      <c r="B85" t="s">
+        <v>694</v>
+      </c>
+      <c r="C85" t="s">
+        <v>695</v>
+      </c>
+      <c r="D85" t="s">
+        <v>59</v>
+      </c>
+      <c r="E85" t="s">
+        <v>696</v>
+      </c>
+      <c r="G85" t="s">
+        <v>60</v>
+      </c>
+      <c r="H85">
+        <v>22574</v>
+      </c>
+      <c r="I85" s="1">
+        <v>46297</v>
+      </c>
+      <c r="J85">
+        <v>805</v>
+      </c>
+      <c r="K85" t="s">
+        <v>494</v>
+      </c>
+      <c r="L85" t="s">
+        <v>62</v>
+      </c>
+      <c r="O85" t="s">
+        <v>495</v>
+      </c>
+      <c r="P85" t="s">
+        <v>496</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>697</v>
+      </c>
+      <c r="R85" t="s">
+        <v>64</v>
+      </c>
+      <c r="S85" t="s">
+        <v>65</v>
+      </c>
+      <c r="T85" t="s">
+        <v>477</v>
+      </c>
+      <c r="U85" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>698</v>
+      </c>
+      <c r="B86" t="s">
+        <v>699</v>
+      </c>
+      <c r="C86" t="s">
+        <v>700</v>
+      </c>
+      <c r="D86" t="s">
+        <v>59</v>
+      </c>
+      <c r="E86" t="s">
+        <v>701</v>
+      </c>
+      <c r="G86" t="s">
+        <v>60</v>
+      </c>
+      <c r="H86">
+        <v>22575</v>
+      </c>
+      <c r="I86" s="1">
+        <v>46297</v>
+      </c>
+      <c r="J86" s="2">
+        <v>930</v>
+      </c>
+      <c r="K86" t="s">
+        <v>702</v>
+      </c>
+      <c r="L86" t="s">
+        <v>62</v>
+      </c>
+      <c r="O86" t="s">
+        <v>495</v>
+      </c>
+      <c r="P86" t="s">
+        <v>496</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>703</v>
+      </c>
+      <c r="R86" t="s">
+        <v>64</v>
+      </c>
+      <c r="S86" t="s">
+        <v>65</v>
+      </c>
+      <c r="T86" t="s">
+        <v>477</v>
+      </c>
+      <c r="U86" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>704</v>
+      </c>
+      <c r="B87" t="s">
+        <v>705</v>
+      </c>
+      <c r="C87" t="s">
+        <v>706</v>
+      </c>
+      <c r="D87" t="s">
+        <v>59</v>
+      </c>
+      <c r="E87" t="s">
+        <v>707</v>
+      </c>
+      <c r="G87" t="s">
+        <v>60</v>
+      </c>
+      <c r="H87">
+        <v>193</v>
+      </c>
+      <c r="I87" s="1">
+        <v>46296</v>
+      </c>
+      <c r="J87">
+        <v>546</v>
+      </c>
+      <c r="K87" t="s">
+        <v>708</v>
+      </c>
+      <c r="L87" t="s">
+        <v>62</v>
+      </c>
+      <c r="M87" t="s">
+        <v>709</v>
+      </c>
+      <c r="O87" t="s">
+        <v>710</v>
+      </c>
+      <c r="P87" t="s">
+        <v>711</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>712</v>
+      </c>
+      <c r="R87" t="s">
+        <v>64</v>
+      </c>
+      <c r="S87" t="s">
+        <v>65</v>
+      </c>
+      <c r="T87" t="s">
+        <v>285</v>
+      </c>
+      <c r="U87" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>713</v>
+      </c>
+      <c r="B88" t="s">
+        <v>714</v>
+      </c>
+      <c r="C88" t="s">
+        <v>715</v>
+      </c>
+      <c r="D88" t="s">
+        <v>59</v>
+      </c>
+      <c r="E88" t="s">
+        <v>716</v>
+      </c>
+      <c r="G88" t="s">
+        <v>60</v>
+      </c>
+      <c r="H88">
+        <v>13018</v>
+      </c>
+      <c r="I88" s="1">
+        <v>46298</v>
+      </c>
+      <c r="J88" s="2">
+        <v>18778.25</v>
+      </c>
+      <c r="K88" t="s">
+        <v>717</v>
+      </c>
+      <c r="L88" t="s">
+        <v>62</v>
+      </c>
+      <c r="M88" t="s">
+        <v>162</v>
+      </c>
+      <c r="O88" t="s">
+        <v>9</v>
+      </c>
+      <c r="P88" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>130</v>
+      </c>
+      <c r="R88" t="s">
+        <v>64</v>
+      </c>
+      <c r="S88" t="s">
+        <v>65</v>
+      </c>
+      <c r="T88" t="s">
+        <v>16</v>
+      </c>
+      <c r="U88" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>168</v>
+      </c>
+      <c r="B89" t="s">
+        <v>169</v>
+      </c>
+      <c r="C89" t="s">
+        <v>170</v>
+      </c>
+      <c r="D89" t="s">
+        <v>59</v>
+      </c>
+      <c r="E89" t="s">
+        <v>82</v>
+      </c>
+      <c r="G89" t="s">
+        <v>60</v>
+      </c>
+      <c r="H89">
+        <v>460</v>
+      </c>
+      <c r="I89" s="1">
+        <v>46262</v>
+      </c>
+      <c r="J89">
+        <v>500</v>
+      </c>
+      <c r="K89" t="s">
+        <v>83</v>
+      </c>
+      <c r="L89" t="s">
+        <v>62</v>
+      </c>
+      <c r="M89" t="s">
+        <v>84</v>
+      </c>
+      <c r="O89" t="s">
+        <v>11</v>
+      </c>
+      <c r="P89" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>85</v>
+      </c>
+      <c r="R89" t="s">
+        <v>64</v>
+      </c>
+      <c r="S89" t="s">
+        <v>65</v>
+      </c>
+      <c r="T89" t="s">
+        <v>18</v>
+      </c>
+      <c r="U89" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>228</v>
+      </c>
+      <c r="B90" t="s">
+        <v>229</v>
+      </c>
+      <c r="C90" t="s">
+        <v>230</v>
+      </c>
+      <c r="D90" t="s">
+        <v>59</v>
+      </c>
+      <c r="E90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G90" t="s">
+        <v>60</v>
+      </c>
+      <c r="H90">
+        <v>464</v>
+      </c>
+      <c r="I90" s="1">
+        <v>46265</v>
+      </c>
+      <c r="J90">
+        <v>500</v>
+      </c>
+      <c r="K90" t="s">
+        <v>83</v>
+      </c>
+      <c r="L90" t="s">
+        <v>62</v>
+      </c>
+      <c r="M90" t="s">
+        <v>84</v>
+      </c>
+      <c r="O90" t="s">
+        <v>11</v>
+      </c>
+      <c r="P90" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>85</v>
+      </c>
+      <c r="R90" t="s">
+        <v>64</v>
+      </c>
+      <c r="S90" t="s">
+        <v>65</v>
+      </c>
+      <c r="T90" t="s">
+        <v>18</v>
+      </c>
+      <c r="U90" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>718</v>
+      </c>
+      <c r="B91" t="s">
+        <v>719</v>
+      </c>
+      <c r="C91" t="s">
+        <v>720</v>
+      </c>
+      <c r="D91" t="s">
+        <v>59</v>
+      </c>
+      <c r="E91" t="s">
+        <v>721</v>
+      </c>
+      <c r="G91" t="s">
+        <v>60</v>
+      </c>
+      <c r="H91">
+        <v>20</v>
+      </c>
+      <c r="I91" s="1">
+        <v>46296</v>
+      </c>
+      <c r="J91">
+        <v>11782</v>
+      </c>
+      <c r="K91" t="s">
+        <v>722</v>
+      </c>
+      <c r="L91" t="s">
+        <v>62</v>
+      </c>
+      <c r="M91" t="s">
+        <v>310</v>
+      </c>
+      <c r="O91" t="s">
+        <v>723</v>
+      </c>
+      <c r="P91" t="s">
+        <v>724</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>725</v>
+      </c>
+      <c r="R91" t="s">
+        <v>64</v>
+      </c>
+      <c r="S91" t="s">
+        <v>65</v>
+      </c>
+      <c r="T91" t="s">
+        <v>726</v>
+      </c>
+      <c r="U91" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>727</v>
+      </c>
+      <c r="B92" t="s">
+        <v>728</v>
+      </c>
+      <c r="C92" t="s">
+        <v>729</v>
+      </c>
+      <c r="D92" t="s">
+        <v>59</v>
+      </c>
+      <c r="E92" t="s">
+        <v>730</v>
+      </c>
+      <c r="G92" t="s">
+        <v>60</v>
+      </c>
+      <c r="H92">
+        <v>345</v>
+      </c>
+      <c r="I92" s="1">
+        <v>46296</v>
+      </c>
+      <c r="J92">
+        <v>1200</v>
+      </c>
+      <c r="K92" t="s">
+        <v>731</v>
+      </c>
+      <c r="L92" t="s">
+        <v>62</v>
+      </c>
+      <c r="M92" t="s">
+        <v>84</v>
+      </c>
+      <c r="O92" t="s">
+        <v>732</v>
+      </c>
+      <c r="P92" t="s">
+        <v>733</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>734</v>
+      </c>
+      <c r="R92" t="s">
+        <v>64</v>
+      </c>
+      <c r="S92" t="s">
+        <v>65</v>
+      </c>
+      <c r="T92" t="s">
+        <v>304</v>
+      </c>
+      <c r="U92" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>735</v>
+      </c>
+      <c r="B93" t="s">
+        <v>736</v>
+      </c>
+      <c r="C93" t="s">
+        <v>737</v>
+      </c>
+      <c r="D93" t="s">
+        <v>59</v>
+      </c>
+      <c r="E93" t="s">
+        <v>730</v>
+      </c>
+      <c r="G93" t="s">
+        <v>60</v>
+      </c>
+      <c r="H93">
+        <v>346</v>
+      </c>
+      <c r="I93" s="1">
+        <v>46296</v>
+      </c>
+      <c r="J93">
+        <v>1200</v>
+      </c>
+      <c r="K93" t="s">
+        <v>731</v>
+      </c>
+      <c r="L93" t="s">
+        <v>62</v>
+      </c>
+      <c r="M93" t="s">
+        <v>84</v>
+      </c>
+      <c r="O93" t="s">
+        <v>732</v>
+      </c>
+      <c r="P93" t="s">
+        <v>733</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>738</v>
+      </c>
+      <c r="R93" t="s">
+        <v>64</v>
+      </c>
+      <c r="S93" t="s">
+        <v>65</v>
+      </c>
+      <c r="T93" t="s">
+        <v>304</v>
+      </c>
+      <c r="U93" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>217</v>
+      </c>
+      <c r="B94" t="s">
+        <v>218</v>
+      </c>
+      <c r="C94" t="s">
+        <v>219</v>
+      </c>
+      <c r="D94" t="s">
+        <v>59</v>
+      </c>
+      <c r="E94" t="s">
+        <v>220</v>
+      </c>
+      <c r="G94" t="s">
+        <v>60</v>
+      </c>
+      <c r="H94">
+        <v>26491</v>
+      </c>
+      <c r="I94" s="1">
+        <v>46267</v>
+      </c>
+      <c r="J94">
+        <v>22510.52</v>
+      </c>
+      <c r="K94" t="s">
         <v>61</v>
       </c>
-      <c r="H64">
+      <c r="L94" t="s">
+        <v>62</v>
+      </c>
+      <c r="M94" t="s">
+        <v>63</v>
+      </c>
+      <c r="O94" t="s">
+        <v>30</v>
+      </c>
+      <c r="P94" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>221</v>
+      </c>
+      <c r="R94" t="s">
+        <v>64</v>
+      </c>
+      <c r="S94" t="s">
+        <v>65</v>
+      </c>
+      <c r="T94" t="s">
+        <v>12</v>
+      </c>
+      <c r="U94" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>222</v>
+      </c>
+      <c r="B95" t="s">
+        <v>223</v>
+      </c>
+      <c r="C95" t="s">
+        <v>224</v>
+      </c>
+      <c r="D95" t="s">
+        <v>59</v>
+      </c>
+      <c r="E95" t="s">
+        <v>225</v>
+      </c>
+      <c r="G95" t="s">
+        <v>60</v>
+      </c>
+      <c r="H95">
+        <v>427</v>
+      </c>
+      <c r="I95">
+        <v>46281</v>
+      </c>
+      <c r="J95">
+        <v>3200</v>
+      </c>
+      <c r="K95" t="s">
+        <v>226</v>
+      </c>
+      <c r="L95" t="s">
+        <v>62</v>
+      </c>
+      <c r="M95" t="s">
+        <v>63</v>
+      </c>
+      <c r="O95" t="s">
+        <v>38</v>
+      </c>
+      <c r="P95" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>227</v>
+      </c>
+      <c r="R95" t="s">
+        <v>64</v>
+      </c>
+      <c r="S95" t="s">
+        <v>65</v>
+      </c>
+      <c r="T95" t="s">
+        <v>23</v>
+      </c>
+      <c r="U95" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>739</v>
+      </c>
+      <c r="B96" t="s">
+        <v>740</v>
+      </c>
+      <c r="C96" t="s">
+        <v>741</v>
+      </c>
+      <c r="D96" t="s">
+        <v>59</v>
+      </c>
+      <c r="E96" t="s">
+        <v>742</v>
+      </c>
+      <c r="G96" t="s">
+        <v>60</v>
+      </c>
+      <c r="H96">
+        <v>39</v>
+      </c>
+      <c r="I96">
+        <v>46297</v>
+      </c>
+      <c r="J96">
+        <v>2958.63</v>
+      </c>
+      <c r="K96" t="s">
+        <v>743</v>
+      </c>
+      <c r="L96" t="s">
+        <v>62</v>
+      </c>
+      <c r="M96" t="s">
+        <v>63</v>
+      </c>
+      <c r="O96" t="s">
+        <v>645</v>
+      </c>
+      <c r="P96" t="s">
+        <v>646</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>744</v>
+      </c>
+      <c r="R96" t="s">
+        <v>64</v>
+      </c>
+      <c r="S96" t="s">
+        <v>65</v>
+      </c>
+      <c r="T96" t="s">
+        <v>285</v>
+      </c>
+      <c r="U96" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>393</v>
+      </c>
+      <c r="B97" t="s">
+        <v>394</v>
+      </c>
+      <c r="C97" t="s">
+        <v>395</v>
+      </c>
+      <c r="D97" t="s">
+        <v>59</v>
+      </c>
+      <c r="E97" t="s">
+        <v>339</v>
+      </c>
+      <c r="G97" t="s">
+        <v>60</v>
+      </c>
+      <c r="H97">
+        <v>1656</v>
+      </c>
+      <c r="I97">
+        <v>46296</v>
+      </c>
+      <c r="J97">
+        <v>9000</v>
+      </c>
+      <c r="K97" t="s">
+        <v>396</v>
+      </c>
+      <c r="L97" t="s">
+        <v>62</v>
+      </c>
+      <c r="M97" t="s">
+        <v>332</v>
+      </c>
+      <c r="O97" t="s">
+        <v>333</v>
+      </c>
+      <c r="P97" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>335</v>
+      </c>
+      <c r="R97" t="s">
+        <v>64</v>
+      </c>
+      <c r="S97" t="s">
+        <v>65</v>
+      </c>
+      <c r="T97" t="s">
+        <v>285</v>
+      </c>
+      <c r="U97" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>397</v>
+      </c>
+      <c r="B98" t="s">
+        <v>398</v>
+      </c>
+      <c r="C98" t="s">
+        <v>399</v>
+      </c>
+      <c r="D98" t="s">
+        <v>59</v>
+      </c>
+      <c r="E98" t="s">
+        <v>400</v>
+      </c>
+      <c r="G98" t="s">
+        <v>60</v>
+      </c>
+      <c r="H98">
+        <v>2564</v>
+      </c>
+      <c r="I98">
+        <v>46296</v>
+      </c>
+      <c r="J98">
+        <v>1300</v>
+      </c>
+      <c r="K98" t="s">
+        <v>401</v>
+      </c>
+      <c r="L98" t="s">
+        <v>62</v>
+      </c>
+      <c r="M98" t="s">
+        <v>80</v>
+      </c>
+      <c r="O98" t="s">
+        <v>402</v>
+      </c>
+      <c r="P98" t="s">
+        <v>403</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>404</v>
+      </c>
+      <c r="R98" t="s">
+        <v>64</v>
+      </c>
+      <c r="S98" t="s">
+        <v>65</v>
+      </c>
+      <c r="T98" t="s">
+        <v>10</v>
+      </c>
+      <c r="U98" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>405</v>
+      </c>
+      <c r="B99" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" t="s">
+        <v>407</v>
+      </c>
+      <c r="D99" t="s">
+        <v>59</v>
+      </c>
+      <c r="E99" t="s">
+        <v>408</v>
+      </c>
+      <c r="G99" t="s">
+        <v>60</v>
+      </c>
+      <c r="H99">
+        <v>6025</v>
+      </c>
+      <c r="I99">
+        <v>46296</v>
+      </c>
+      <c r="J99">
+        <v>9204</v>
+      </c>
+      <c r="K99" t="s">
+        <v>409</v>
+      </c>
+      <c r="L99" t="s">
+        <v>62</v>
+      </c>
+      <c r="M99" t="s">
+        <v>84</v>
+      </c>
+      <c r="O99" t="s">
+        <v>410</v>
+      </c>
+      <c r="P99" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>412</v>
+      </c>
+      <c r="R99" t="s">
+        <v>64</v>
+      </c>
+      <c r="S99" t="s">
+        <v>65</v>
+      </c>
+      <c r="T99" t="s">
+        <v>413</v>
+      </c>
+      <c r="U99" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>414</v>
+      </c>
+      <c r="B100" t="s">
+        <v>415</v>
+      </c>
+      <c r="C100" t="s">
+        <v>416</v>
+      </c>
+      <c r="D100" t="s">
+        <v>59</v>
+      </c>
+      <c r="E100" t="s">
+        <v>417</v>
+      </c>
+      <c r="G100" t="s">
+        <v>60</v>
+      </c>
+      <c r="H100">
+        <v>10823</v>
+      </c>
+      <c r="I100">
+        <v>46296</v>
+      </c>
+      <c r="J100">
+        <v>19950</v>
+      </c>
+      <c r="K100" t="s">
+        <v>418</v>
+      </c>
+      <c r="L100" t="s">
+        <v>62</v>
+      </c>
+      <c r="M100" t="s">
+        <v>419</v>
+      </c>
+      <c r="O100" t="s">
+        <v>420</v>
+      </c>
+      <c r="P100" t="s">
+        <v>745</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>421</v>
+      </c>
+      <c r="R100" t="s">
+        <v>64</v>
+      </c>
+      <c r="S100" t="s">
+        <v>65</v>
+      </c>
+      <c r="T100" t="s">
+        <v>304</v>
+      </c>
+      <c r="U100" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>422</v>
+      </c>
+      <c r="B101" t="s">
+        <v>423</v>
+      </c>
+      <c r="C101" t="s">
+        <v>424</v>
+      </c>
+      <c r="D101" t="s">
+        <v>59</v>
+      </c>
+      <c r="E101" t="s">
+        <v>425</v>
+      </c>
+      <c r="G101" t="s">
+        <v>60</v>
+      </c>
+      <c r="H101">
+        <v>342</v>
+      </c>
+      <c r="I101">
+        <v>46296</v>
+      </c>
+      <c r="J101">
+        <v>1270.83</v>
+      </c>
+      <c r="K101" t="s">
+        <v>426</v>
+      </c>
+      <c r="L101" t="s">
+        <v>62</v>
+      </c>
+      <c r="M101" t="s">
+        <v>80</v>
+      </c>
+      <c r="O101" t="s">
+        <v>333</v>
+      </c>
+      <c r="P101" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>335</v>
+      </c>
+      <c r="R101" t="s">
+        <v>64</v>
+      </c>
+      <c r="S101" t="s">
+        <v>65</v>
+      </c>
+      <c r="T101" t="s">
+        <v>285</v>
+      </c>
+      <c r="U101" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>387</v>
+      </c>
+      <c r="B102" t="s">
+        <v>388</v>
+      </c>
+      <c r="C102" t="s">
+        <v>389</v>
+      </c>
+      <c r="D102" t="s">
+        <v>59</v>
+      </c>
+      <c r="E102" t="s">
+        <v>82</v>
+      </c>
+      <c r="G102" t="s">
+        <v>60</v>
+      </c>
+      <c r="H102">
+        <v>764</v>
+      </c>
+      <c r="I102">
+        <v>46294</v>
+      </c>
+      <c r="J102">
+        <v>500</v>
+      </c>
+      <c r="K102" t="s">
+        <v>261</v>
+      </c>
+      <c r="L102" t="s">
+        <v>62</v>
+      </c>
+      <c r="M102" t="s">
+        <v>84</v>
+      </c>
+      <c r="O102" t="s">
+        <v>11</v>
+      </c>
+      <c r="P102" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>85</v>
+      </c>
+      <c r="R102" t="s">
+        <v>64</v>
+      </c>
+      <c r="S102" t="s">
+        <v>65</v>
+      </c>
+      <c r="T102" t="s">
+        <v>29</v>
+      </c>
+      <c r="U102" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>390</v>
+      </c>
+      <c r="B103" t="s">
+        <v>391</v>
+      </c>
+      <c r="C103" t="s">
+        <v>392</v>
+      </c>
+      <c r="D103" t="s">
+        <v>59</v>
+      </c>
+      <c r="E103" t="s">
+        <v>82</v>
+      </c>
+      <c r="G103" t="s">
+        <v>60</v>
+      </c>
+      <c r="H103">
+        <v>762</v>
+      </c>
+      <c r="I103">
+        <v>46294</v>
+      </c>
+      <c r="J103">
+        <v>500</v>
+      </c>
+      <c r="K103" t="s">
+        <v>261</v>
+      </c>
+      <c r="L103" t="s">
+        <v>62</v>
+      </c>
+      <c r="M103" t="s">
+        <v>84</v>
+      </c>
+      <c r="O103" t="s">
+        <v>11</v>
+      </c>
+      <c r="P103" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>85</v>
+      </c>
+      <c r="R103" t="s">
+        <v>64</v>
+      </c>
+      <c r="S103" t="s">
+        <v>65</v>
+      </c>
+      <c r="T103" t="s">
+        <v>29</v>
+      </c>
+      <c r="U103" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>427</v>
+      </c>
+      <c r="B104" t="s">
+        <v>428</v>
+      </c>
+      <c r="C104" t="s">
+        <v>429</v>
+      </c>
+      <c r="D104" t="s">
+        <v>59</v>
+      </c>
+      <c r="E104" t="s">
+        <v>82</v>
+      </c>
+      <c r="G104" t="s">
+        <v>60</v>
+      </c>
+      <c r="H104">
+        <v>761</v>
+      </c>
+      <c r="I104">
+        <v>46294</v>
+      </c>
+      <c r="J104">
+        <v>500</v>
+      </c>
+      <c r="K104" t="s">
+        <v>261</v>
+      </c>
+      <c r="L104" t="s">
+        <v>62</v>
+      </c>
+      <c r="M104" t="s">
+        <v>84</v>
+      </c>
+      <c r="O104" t="s">
+        <v>11</v>
+      </c>
+      <c r="P104" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>85</v>
+      </c>
+      <c r="R104" t="s">
+        <v>64</v>
+      </c>
+      <c r="S104" t="s">
+        <v>65</v>
+      </c>
+      <c r="T104" t="s">
+        <v>29</v>
+      </c>
+      <c r="U104" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>190</v>
+      </c>
+      <c r="B105" t="s">
+        <v>191</v>
+      </c>
+      <c r="C105" t="s">
+        <v>192</v>
+      </c>
+      <c r="D105" t="s">
+        <v>59</v>
+      </c>
+      <c r="E105" t="s">
+        <v>193</v>
+      </c>
+      <c r="G105" t="s">
+        <v>60</v>
+      </c>
+      <c r="H105">
+        <v>203</v>
+      </c>
+      <c r="I105">
+        <v>46189</v>
+      </c>
+      <c r="J105">
+        <v>5280</v>
+      </c>
+      <c r="K105" t="s">
+        <v>194</v>
+      </c>
+      <c r="L105" t="s">
+        <v>62</v>
+      </c>
+      <c r="M105" t="s">
+        <v>84</v>
+      </c>
+      <c r="O105" t="s">
+        <v>7</v>
+      </c>
+      <c r="P105" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>195</v>
+      </c>
+      <c r="R105" t="s">
+        <v>64</v>
+      </c>
+      <c r="S105" t="s">
+        <v>65</v>
+      </c>
+      <c r="T105" t="s">
+        <v>6</v>
+      </c>
+      <c r="U105" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>196</v>
+      </c>
+      <c r="B106" t="s">
+        <v>197</v>
+      </c>
+      <c r="C106" t="s">
+        <v>198</v>
+      </c>
+      <c r="D106" t="s">
+        <v>59</v>
+      </c>
+      <c r="E106" t="s">
+        <v>199</v>
+      </c>
+      <c r="G106" t="s">
+        <v>60</v>
+      </c>
+      <c r="H106">
         <v>202</v>
       </c>
-      <c r="I64" s="1">
+      <c r="I106">
         <v>46189</v>
       </c>
-      <c r="J64" s="2">
+      <c r="J106">
         <v>16720</v>
       </c>
-      <c r="K64" t="s">
-        <v>201</v>
-      </c>
-      <c r="L64" t="s">
-        <v>63</v>
-      </c>
-      <c r="M64" t="s">
-        <v>85</v>
-      </c>
-      <c r="O64" t="s">
+      <c r="K106" t="s">
+        <v>194</v>
+      </c>
+      <c r="L106" t="s">
+        <v>62</v>
+      </c>
+      <c r="M106" t="s">
+        <v>84</v>
+      </c>
+      <c r="O106" t="s">
         <v>7</v>
       </c>
-      <c r="P64" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>207</v>
-      </c>
-      <c r="R64" t="s">
-        <v>65</v>
-      </c>
-      <c r="S64" t="s">
-        <v>66</v>
-      </c>
-      <c r="T64" t="s">
+      <c r="P106" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>200</v>
+      </c>
+      <c r="R106" t="s">
+        <v>64</v>
+      </c>
+      <c r="S106" t="s">
+        <v>65</v>
+      </c>
+      <c r="T106" t="s">
         <v>6</v>
       </c>
-      <c r="U64" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="65" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I65" s="1"/>
-      <c r="J65" s="2"/>
-    </row>
-    <row r="66" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I66" s="1"/>
-      <c r="J66" s="2"/>
-    </row>
-    <row r="67" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I67" s="1"/>
-      <c r="J67" s="2"/>
-    </row>
-    <row r="68" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I68" s="1"/>
-    </row>
-    <row r="69" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I69" s="1"/>
-    </row>
-    <row r="70" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I70" s="1"/>
-    </row>
-    <row r="71" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I71" s="1"/>
-      <c r="J71" s="2"/>
-    </row>
-    <row r="72" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I72" s="1"/>
-    </row>
-    <row r="73" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I73" s="1"/>
-    </row>
-    <row r="74" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I74" s="1"/>
-    </row>
-    <row r="75" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I75" s="1"/>
-    </row>
-    <row r="76" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I76" s="1"/>
-    </row>
-    <row r="77" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I77" s="1"/>
-    </row>
-    <row r="78" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I78" s="1"/>
-      <c r="O78" s="3"/>
-    </row>
-    <row r="79" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I79" s="1"/>
-      <c r="O79" s="3"/>
-    </row>
-    <row r="80" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I80" s="1"/>
-    </row>
-    <row r="81" spans="9:10" x14ac:dyDescent="0.35">
-      <c r="I81" s="1"/>
-      <c r="J81" s="2"/>
-    </row>
-    <row r="82" spans="9:10" x14ac:dyDescent="0.35">
-      <c r="I82" s="1"/>
-      <c r="J82" s="2"/>
-    </row>
-    <row r="83" spans="9:10" x14ac:dyDescent="0.35">
-      <c r="I83" s="1"/>
-      <c r="J83" s="2"/>
-    </row>
-    <row r="84" spans="9:10" x14ac:dyDescent="0.35">
-      <c r="I84" s="1"/>
-      <c r="J84" s="2"/>
-    </row>
-    <row r="85" spans="9:10" x14ac:dyDescent="0.35">
-      <c r="I85" s="1"/>
-    </row>
-    <row r="86" spans="9:10" x14ac:dyDescent="0.35">
-      <c r="I86" s="1"/>
-      <c r="J86" s="2"/>
-    </row>
-    <row r="87" spans="9:10" x14ac:dyDescent="0.35">
-      <c r="I87" s="1"/>
-    </row>
-    <row r="88" spans="9:10" x14ac:dyDescent="0.35">
-      <c r="I88" s="1"/>
-      <c r="J88" s="2"/>
-    </row>
-    <row r="89" spans="9:10" x14ac:dyDescent="0.35">
-      <c r="I89" s="1"/>
-    </row>
-    <row r="90" spans="9:10" x14ac:dyDescent="0.35">
-      <c r="I90" s="1"/>
-    </row>
-    <row r="91" spans="9:10" x14ac:dyDescent="0.35">
-      <c r="I91" s="1"/>
-    </row>
-    <row r="92" spans="9:10" x14ac:dyDescent="0.35">
-      <c r="I92" s="1"/>
-    </row>
-    <row r="93" spans="9:10" x14ac:dyDescent="0.35">
-      <c r="I93" s="1"/>
-    </row>
-    <row r="94" spans="9:10" x14ac:dyDescent="0.35">
-      <c r="I94" s="1"/>
+      <c r="U106" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>746</v>
+      </c>
+      <c r="B107" t="s">
+        <v>747</v>
+      </c>
+      <c r="C107" t="s">
+        <v>748</v>
+      </c>
+      <c r="D107" t="s">
+        <v>59</v>
+      </c>
+      <c r="E107" t="s">
+        <v>749</v>
+      </c>
+      <c r="G107" t="s">
+        <v>60</v>
+      </c>
+      <c r="H107">
+        <v>21395</v>
+      </c>
+      <c r="I107">
+        <v>46296</v>
+      </c>
+      <c r="J107">
+        <v>2800</v>
+      </c>
+      <c r="K107" t="s">
+        <v>750</v>
+      </c>
+      <c r="L107" t="s">
+        <v>62</v>
+      </c>
+      <c r="M107" t="s">
+        <v>332</v>
+      </c>
+      <c r="O107" t="s">
+        <v>621</v>
+      </c>
+      <c r="P107" t="s">
+        <v>622</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>623</v>
+      </c>
+      <c r="R107" t="s">
+        <v>64</v>
+      </c>
+      <c r="S107" t="s">
+        <v>65</v>
+      </c>
+      <c r="T107" t="s">
+        <v>3</v>
+      </c>
+      <c r="U107" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>751</v>
+      </c>
+      <c r="B108" t="s">
+        <v>752</v>
+      </c>
+      <c r="C108" t="s">
+        <v>753</v>
+      </c>
+      <c r="D108" t="s">
+        <v>59</v>
+      </c>
+      <c r="E108" t="s">
+        <v>754</v>
+      </c>
+      <c r="G108" t="s">
+        <v>60</v>
+      </c>
+      <c r="H108">
+        <v>60958</v>
+      </c>
+      <c r="I108">
+        <v>46296</v>
+      </c>
+      <c r="J108">
+        <v>15.93</v>
+      </c>
+      <c r="K108" t="s">
+        <v>473</v>
+      </c>
+      <c r="L108" t="s">
+        <v>62</v>
+      </c>
+      <c r="M108" t="s">
+        <v>162</v>
+      </c>
+      <c r="O108" t="s">
+        <v>474</v>
+      </c>
+      <c r="P108" t="s">
+        <v>475</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>476</v>
+      </c>
+      <c r="R108" t="s">
+        <v>64</v>
+      </c>
+      <c r="S108" t="s">
+        <v>65</v>
+      </c>
+      <c r="T108" t="s">
+        <v>477</v>
+      </c>
+      <c r="U108" t="s">
+        <v>66</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/INDUSTRIAL.xlsx
+++ b/INDUSTRIAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GUDESCHA\Downloads\Dashaboard em HTML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36787315-9C33-42DF-BEB1-D38F331D260E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A4A553-8038-47F9-B4EE-276762485B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F2E2EF4D-F0CD-41CA-9DD0-62727A1AD53A}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1716" uniqueCount="755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="734">
   <si>
     <t>Fornecedor</t>
   </si>
@@ -117,9 +117,6 @@
     <t>Rafaela Alves</t>
   </si>
   <si>
-    <t>B67827</t>
-  </si>
-  <si>
     <t>Marinete Pereira</t>
   </si>
   <si>
@@ -453,9 +450,6 @@
     <t>31861323000527&amp;08/05/2026&amp;</t>
   </si>
   <si>
-    <t>Pedido não informado</t>
-  </si>
-  <si>
     <t>SKFAPE202609041641230889</t>
   </si>
   <si>
@@ -648,24 +642,6 @@
     <t>P116642</t>
   </si>
   <si>
-    <t>SKFAPE202609041348390846</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85830427PO</t>
-  </si>
-  <si>
-    <t>2026-09-04 13:48:39.54</t>
-  </si>
-  <si>
-    <t>270515.57</t>
-  </si>
-  <si>
-    <t>03519007000102&amp;30/11/2026</t>
-  </si>
-  <si>
-    <t>EP1457750</t>
-  </si>
-  <si>
     <t>SKFAPE202608311931510712</t>
   </si>
   <si>
@@ -792,9 +768,6 @@
     <t>RAZAC INTERNATIONAL TRADE LTDA</t>
   </si>
   <si>
-    <t>ILS CARGO TRANSPORTES INTERNAC</t>
-  </si>
-  <si>
     <t>CRESCIMENTUM CON PESSOAL E EMP</t>
   </si>
   <si>
@@ -819,36 +792,6 @@
     <t>SPEED IO SERV ESPECIALI LTDA</t>
   </si>
   <si>
-    <t>SKFAPE202609301743310915</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85852322PO</t>
-  </si>
-  <si>
-    <t>2026-09-30 17:43:31.193</t>
-  </si>
-  <si>
-    <t>09059224000224&amp;NA&amp;5000</t>
-  </si>
-  <si>
-    <t>SKFAPE202609301743510916</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85852323PO</t>
-  </si>
-  <si>
-    <t>2026-09-30 17:43:51.417</t>
-  </si>
-  <si>
-    <t>SKFAPE202609301744100917</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85852324PO</t>
-  </si>
-  <si>
-    <t>2026-09-30 17:44:10.827</t>
-  </si>
-  <si>
     <t>SKFAPE202609301744140918</t>
   </si>
   <si>
@@ -933,87 +876,12 @@
     <t>03857930001479&amp;31/12/2026</t>
   </si>
   <si>
-    <t>SKFAPE202610021137270649</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85854472PO</t>
-  </si>
-  <si>
-    <t>2026-10-02 11:37:27.777</t>
-  </si>
-  <si>
-    <t>41919.46</t>
-  </si>
-  <si>
-    <t>17895646000187&amp;NA&amp;9001</t>
-  </si>
-  <si>
-    <t>B71555</t>
-  </si>
-  <si>
-    <t>UBER DO BRASIL TECNOLOGIA</t>
-  </si>
-  <si>
-    <t>EP1662958</t>
-  </si>
-  <si>
-    <t>Viviane Silva</t>
-  </si>
-  <si>
-    <t>SKFAPE202610021137470650</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85854473PO</t>
-  </si>
-  <si>
-    <t>2026-10-02 11:37:47.527</t>
-  </si>
-  <si>
-    <t>3628.00</t>
-  </si>
-  <si>
-    <t>10403559000116&amp;01/11/2026&amp;</t>
-  </si>
-  <si>
     <t>14.01</t>
   </si>
   <si>
-    <t>B69598</t>
-  </si>
-  <si>
-    <t>KFAB IND E CO DE PR P FIL E TR</t>
-  </si>
-  <si>
-    <t>EP1799054</t>
-  </si>
-  <si>
     <t>Glaucilaine Demarchi</t>
   </si>
   <si>
-    <t>SKFAPE202610021138080651</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85854474PO</t>
-  </si>
-  <si>
-    <t>2026-10-02 11:38:08.343</t>
-  </si>
-  <si>
-    <t>1700.00</t>
-  </si>
-  <si>
-    <t>20593699000158&amp;02/09/2026&amp;</t>
-  </si>
-  <si>
-    <t>07.11</t>
-  </si>
-  <si>
-    <t>B73269</t>
-  </si>
-  <si>
-    <t>EP1771835</t>
-  </si>
-  <si>
     <t>SKFAPE202610021140150658</t>
   </si>
   <si>
@@ -1065,18 +933,6 @@
     <t>7051.50</t>
   </si>
   <si>
-    <t>SKFAPE202610012001020379</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85853738PO</t>
-  </si>
-  <si>
-    <t>2026-10-01 20:01:02.233</t>
-  </si>
-  <si>
-    <t>247890.09</t>
-  </si>
-  <si>
     <t>60625431000175&amp;25/10/2026</t>
   </si>
   <si>
@@ -1086,9 +942,6 @@
     <t>DELTA MONTAGENS IND LTDA</t>
   </si>
   <si>
-    <t>EP1659530</t>
-  </si>
-  <si>
     <t>SKFAPE202610012001210380</t>
   </si>
   <si>
@@ -1104,69 +957,6 @@
     <t>EP1778417</t>
   </si>
   <si>
-    <t>SKFAPE202609302006050948</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85852564PO</t>
-  </si>
-  <si>
-    <t>2026-09-30 20:06:05.717</t>
-  </si>
-  <si>
-    <t>SKFAPE202609302006250949</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85852565PO</t>
-  </si>
-  <si>
-    <t>2026-09-30 20:06:25.697</t>
-  </si>
-  <si>
-    <t>SKFAPE202609302006310950</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85852566PO</t>
-  </si>
-  <si>
-    <t>2026-09-30 20:06:31.8</t>
-  </si>
-  <si>
-    <t>SKFAPE202609301742110911</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85852316PO</t>
-  </si>
-  <si>
-    <t>2026-09-30 17:42:12.107</t>
-  </si>
-  <si>
-    <t>SKFAPE202609301742310912</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85852317PO</t>
-  </si>
-  <si>
-    <t>2026-09-30 17:42:31.877</t>
-  </si>
-  <si>
-    <t>SKFAPE202609301742520913</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85852320PO</t>
-  </si>
-  <si>
-    <t>2026-09-30 17:42:52.297</t>
-  </si>
-  <si>
-    <t>SKFAPE202609301743110914</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85852321PO</t>
-  </si>
-  <si>
-    <t>2026-09-30 17:43:11.687</t>
-  </si>
-  <si>
     <t>SKFAPE202609301745130921</t>
   </si>
   <si>
@@ -1179,51 +969,6 @@
     <t>22920.95</t>
   </si>
   <si>
-    <t>SKFAPE202609301740280905</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85852310PO</t>
-  </si>
-  <si>
-    <t>2026-09-30 17:40:28.703</t>
-  </si>
-  <si>
-    <t>SKFAPE202609301740480906</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85852311PO</t>
-  </si>
-  <si>
-    <t>2026-09-30 17:40:49.117</t>
-  </si>
-  <si>
-    <t>SKFAPE202609301741080907</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85852312PO</t>
-  </si>
-  <si>
-    <t>2026-09-30 17:41:08.603</t>
-  </si>
-  <si>
-    <t>SKFAPE202609301741280908</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85852313PO</t>
-  </si>
-  <si>
-    <t>2026-09-30 17:41:28.54</t>
-  </si>
-  <si>
-    <t>SKFAPE202609301741470909</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85852314PO</t>
-  </si>
-  <si>
-    <t>2026-09-30 17:41:48.073</t>
-  </si>
-  <si>
     <t>SKFAPE202610021138270652</t>
   </si>
   <si>
@@ -1287,30 +1032,6 @@
     <t>Patricia Pinto Dias de Souza</t>
   </si>
   <si>
-    <t>SKFAPE202610021139110655</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85854478PO</t>
-  </si>
-  <si>
-    <t>2026-10-02 11:39:11.927</t>
-  </si>
-  <si>
-    <t>19950.00</t>
-  </si>
-  <si>
-    <t>11633691000187&amp;NA&amp;9001</t>
-  </si>
-  <si>
-    <t>14.06</t>
-  </si>
-  <si>
-    <t>B73235</t>
-  </si>
-  <si>
-    <t>EP1658693</t>
-  </si>
-  <si>
     <t>SKFAPE202610021139560657</t>
   </si>
   <si>
@@ -1326,15 +1047,6 @@
     <t>07100026000150&amp;01/12/2026&amp;</t>
   </si>
   <si>
-    <t>SKFAPE202609301742070910</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85852315PO</t>
-  </si>
-  <si>
-    <t>2026-09-30 17:42:07.57</t>
-  </si>
-  <si>
     <t>SKFAPE202610051221090991</t>
   </si>
   <si>
@@ -1359,99 +1071,9 @@
     <t>EP1759507</t>
   </si>
   <si>
-    <t>SKFAPE202610051221280992</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85855782PO</t>
-  </si>
-  <si>
-    <t>2026-10-05 12:21:28.837</t>
-  </si>
-  <si>
-    <t>3315.00</t>
-  </si>
-  <si>
-    <t>31199199000152&amp;NA&amp;9001</t>
-  </si>
-  <si>
-    <t>04.01</t>
-  </si>
-  <si>
-    <t>B71492</t>
-  </si>
-  <si>
-    <t>PRAM SERVIÇOS MEDICO</t>
-  </si>
-  <si>
-    <t>EP1735635</t>
-  </si>
-  <si>
     <t>Kamila Vieira</t>
   </si>
   <si>
-    <t>SKFAPE202610051221480993</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85855783PO</t>
-  </si>
-  <si>
-    <t>2026-10-05 12:21:48.293</t>
-  </si>
-  <si>
-    <t>18221.90</t>
-  </si>
-  <si>
-    <t>48109110000112&amp;16/11/2026&amp;9002</t>
-  </si>
-  <si>
-    <t>17.14</t>
-  </si>
-  <si>
-    <t>EP1799619</t>
-  </si>
-  <si>
-    <t>Joyce Santos</t>
-  </si>
-  <si>
-    <t>SKFAPE202610051222280995</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85855785PO</t>
-  </si>
-  <si>
-    <t>2026-10-05 12:22:28.153</t>
-  </si>
-  <si>
-    <t>1820.12</t>
-  </si>
-  <si>
-    <t>EP1799620</t>
-  </si>
-  <si>
-    <t>SKFAPE202610051215360971</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85855757PO</t>
-  </si>
-  <si>
-    <t>2026-10-05 12:15:36.97</t>
-  </si>
-  <si>
-    <t>23000.00</t>
-  </si>
-  <si>
-    <t>20329532000184&amp;NA</t>
-  </si>
-  <si>
-    <t>B73254</t>
-  </si>
-  <si>
-    <t>ALEXANDRE DE ALMEIDA CHIA</t>
-  </si>
-  <si>
-    <t>EP1665486</t>
-  </si>
-  <si>
     <t>SKFAPE202610051215550972</t>
   </si>
   <si>
@@ -1539,33 +1161,6 @@
     <t>EP1660609</t>
   </si>
   <si>
-    <t>SKFAPE202610051211260956</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85855740PO</t>
-  </si>
-  <si>
-    <t>2026-10-05 12:11:26.213</t>
-  </si>
-  <si>
-    <t>2650.00</t>
-  </si>
-  <si>
-    <t>09397942000120&amp;NA</t>
-  </si>
-  <si>
-    <t>14.02</t>
-  </si>
-  <si>
-    <t>B67053</t>
-  </si>
-  <si>
-    <t>SYLAMAG INFORMATICA COM E SER</t>
-  </si>
-  <si>
-    <t>EP1664305</t>
-  </si>
-  <si>
     <t>SKFAPE202610051211450957</t>
   </si>
   <si>
@@ -1776,30 +1371,6 @@
     <t>5631.00</t>
   </si>
   <si>
-    <t>SKFAPE202610051217570979</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85855765PO</t>
-  </si>
-  <si>
-    <t>2026-10-05 12:17:57.613</t>
-  </si>
-  <si>
-    <t>1575.00</t>
-  </si>
-  <si>
-    <t>05538148000106&amp;28/10/2026</t>
-  </si>
-  <si>
-    <t>B70590</t>
-  </si>
-  <si>
-    <t>PROAQT EMPREENDIMENTOS TEC LTD</t>
-  </si>
-  <si>
-    <t>EP1795365</t>
-  </si>
-  <si>
     <t>SKFAPE202610051219440986</t>
   </si>
   <si>
@@ -1848,51 +1419,6 @@
     <t>EP1804330</t>
   </si>
   <si>
-    <t>SKFAPE202610051220490990</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85855780PO</t>
-  </si>
-  <si>
-    <t>2026-10-05 12:20:49.337</t>
-  </si>
-  <si>
-    <t>2270.00</t>
-  </si>
-  <si>
-    <t>16549592000135&amp;NA&amp;9001</t>
-  </si>
-  <si>
-    <t>04.21</t>
-  </si>
-  <si>
-    <t>B73371</t>
-  </si>
-  <si>
-    <t>TRANSHELP - SERV AMBULAN</t>
-  </si>
-  <si>
-    <t>EP1769937</t>
-  </si>
-  <si>
-    <t>SKFAPE202610051222320996</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85855786PO</t>
-  </si>
-  <si>
-    <t>2026-10-05 12:22:32.56</t>
-  </si>
-  <si>
-    <t>1478.13</t>
-  </si>
-  <si>
-    <t>05538148000106&amp;NA&amp;&amp;7502</t>
-  </si>
-  <si>
-    <t>EP1774329</t>
-  </si>
-  <si>
     <t>SKFAPE202610051222510997</t>
   </si>
   <si>
@@ -1941,30 +1467,6 @@
     <t>EP1780835</t>
   </si>
   <si>
-    <t>SKFAPE202610051225570109</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85855798PO</t>
-  </si>
-  <si>
-    <t>2026-10-05 12:25:58.007</t>
-  </si>
-  <si>
-    <t>17069.99</t>
-  </si>
-  <si>
-    <t>03506307000157&amp;22/10/2026&amp;9001</t>
-  </si>
-  <si>
-    <t>B70837</t>
-  </si>
-  <si>
-    <t>TICKET SOLUCOES HDFGT SA</t>
-  </si>
-  <si>
-    <t>EP1769947</t>
-  </si>
-  <si>
     <t>SKFAPE202610051226030110</t>
   </si>
   <si>
@@ -1989,9 +1491,6 @@
     <t>EP1802975</t>
   </si>
   <si>
-    <t>RODRIGO BERTOLINO JOSE</t>
-  </si>
-  <si>
     <t>SKFAPE202609081425380594</t>
   </si>
   <si>
@@ -2016,60 +1515,6 @@
     <t>EP1702648</t>
   </si>
   <si>
-    <t>SKFAPE202610051223350101</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85855790PO</t>
-  </si>
-  <si>
-    <t>2026-10-05 12:23:36.05</t>
-  </si>
-  <si>
-    <t>7704.80</t>
-  </si>
-  <si>
-    <t>33040981000150&amp;</t>
-  </si>
-  <si>
-    <t>B71171</t>
-  </si>
-  <si>
-    <t>AIG SEGUROS BRASIL S.A.</t>
-  </si>
-  <si>
-    <t>EP1805915</t>
-  </si>
-  <si>
-    <t>SKFAPE202610051223550102</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85855791PO</t>
-  </si>
-  <si>
-    <t>2026-10-05 12:23:55.517</t>
-  </si>
-  <si>
-    <t>198612.03</t>
-  </si>
-  <si>
-    <t>EP1805916</t>
-  </si>
-  <si>
-    <t>SKFAPE202610051212290960</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85855744PO</t>
-  </si>
-  <si>
-    <t>2026-10-05 12:12:29.603</t>
-  </si>
-  <si>
-    <t>7304.80</t>
-  </si>
-  <si>
-    <t>15664649000184&amp;31/10/2026</t>
-  </si>
-  <si>
     <t>B72251</t>
   </si>
   <si>
@@ -2157,33 +1602,6 @@
     <t>EP1683421</t>
   </si>
   <si>
-    <t>SKFAPE202610051219000983</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85855769PO</t>
-  </si>
-  <si>
-    <t>2026-10-05 12:19:01.04</t>
-  </si>
-  <si>
-    <t>546.00</t>
-  </si>
-  <si>
-    <t>22226517000136&amp;NA</t>
-  </si>
-  <si>
-    <t>24.01</t>
-  </si>
-  <si>
-    <t>B72133</t>
-  </si>
-  <si>
-    <t>MAURO FIORAVANTI TASCHETTO</t>
-  </si>
-  <si>
-    <t>EP1799056</t>
-  </si>
-  <si>
     <t>SKFAPE202610051219210984</t>
   </si>
   <si>
@@ -2226,42 +1644,6 @@
     <t>Anderson R Doimo</t>
   </si>
   <si>
-    <t>SKFAPE202610051210460954</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85855738PO</t>
-  </si>
-  <si>
-    <t>2026-10-05 12:10:46.36</t>
-  </si>
-  <si>
-    <t>1126.20</t>
-  </si>
-  <si>
-    <t>13965130000100&amp;NA</t>
-  </si>
-  <si>
-    <t>B71576</t>
-  </si>
-  <si>
-    <t>ENERGY &amp; TELL SOL Q REDUZ CUST</t>
-  </si>
-  <si>
-    <t>EP1753516</t>
-  </si>
-  <si>
-    <t>SKFAPE202610051211060955</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85855739PO</t>
-  </si>
-  <si>
-    <t>2026-10-05 12:11:06.96</t>
-  </si>
-  <si>
-    <t>EP1735901</t>
-  </si>
-  <si>
     <t>SKFAPE202610051219250985</t>
   </si>
   <si>
@@ -2280,9 +1662,6 @@
     <t>EP1800415</t>
   </si>
   <si>
-    <t>AREA 19 TELECOMUNICAÇOES</t>
-  </si>
-  <si>
     <t>SKFAPE202610051213480964</t>
   </si>
   <si>
@@ -2308,6 +1687,564 @@
   </si>
   <si>
     <t>15.93</t>
+  </si>
+  <si>
+    <t>SKFAPM202610061112520439</t>
+  </si>
+  <si>
+    <t>2026-10-06 11:14:16.867</t>
+  </si>
+  <si>
+    <t>605254.44</t>
+  </si>
+  <si>
+    <t>13024&amp;01</t>
+  </si>
+  <si>
+    <t>02833315000579&amp;07/11/2026</t>
+  </si>
+  <si>
+    <t>Informar se a nota será cancelada</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061249040479</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85856957PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 12:49:04.617</t>
+  </si>
+  <si>
+    <t>5629.27</t>
+  </si>
+  <si>
+    <t>EP1664682</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061248000475</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85856953PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 12:48:00.367</t>
+  </si>
+  <si>
+    <t>528.60</t>
+  </si>
+  <si>
+    <t>07312805000110&amp;04/11/2026</t>
+  </si>
+  <si>
+    <t>B72214</t>
+  </si>
+  <si>
+    <t>DHARMACOM TELECOMUNICACOES LTD</t>
+  </si>
+  <si>
+    <t>EP1660605</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061248190476</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85856954PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 12:48:19.79</t>
+  </si>
+  <si>
+    <t>EP1660606</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061742480549</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85857328PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 17:42:49.047</t>
+  </si>
+  <si>
+    <t>44444.48</t>
+  </si>
+  <si>
+    <t>04911895000177&amp;NA</t>
+  </si>
+  <si>
+    <t>17.06</t>
+  </si>
+  <si>
+    <t>B72612</t>
+  </si>
+  <si>
+    <t>MAPA COMUNIC E ASSESSORIA LTDA</t>
+  </si>
+  <si>
+    <t>EP1714670</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061248440478</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85856956PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 12:48:44.933</t>
+  </si>
+  <si>
+    <t>44.90</t>
+  </si>
+  <si>
+    <t>01.06</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061744320555</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85857362PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 17:44:32.643</t>
+  </si>
+  <si>
+    <t>406.15</t>
+  </si>
+  <si>
+    <t>24425691000133&amp;05/12/2026</t>
+  </si>
+  <si>
+    <t>B73069</t>
+  </si>
+  <si>
+    <t>PREDICTUS PES COM A TEND NEG</t>
+  </si>
+  <si>
+    <t>EP1664308</t>
+  </si>
+  <si>
+    <t>Pedido sem saldo</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051757560169</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85856056PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 17:57:56.947</t>
+  </si>
+  <si>
+    <t>308.75</t>
+  </si>
+  <si>
+    <t>33463323000170&amp;NA</t>
+  </si>
+  <si>
+    <t>14.10</t>
+  </si>
+  <si>
+    <t>B71856</t>
+  </si>
+  <si>
+    <t>PRISCILA MARIA DA SILVA</t>
+  </si>
+  <si>
+    <t>EP1804441</t>
+  </si>
+  <si>
+    <t>Vanessa Formico</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061740440542</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85857321PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 17:40:44.583</t>
+  </si>
+  <si>
+    <t>2775.88</t>
+  </si>
+  <si>
+    <t>EP1660440</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061245320466</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85856942PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 12:45:32.247</t>
+  </si>
+  <si>
+    <t>24858.86</t>
+  </si>
+  <si>
+    <t>15664649000184&amp;01/11/2026</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061742290548</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85857327PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 17:42:29.477</t>
+  </si>
+  <si>
+    <t>21151.37</t>
+  </si>
+  <si>
+    <t>35208487000187&amp;NA</t>
+  </si>
+  <si>
+    <t>16.02</t>
+  </si>
+  <si>
+    <t>B73237</t>
+  </si>
+  <si>
+    <t>COOPERATIVA DE RADIOM. DOS COND. AUTON. E TAX</t>
+  </si>
+  <si>
+    <t>EP1694950</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061245560468</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85856944PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 12:45:56.453</t>
+  </si>
+  <si>
+    <t>1737.06</t>
+  </si>
+  <si>
+    <t>03175428000163&amp;31/12/2026</t>
+  </si>
+  <si>
+    <t>B72668</t>
+  </si>
+  <si>
+    <t>AMBIPAR GREEN TECH LTDA</t>
+  </si>
+  <si>
+    <t>EP1788084</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061742050546</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85857325PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 17:42:05.533</t>
+  </si>
+  <si>
+    <t>31518.00</t>
+  </si>
+  <si>
+    <t>EP1659152</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061311430486</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85856973PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 13:11:43.373</t>
+  </si>
+  <si>
+    <t>30640.00</t>
+  </si>
+  <si>
+    <t>30229786000184&amp;NA</t>
+  </si>
+  <si>
+    <t>B72011</t>
+  </si>
+  <si>
+    <t>C9 APPS DES DE SOFTWARE LTDA</t>
+  </si>
+  <si>
+    <t>EP1671314</t>
+  </si>
+  <si>
+    <t>Fabio Caner</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061742240547</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85857326PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 17:42:24.867</t>
+  </si>
+  <si>
+    <t>18540.00</t>
+  </si>
+  <si>
+    <t>EP1659153</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061743280551</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85857330PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 17:43:28.677</t>
+  </si>
+  <si>
+    <t>15965.00</t>
+  </si>
+  <si>
+    <t>EP1667071</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061248240477</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85856955PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 12:48:24.367</t>
+  </si>
+  <si>
+    <t>11000.00</t>
+  </si>
+  <si>
+    <t>31980223000196&amp;NA</t>
+  </si>
+  <si>
+    <t>B71473</t>
+  </si>
+  <si>
+    <t>EDIEL SIQUEIRA DE ANDRADE JUNI</t>
+  </si>
+  <si>
+    <t>EP1786099</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061741040543</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85857322PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 17:41:04.493</t>
+  </si>
+  <si>
+    <t>10000.00</t>
+  </si>
+  <si>
+    <t>EP1658706</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061743080550</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85857329PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 17:43:08.923</t>
+  </si>
+  <si>
+    <t>7750.00</t>
+  </si>
+  <si>
+    <t>14757044000256&amp;NA</t>
+  </si>
+  <si>
+    <t>B72500</t>
+  </si>
+  <si>
+    <t>EXTIMBRAS MATERIAL DE SEGURANC</t>
+  </si>
+  <si>
+    <t>EP1804997</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061744520556</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85857363PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 17:44:52.23</t>
+  </si>
+  <si>
+    <t>5824.00</t>
+  </si>
+  <si>
+    <t>01438656000153&amp;20/11/2026</t>
+  </si>
+  <si>
+    <t>B63863</t>
+  </si>
+  <si>
+    <t>JHM EQUIPAMENTOS INDUSTRIAIS L</t>
+  </si>
+  <si>
+    <t>EP1805561</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061246560471</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85856949PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 12:46:56.177</t>
+  </si>
+  <si>
+    <t>4860.00</t>
+  </si>
+  <si>
+    <t>EP1798662</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061247400474</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85856952PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 12:47:41.043</t>
+  </si>
+  <si>
+    <t>3531.00</t>
+  </si>
+  <si>
+    <t>EP1678556</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061743480552</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85857332PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 17:43:48.507</t>
+  </si>
+  <si>
+    <t>3090.00</t>
+  </si>
+  <si>
+    <t>61827713000118&amp;29/11/2026</t>
+  </si>
+  <si>
+    <t>B65526</t>
+  </si>
+  <si>
+    <t>JHM MOTORES E EQUIP IND LTDA M</t>
+  </si>
+  <si>
+    <t>EP1804905</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051757370168</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85856055PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 17:57:37.543</t>
+  </si>
+  <si>
+    <t>850.00</t>
+  </si>
+  <si>
+    <t>07689002000189&amp;01/12/2026</t>
+  </si>
+  <si>
+    <t>7689002000189</t>
+  </si>
+  <si>
+    <t>TO INDO EXPRESS LTDA</t>
+  </si>
+  <si>
+    <t>EP1805766</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061739400538</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85857317PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 17:39:40.183</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061743530553</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85857334PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 17:43:53.74</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061740000539</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85857318PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 17:40:00.673</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061740200540</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85857319PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 17:40:20.317</t>
+  </si>
+  <si>
+    <t>EP1685518</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061740240541</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85857320PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 17:40:24.857</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061741240544</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85857323PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 17:41:24.183</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051756300167</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85856054PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 17:56:31.023</t>
+  </si>
+  <si>
+    <t>285.00</t>
+  </si>
+  <si>
+    <t>EP1660607</t>
   </si>
 </sst>
 </file>
@@ -2685,7 +2622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{442415D8-C6A7-43A8-8242-0B2814FB2593}">
-  <dimension ref="A1:U108"/>
+  <dimension ref="A1:U102"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.36328125" bestFit="1" customWidth="1"/>
@@ -2712,444 +2649,444 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
         <v>39</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>40</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>41</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>42</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>43</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>44</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>45</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>46</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>47</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>48</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>49</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>50</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>51</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>52</v>
-      </c>
-      <c r="O1" t="s">
-        <v>53</v>
       </c>
       <c r="P1" t="s">
         <v>0</v>
       </c>
       <c r="Q1" t="s">
+        <v>53</v>
+      </c>
+      <c r="R1" t="s">
         <v>54</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>55</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>56</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>57</v>
-      </c>
-      <c r="U1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>430</v>
+        <v>283</v>
       </c>
       <c r="B2" t="s">
-        <v>431</v>
+        <v>284</v>
       </c>
       <c r="C2" t="s">
-        <v>432</v>
+        <v>285</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>433</v>
+        <v>286</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H2">
-        <v>1329151</v>
+        <v>1657</v>
       </c>
       <c r="I2" s="1">
         <v>46296</v>
       </c>
       <c r="J2">
-        <v>9079.8799999999992</v>
+        <v>9909.09</v>
       </c>
       <c r="K2" t="s">
-        <v>434</v>
+        <v>287</v>
       </c>
       <c r="L2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M2" t="s">
-        <v>84</v>
+        <v>288</v>
       </c>
       <c r="O2" t="s">
-        <v>435</v>
+        <v>289</v>
       </c>
       <c r="P2" t="s">
-        <v>436</v>
+        <v>290</v>
       </c>
       <c r="Q2" t="s">
-        <v>437</v>
+        <v>291</v>
       </c>
       <c r="R2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S2" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="T2" t="s">
-        <v>413</v>
+        <v>23</v>
       </c>
       <c r="U2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>438</v>
+        <v>352</v>
       </c>
       <c r="B3" t="s">
-        <v>439</v>
+        <v>353</v>
       </c>
       <c r="C3" t="s">
-        <v>440</v>
+        <v>354</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>441</v>
+        <v>355</v>
       </c>
       <c r="G3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H3">
-        <v>220</v>
+        <v>61031</v>
       </c>
       <c r="I3" s="1">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="J3">
-        <v>3400</v>
+        <v>976.95</v>
       </c>
       <c r="K3" t="s">
-        <v>442</v>
+        <v>347</v>
       </c>
       <c r="L3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M3" t="s">
-        <v>443</v>
+        <v>160</v>
       </c>
       <c r="O3" t="s">
-        <v>444</v>
+        <v>348</v>
       </c>
       <c r="P3" t="s">
-        <v>445</v>
+        <v>349</v>
       </c>
       <c r="Q3" t="s">
-        <v>446</v>
+        <v>350</v>
       </c>
       <c r="R3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T3" t="s">
-        <v>447</v>
+        <v>351</v>
       </c>
       <c r="U3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>448</v>
+        <v>199</v>
       </c>
       <c r="B4" t="s">
-        <v>449</v>
+        <v>200</v>
       </c>
       <c r="C4" t="s">
-        <v>450</v>
+        <v>201</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>451</v>
+        <v>202</v>
       </c>
       <c r="G4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H4">
-        <v>177670</v>
+        <v>21985</v>
       </c>
       <c r="I4" s="1">
-        <v>46297</v>
+        <v>46262</v>
       </c>
       <c r="J4">
-        <v>19415.98</v>
+        <v>969.98</v>
       </c>
       <c r="K4" t="s">
-        <v>452</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M4" t="s">
-        <v>453</v>
+        <v>96</v>
       </c>
       <c r="O4" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="P4" t="s">
-        <v>256</v>
+        <v>223</v>
       </c>
       <c r="Q4" t="s">
-        <v>454</v>
+        <v>224</v>
       </c>
       <c r="R4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T4" t="s">
-        <v>455</v>
+        <v>266</v>
       </c>
       <c r="U4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>456</v>
+        <v>334</v>
       </c>
       <c r="B5" t="s">
-        <v>457</v>
+        <v>335</v>
       </c>
       <c r="C5" t="s">
-        <v>458</v>
+        <v>336</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
-        <v>459</v>
+        <v>337</v>
       </c>
       <c r="G5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H5">
-        <v>177671</v>
+        <v>1329151</v>
       </c>
       <c r="I5" s="1">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="J5">
-        <v>1939.39</v>
+        <v>9079.8799999999992</v>
       </c>
       <c r="K5" t="s">
-        <v>452</v>
+        <v>338</v>
       </c>
       <c r="L5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M5" t="s">
-        <v>453</v>
+        <v>83</v>
       </c>
       <c r="O5" t="s">
-        <v>35</v>
+        <v>339</v>
       </c>
       <c r="P5" t="s">
-        <v>256</v>
+        <v>340</v>
       </c>
       <c r="Q5" t="s">
-        <v>460</v>
+        <v>341</v>
       </c>
       <c r="R5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T5" t="s">
-        <v>455</v>
+        <v>328</v>
       </c>
       <c r="U5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>461</v>
+        <v>499</v>
       </c>
       <c r="B6" t="s">
-        <v>462</v>
+        <v>500</v>
       </c>
       <c r="C6" t="s">
-        <v>463</v>
+        <v>501</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
-        <v>464</v>
+        <v>502</v>
       </c>
       <c r="G6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H6">
-        <v>39</v>
+        <v>5881</v>
       </c>
       <c r="I6" s="1">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="J6" s="2">
-        <v>23000</v>
+        <v>7887.75</v>
       </c>
       <c r="K6" t="s">
-        <v>465</v>
+        <v>503</v>
       </c>
       <c r="L6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M6" t="s">
-        <v>443</v>
+        <v>103</v>
       </c>
       <c r="O6" t="s">
-        <v>466</v>
+        <v>504</v>
       </c>
       <c r="P6" t="s">
-        <v>467</v>
+        <v>505</v>
       </c>
       <c r="Q6" t="s">
-        <v>468</v>
+        <v>506</v>
       </c>
       <c r="R6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T6" t="s">
-        <v>12</v>
+        <v>507</v>
       </c>
       <c r="U6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>469</v>
+        <v>91</v>
       </c>
       <c r="B7" t="s">
-        <v>470</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>471</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>472</v>
+        <v>94</v>
       </c>
       <c r="G7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H7">
-        <v>61032</v>
+        <v>21941</v>
       </c>
       <c r="I7" s="1">
-        <v>46296</v>
+        <v>46247</v>
       </c>
       <c r="J7" s="2">
-        <v>484.87</v>
+        <v>7881.75</v>
       </c>
       <c r="K7" t="s">
-        <v>473</v>
+        <v>95</v>
       </c>
       <c r="L7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M7" t="s">
-        <v>162</v>
+        <v>96</v>
       </c>
       <c r="O7" t="s">
-        <v>474</v>
+        <v>17</v>
       </c>
       <c r="P7" t="s">
-        <v>475</v>
+        <v>223</v>
       </c>
       <c r="Q7" t="s">
-        <v>476</v>
+        <v>97</v>
       </c>
       <c r="R7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T7" t="s">
-        <v>477</v>
+        <v>266</v>
       </c>
       <c r="U7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B8" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C8" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="G8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H8" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="I8" s="1">
         <v>46241</v>
@@ -3161,635 +3098,638 @@
         <v>45815647000100</v>
       </c>
       <c r="L8" t="s">
+        <v>61</v>
+      </c>
+      <c r="M8" t="s">
         <v>62</v>
       </c>
-      <c r="M8" t="s">
-        <v>63</v>
-      </c>
       <c r="O8" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="P8" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="Q8" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="R8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T8" t="s">
         <v>12</v>
       </c>
       <c r="U8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>123</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="G9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H9">
-        <v>201</v>
+        <v>12958</v>
       </c>
       <c r="I9" s="1">
-        <v>46253</v>
+        <v>46244</v>
       </c>
       <c r="J9" s="2">
-        <v>45439</v>
+        <v>746101.35</v>
       </c>
       <c r="K9" t="s">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="L9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M9" t="s">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="O9" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="P9" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="Q9" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="R9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T9" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="U9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="B10" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="C10" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="G10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H10">
-        <v>757</v>
+        <v>251785</v>
       </c>
       <c r="I10" s="1">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="J10" s="2">
-        <v>500</v>
+        <v>69505.789999999994</v>
       </c>
       <c r="K10" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="L10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M10" t="s">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="O10" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="P10" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="Q10" t="s">
-        <v>85</v>
+        <v>174</v>
       </c>
       <c r="R10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T10" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="U10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>262</v>
+        <v>169</v>
       </c>
       <c r="B11" t="s">
-        <v>263</v>
+        <v>170</v>
       </c>
       <c r="C11" t="s">
-        <v>264</v>
+        <v>171</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="G11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H11">
-        <v>755</v>
+        <v>251216</v>
       </c>
       <c r="I11" s="1">
-        <v>46294</v>
+        <v>46283</v>
       </c>
       <c r="J11" s="2">
-        <v>500</v>
+        <v>69505.789999999994</v>
       </c>
       <c r="K11" t="s">
-        <v>261</v>
+        <v>173</v>
       </c>
       <c r="L11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M11" t="s">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="O11" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="P11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="Q11" t="s">
-        <v>85</v>
+        <v>174</v>
       </c>
       <c r="R11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T11" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="U11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>265</v>
+        <v>474</v>
       </c>
       <c r="B12" t="s">
+        <v>475</v>
+      </c>
+      <c r="C12" t="s">
+        <v>476</v>
+      </c>
+      <c r="D12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" t="s">
+        <v>477</v>
+      </c>
+      <c r="G12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12">
+        <v>40</v>
+      </c>
+      <c r="I12" s="1">
+        <v>46297</v>
+      </c>
+      <c r="J12" s="2">
+        <v>6686.5</v>
+      </c>
+      <c r="K12" t="s">
+        <v>478</v>
+      </c>
+      <c r="L12" t="s">
+        <v>61</v>
+      </c>
+      <c r="M12" t="s">
+        <v>62</v>
+      </c>
+      <c r="O12" t="s">
+        <v>479</v>
+      </c>
+      <c r="P12" t="s">
+        <v>480</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>481</v>
+      </c>
+      <c r="R12" t="s">
+        <v>63</v>
+      </c>
+      <c r="S12" t="s">
+        <v>64</v>
+      </c>
+      <c r="T12" t="s">
         <v>266</v>
       </c>
-      <c r="C12" t="s">
-        <v>267</v>
-      </c>
-      <c r="D12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" t="s">
-        <v>82</v>
-      </c>
-      <c r="G12" t="s">
-        <v>60</v>
-      </c>
-      <c r="H12">
-        <v>754</v>
-      </c>
-      <c r="I12" s="1">
-        <v>46294</v>
-      </c>
-      <c r="J12" s="2">
-        <v>500</v>
-      </c>
-      <c r="K12" t="s">
-        <v>261</v>
-      </c>
-      <c r="L12" t="s">
-        <v>62</v>
-      </c>
-      <c r="M12" t="s">
-        <v>84</v>
-      </c>
-      <c r="O12" t="s">
-        <v>11</v>
-      </c>
-      <c r="P12" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>85</v>
-      </c>
-      <c r="R12" t="s">
-        <v>64</v>
-      </c>
-      <c r="S12" t="s">
-        <v>65</v>
-      </c>
-      <c r="T12" t="s">
-        <v>29</v>
-      </c>
       <c r="U12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>268</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s">
-        <v>269</v>
+        <v>162</v>
       </c>
       <c r="C13" t="s">
-        <v>270</v>
+        <v>163</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H13">
-        <v>752</v>
+        <v>12908</v>
       </c>
       <c r="I13" s="1">
-        <v>46294</v>
+        <v>46205</v>
       </c>
       <c r="J13" s="2">
-        <v>18357.18</v>
+        <v>643664.51</v>
       </c>
       <c r="K13" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
       <c r="L13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M13" t="s">
-        <v>273</v>
+        <v>128</v>
       </c>
       <c r="O13" t="s">
-        <v>274</v>
+        <v>9</v>
       </c>
       <c r="P13" t="s">
-        <v>275</v>
+        <v>233</v>
       </c>
       <c r="Q13" t="s">
-        <v>276</v>
+        <v>129</v>
       </c>
       <c r="R13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S13" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="T13" t="s">
-        <v>277</v>
+        <v>16</v>
       </c>
       <c r="U13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>278</v>
+        <v>548</v>
       </c>
       <c r="B14" t="s">
-        <v>279</v>
+        <v>548</v>
       </c>
       <c r="C14" t="s">
-        <v>280</v>
+        <v>549</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
-        <v>281</v>
+        <v>550</v>
       </c>
       <c r="G14" t="s">
-        <v>60</v>
-      </c>
-      <c r="H14">
-        <v>260283</v>
+        <v>59</v>
+      </c>
+      <c r="H14" t="s">
+        <v>551</v>
       </c>
       <c r="I14" s="1">
-        <v>46248</v>
+        <v>46273</v>
       </c>
       <c r="J14" s="2">
-        <v>2983.75</v>
+        <v>605254.43999999994</v>
       </c>
       <c r="K14" t="s">
-        <v>282</v>
+        <v>552</v>
       </c>
       <c r="L14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O14" t="s">
-        <v>283</v>
+        <v>9</v>
       </c>
       <c r="P14" t="s">
-        <v>284</v>
+        <v>233</v>
       </c>
       <c r="Q14" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="R14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T14" t="s">
-        <v>285</v>
+        <v>16</v>
       </c>
       <c r="U14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>478</v>
+        <v>389</v>
       </c>
       <c r="B15" t="s">
-        <v>479</v>
+        <v>390</v>
       </c>
       <c r="C15" t="s">
-        <v>480</v>
+        <v>391</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s">
-        <v>481</v>
+        <v>392</v>
       </c>
       <c r="G15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H15">
-        <v>61031</v>
+        <v>60201</v>
       </c>
       <c r="I15" s="1">
         <v>46296</v>
       </c>
       <c r="J15" s="2">
-        <v>976.95</v>
+        <v>587.86</v>
       </c>
       <c r="K15" t="s">
-        <v>473</v>
+        <v>347</v>
       </c>
       <c r="L15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M15" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="O15" t="s">
-        <v>474</v>
+        <v>348</v>
       </c>
       <c r="P15" t="s">
-        <v>475</v>
+        <v>349</v>
       </c>
       <c r="Q15" t="s">
-        <v>476</v>
+        <v>393</v>
       </c>
       <c r="R15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T15" t="s">
-        <v>477</v>
+        <v>351</v>
       </c>
       <c r="U15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>482</v>
+        <v>267</v>
       </c>
       <c r="B16" t="s">
-        <v>483</v>
+        <v>268</v>
       </c>
       <c r="C16" t="s">
-        <v>484</v>
+        <v>269</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s">
-        <v>485</v>
+        <v>270</v>
       </c>
       <c r="G16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H16">
-        <v>21027</v>
+        <v>751</v>
       </c>
       <c r="I16" s="1">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="J16" s="2">
-        <v>2918.92</v>
+        <v>5856.07</v>
       </c>
       <c r="K16" t="s">
-        <v>486</v>
+        <v>253</v>
       </c>
       <c r="L16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M16" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="O16" t="s">
-        <v>487</v>
+        <v>255</v>
       </c>
       <c r="P16" t="s">
-        <v>488</v>
+        <v>256</v>
       </c>
       <c r="Q16" t="s">
-        <v>489</v>
+        <v>257</v>
       </c>
       <c r="R16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T16" t="s">
-        <v>413</v>
+        <v>258</v>
       </c>
       <c r="U16" t="s">
-        <v>66</v>
+        <v>553</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>490</v>
+        <v>402</v>
       </c>
       <c r="B17" t="s">
-        <v>491</v>
+        <v>403</v>
       </c>
       <c r="C17" t="s">
-        <v>492</v>
+        <v>404</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" t="s">
-        <v>493</v>
+        <v>405</v>
       </c>
       <c r="G17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H17">
-        <v>22573</v>
+        <v>2802</v>
       </c>
       <c r="I17" s="1">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="J17" s="2">
-        <v>950</v>
+        <v>5822.99</v>
       </c>
       <c r="K17" t="s">
-        <v>494</v>
+        <v>406</v>
       </c>
       <c r="L17" t="s">
-        <v>62</v>
+        <v>61</v>
+      </c>
+      <c r="M17" t="s">
+        <v>407</v>
       </c>
       <c r="O17" t="s">
-        <v>495</v>
+        <v>408</v>
       </c>
       <c r="P17" t="s">
-        <v>496</v>
+        <v>409</v>
       </c>
       <c r="Q17" t="s">
-        <v>497</v>
+        <v>410</v>
       </c>
       <c r="R17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T17" t="s">
-        <v>477</v>
+        <v>20</v>
       </c>
       <c r="U17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>554</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>555</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>556</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" t="s">
-        <v>78</v>
+        <v>557</v>
       </c>
       <c r="G18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H18">
-        <v>157417</v>
+        <v>10993</v>
       </c>
       <c r="I18" s="1">
-        <v>46283</v>
+        <v>46300</v>
       </c>
       <c r="J18" s="2">
-        <v>199</v>
+        <v>5629.27</v>
       </c>
       <c r="K18" t="s">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="L18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M18" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="O18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P18" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="Q18" t="s">
-        <v>81</v>
+        <v>558</v>
       </c>
       <c r="R18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T18" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="U18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" t="s">
         <v>86</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>87</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" t="s">
         <v>88</v>
       </c>
-      <c r="D19" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19" t="s">
-        <v>89</v>
-      </c>
       <c r="G19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H19">
         <v>143685</v>
@@ -3801,1656 +3741,1635 @@
         <v>560.28</v>
       </c>
       <c r="K19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O19" t="s">
         <v>13</v>
       </c>
       <c r="P19" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="Q19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T19" t="s">
         <v>1</v>
       </c>
       <c r="U19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>290</v>
+        <v>188</v>
       </c>
       <c r="B20" t="s">
-        <v>291</v>
+        <v>189</v>
       </c>
       <c r="C20" t="s">
-        <v>292</v>
+        <v>190</v>
       </c>
       <c r="D20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E20" t="s">
-        <v>293</v>
+        <v>191</v>
       </c>
       <c r="G20" t="s">
-        <v>60</v>
-      </c>
-      <c r="H20" t="s">
-        <v>294</v>
+        <v>59</v>
+      </c>
+      <c r="H20">
+        <v>203</v>
       </c>
       <c r="I20" s="1">
-        <v>46294</v>
+        <v>46189</v>
       </c>
       <c r="J20" s="2">
-        <v>341619.74</v>
+        <v>5280</v>
       </c>
       <c r="K20" t="s">
-        <v>295</v>
+        <v>192</v>
       </c>
       <c r="L20" t="s">
-        <v>62</v>
+        <v>61</v>
+      </c>
+      <c r="M20" t="s">
+        <v>83</v>
       </c>
       <c r="O20" t="s">
-        <v>274</v>
+        <v>7</v>
       </c>
       <c r="P20" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
       <c r="Q20" t="s">
-        <v>276</v>
+        <v>193</v>
       </c>
       <c r="R20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T20" t="s">
-        <v>277</v>
+        <v>6</v>
       </c>
       <c r="U20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>286</v>
+        <v>559</v>
       </c>
       <c r="B21" t="s">
-        <v>287</v>
+        <v>560</v>
       </c>
       <c r="C21" t="s">
-        <v>288</v>
+        <v>561</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E21" t="s">
-        <v>289</v>
+        <v>562</v>
       </c>
       <c r="G21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H21">
-        <v>751</v>
+        <v>81453</v>
       </c>
       <c r="I21" s="1">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="J21" s="2">
-        <v>5856.07</v>
+        <v>528.6</v>
       </c>
       <c r="K21" t="s">
-        <v>272</v>
+        <v>563</v>
       </c>
       <c r="L21" t="s">
-        <v>62</v>
-      </c>
-      <c r="M21" t="s">
-        <v>273</v>
+        <v>61</v>
       </c>
       <c r="O21" t="s">
-        <v>274</v>
+        <v>564</v>
       </c>
       <c r="P21" t="s">
-        <v>275</v>
+        <v>565</v>
       </c>
       <c r="Q21" t="s">
-        <v>276</v>
+        <v>566</v>
       </c>
       <c r="R21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T21" t="s">
-        <v>277</v>
+        <v>351</v>
       </c>
       <c r="U21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>353</v>
+        <v>567</v>
       </c>
       <c r="B22" t="s">
-        <v>354</v>
+        <v>568</v>
       </c>
       <c r="C22" t="s">
-        <v>355</v>
+        <v>569</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E22" t="s">
-        <v>82</v>
+        <v>562</v>
       </c>
       <c r="G22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H22">
-        <v>774</v>
+        <v>81451</v>
       </c>
       <c r="I22" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="J22" s="2">
-        <v>500</v>
+        <v>528.6</v>
       </c>
       <c r="K22" t="s">
-        <v>261</v>
+        <v>563</v>
       </c>
       <c r="L22" t="s">
-        <v>62</v>
-      </c>
-      <c r="M22" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="O22" t="s">
-        <v>11</v>
+        <v>564</v>
       </c>
       <c r="P22" t="s">
-        <v>248</v>
+        <v>565</v>
       </c>
       <c r="Q22" t="s">
-        <v>85</v>
+        <v>570</v>
       </c>
       <c r="R22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T22" t="s">
-        <v>29</v>
+        <v>351</v>
       </c>
       <c r="U22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>356</v>
+        <v>105</v>
       </c>
       <c r="B23" t="s">
-        <v>357</v>
+        <v>106</v>
       </c>
       <c r="C23" t="s">
-        <v>358</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="G23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H23">
-        <v>773</v>
+        <v>373798</v>
       </c>
       <c r="I23" s="1">
-        <v>46295</v>
+        <v>46195</v>
       </c>
       <c r="J23" s="2">
-        <v>500</v>
+        <v>5136.25</v>
       </c>
       <c r="K23" t="s">
-        <v>261</v>
+        <v>109</v>
       </c>
       <c r="L23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M23" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="O23" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P23" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="Q23" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="R23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T23" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="U23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>359</v>
+        <v>493</v>
       </c>
       <c r="B24" t="s">
-        <v>360</v>
+        <v>494</v>
       </c>
       <c r="C24" t="s">
-        <v>361</v>
+        <v>495</v>
       </c>
       <c r="D24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" t="s">
-        <v>82</v>
+        <v>496</v>
       </c>
       <c r="G24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H24">
-        <v>772</v>
+        <v>2042</v>
       </c>
       <c r="I24" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="J24" s="2">
-        <v>500</v>
+        <v>4944.6000000000004</v>
       </c>
       <c r="K24" t="s">
-        <v>261</v>
+        <v>497</v>
       </c>
       <c r="L24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M24" t="s">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="O24" t="s">
-        <v>11</v>
+        <v>421</v>
       </c>
       <c r="P24" t="s">
-        <v>248</v>
+        <v>422</v>
       </c>
       <c r="Q24" t="s">
-        <v>85</v>
+        <v>498</v>
       </c>
       <c r="R24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T24" t="s">
-        <v>29</v>
+        <v>351</v>
       </c>
       <c r="U24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>498</v>
+        <v>372</v>
       </c>
       <c r="B25" t="s">
-        <v>499</v>
+        <v>373</v>
       </c>
       <c r="C25" t="s">
-        <v>500</v>
+        <v>374</v>
       </c>
       <c r="D25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" t="s">
-        <v>501</v>
+        <v>375</v>
       </c>
       <c r="G25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H25">
-        <v>3243</v>
+        <v>882</v>
       </c>
       <c r="I25" s="1">
         <v>46296</v>
       </c>
       <c r="J25" s="2">
-        <v>2650</v>
+        <v>492.26</v>
       </c>
       <c r="K25" t="s">
-        <v>502</v>
+        <v>376</v>
       </c>
       <c r="L25" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M25" t="s">
-        <v>503</v>
+        <v>377</v>
       </c>
       <c r="O25" t="s">
-        <v>504</v>
+        <v>378</v>
       </c>
       <c r="P25" t="s">
-        <v>505</v>
+        <v>379</v>
       </c>
       <c r="Q25" t="s">
-        <v>506</v>
+        <v>380</v>
       </c>
       <c r="R25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S25" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="T25" t="s">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="U25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>507</v>
+        <v>343</v>
       </c>
       <c r="B26" t="s">
-        <v>508</v>
+        <v>344</v>
       </c>
       <c r="C26" t="s">
-        <v>509</v>
+        <v>345</v>
       </c>
       <c r="D26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" t="s">
-        <v>510</v>
+        <v>346</v>
       </c>
       <c r="G26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H26">
-        <v>882</v>
+        <v>61032</v>
       </c>
       <c r="I26" s="1">
         <v>46296</v>
       </c>
       <c r="J26" s="2">
-        <v>492.26</v>
+        <v>484.87</v>
       </c>
       <c r="K26" t="s">
-        <v>511</v>
+        <v>347</v>
       </c>
       <c r="L26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M26" t="s">
-        <v>512</v>
+        <v>160</v>
       </c>
       <c r="O26" t="s">
-        <v>513</v>
+        <v>348</v>
       </c>
       <c r="P26" t="s">
-        <v>514</v>
+        <v>349</v>
       </c>
       <c r="Q26" t="s">
-        <v>515</v>
+        <v>350</v>
       </c>
       <c r="R26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T26" t="s">
-        <v>285</v>
+        <v>351</v>
       </c>
       <c r="U26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>516</v>
+        <v>571</v>
       </c>
       <c r="B27" t="s">
-        <v>517</v>
+        <v>572</v>
       </c>
       <c r="C27" t="s">
-        <v>518</v>
+        <v>573</v>
       </c>
       <c r="D27" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E27" t="s">
-        <v>519</v>
+        <v>574</v>
       </c>
       <c r="G27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H27">
-        <v>16607</v>
+        <v>4585</v>
       </c>
       <c r="I27" s="1">
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="J27" s="2">
-        <v>2965.55</v>
+        <v>44444.480000000003</v>
       </c>
       <c r="K27" t="s">
-        <v>520</v>
+        <v>575</v>
       </c>
       <c r="L27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M27" t="s">
-        <v>84</v>
+        <v>576</v>
       </c>
       <c r="O27" t="s">
-        <v>521</v>
+        <v>577</v>
       </c>
       <c r="P27" t="s">
-        <v>522</v>
+        <v>578</v>
       </c>
       <c r="Q27" t="s">
-        <v>523</v>
+        <v>579</v>
       </c>
       <c r="R27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T27" t="s">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="U27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>524</v>
+        <v>580</v>
       </c>
       <c r="B28" t="s">
-        <v>525</v>
+        <v>581</v>
       </c>
       <c r="C28" t="s">
-        <v>526</v>
+        <v>582</v>
       </c>
       <c r="D28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E28" t="s">
-        <v>527</v>
+        <v>583</v>
       </c>
       <c r="G28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H28">
-        <v>60201</v>
+        <v>61964</v>
       </c>
       <c r="I28" s="1">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="J28" s="2">
-        <v>587.86</v>
+        <v>44.9</v>
       </c>
       <c r="K28" t="s">
-        <v>473</v>
+        <v>347</v>
       </c>
       <c r="L28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M28" t="s">
-        <v>162</v>
+        <v>584</v>
       </c>
       <c r="O28" t="s">
-        <v>474</v>
+        <v>348</v>
       </c>
       <c r="P28" t="s">
-        <v>475</v>
+        <v>349</v>
       </c>
       <c r="Q28" t="s">
-        <v>528</v>
+        <v>350</v>
       </c>
       <c r="R28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T28" t="s">
-        <v>477</v>
+        <v>351</v>
       </c>
       <c r="U28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>529</v>
+        <v>585</v>
       </c>
       <c r="B29" t="s">
-        <v>530</v>
+        <v>586</v>
       </c>
       <c r="C29" t="s">
-        <v>531</v>
+        <v>587</v>
       </c>
       <c r="D29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E29" t="s">
-        <v>532</v>
+        <v>588</v>
       </c>
       <c r="G29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H29">
-        <v>31567</v>
+        <v>5373</v>
       </c>
       <c r="I29" s="1">
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="J29" s="2">
-        <v>6144</v>
+        <v>406.15</v>
       </c>
       <c r="K29" t="s">
-        <v>533</v>
+        <v>589</v>
       </c>
       <c r="L29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O29" t="s">
-        <v>534</v>
+        <v>590</v>
       </c>
       <c r="P29" t="s">
-        <v>535</v>
+        <v>591</v>
       </c>
       <c r="Q29" t="s">
-        <v>536</v>
+        <v>592</v>
       </c>
       <c r="R29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T29" t="s">
-        <v>413</v>
+        <v>266</v>
       </c>
       <c r="U29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>537</v>
+        <v>175</v>
       </c>
       <c r="B30" t="s">
-        <v>538</v>
+        <v>176</v>
       </c>
       <c r="C30" t="s">
-        <v>539</v>
+        <v>177</v>
       </c>
       <c r="D30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E30" t="s">
-        <v>540</v>
+        <v>178</v>
       </c>
       <c r="G30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H30">
-        <v>2802</v>
+        <v>10760</v>
       </c>
       <c r="I30" s="1">
-        <v>46296</v>
+        <v>46276</v>
       </c>
       <c r="J30">
-        <v>5822.99</v>
+        <v>3770.93</v>
       </c>
       <c r="K30" t="s">
-        <v>541</v>
+        <v>179</v>
       </c>
       <c r="L30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M30" t="s">
-        <v>542</v>
+        <v>180</v>
       </c>
       <c r="O30" t="s">
-        <v>543</v>
+        <v>33</v>
       </c>
       <c r="P30" t="s">
-        <v>544</v>
+        <v>238</v>
       </c>
       <c r="Q30" t="s">
-        <v>545</v>
+        <v>181</v>
       </c>
       <c r="R30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T30" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>546</v>
+        <v>149</v>
       </c>
       <c r="B31" t="s">
-        <v>547</v>
+        <v>150</v>
       </c>
       <c r="C31" t="s">
-        <v>548</v>
+        <v>151</v>
       </c>
       <c r="D31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E31" t="s">
-        <v>549</v>
+        <v>152</v>
       </c>
       <c r="G31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H31">
-        <v>2800</v>
+        <v>237</v>
       </c>
       <c r="I31" s="1">
-        <v>46296</v>
+        <v>46282</v>
       </c>
       <c r="J31">
-        <v>5400</v>
-      </c>
-      <c r="K31" t="s">
-        <v>541</v>
+        <v>35467.589999999997</v>
+      </c>
+      <c r="K31">
+        <v>51990695000137</v>
       </c>
       <c r="L31" t="s">
-        <v>62</v>
-      </c>
-      <c r="M31" t="s">
-        <v>542</v>
+        <v>61</v>
       </c>
       <c r="O31" t="s">
-        <v>543</v>
+        <v>36</v>
       </c>
       <c r="P31" t="s">
-        <v>544</v>
+        <v>239</v>
       </c>
       <c r="Q31" t="s">
-        <v>550</v>
+        <v>153</v>
       </c>
       <c r="R31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T31" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="U31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>551</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s">
-        <v>552</v>
+        <v>272</v>
       </c>
       <c r="C32" t="s">
-        <v>553</v>
+        <v>273</v>
       </c>
       <c r="D32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E32" t="s">
-        <v>554</v>
+        <v>274</v>
       </c>
       <c r="G32" t="s">
-        <v>60</v>
-      </c>
-      <c r="H32">
-        <v>2041</v>
+        <v>59</v>
+      </c>
+      <c r="H32" t="s">
+        <v>275</v>
       </c>
       <c r="I32" s="1">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="J32" s="2">
-        <v>12769.32</v>
+        <v>341619.74</v>
       </c>
       <c r="K32" t="s">
-        <v>555</v>
+        <v>276</v>
       </c>
       <c r="L32" t="s">
-        <v>62</v>
-      </c>
-      <c r="M32" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
       <c r="O32" t="s">
-        <v>556</v>
+        <v>255</v>
       </c>
       <c r="P32" t="s">
-        <v>557</v>
+        <v>256</v>
       </c>
       <c r="Q32" t="s">
-        <v>558</v>
+        <v>257</v>
       </c>
       <c r="R32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T32" t="s">
-        <v>477</v>
+        <v>258</v>
       </c>
       <c r="U32" t="s">
-        <v>66</v>
+        <v>593</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>559</v>
+        <v>182</v>
       </c>
       <c r="B33" t="s">
-        <v>560</v>
+        <v>183</v>
       </c>
       <c r="C33" t="s">
-        <v>561</v>
+        <v>184</v>
       </c>
       <c r="D33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E33" t="s">
-        <v>562</v>
+        <v>185</v>
       </c>
       <c r="G33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H33">
-        <v>10858</v>
+        <v>13020</v>
       </c>
       <c r="I33" s="1">
-        <v>46296</v>
+        <v>46268</v>
       </c>
       <c r="J33" s="2">
-        <v>24302</v>
+        <v>330986.02</v>
       </c>
       <c r="K33" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="L33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M33" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="O33" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="P33" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="Q33" t="s">
-        <v>563</v>
+        <v>129</v>
       </c>
       <c r="R33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T33" t="s">
-        <v>564</v>
+        <v>16</v>
       </c>
       <c r="U33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>565</v>
+        <v>594</v>
       </c>
       <c r="B34" t="s">
-        <v>566</v>
+        <v>595</v>
       </c>
       <c r="C34" t="s">
-        <v>567</v>
+        <v>596</v>
       </c>
       <c r="D34" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E34" t="s">
-        <v>568</v>
+        <v>597</v>
       </c>
       <c r="G34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H34">
-        <v>1246</v>
+        <v>1261</v>
       </c>
       <c r="I34" s="1">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="J34" s="2">
-        <v>41270</v>
+        <v>308.75</v>
       </c>
       <c r="K34" t="s">
-        <v>569</v>
+        <v>598</v>
       </c>
       <c r="L34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M34" t="s">
-        <v>104</v>
+        <v>599</v>
       </c>
       <c r="O34" t="s">
-        <v>570</v>
+        <v>600</v>
       </c>
       <c r="P34" t="s">
-        <v>571</v>
+        <v>601</v>
       </c>
       <c r="Q34" t="s">
-        <v>572</v>
+        <v>602</v>
       </c>
       <c r="R34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T34" t="s">
-        <v>413</v>
+        <v>351</v>
       </c>
       <c r="U34" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>573</v>
+        <v>259</v>
       </c>
       <c r="B35" t="s">
-        <v>574</v>
+        <v>260</v>
       </c>
       <c r="C35" t="s">
-        <v>575</v>
+        <v>261</v>
       </c>
       <c r="D35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E35" t="s">
-        <v>576</v>
+        <v>262</v>
       </c>
       <c r="G35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H35">
-        <v>1232</v>
+        <v>260283</v>
       </c>
       <c r="I35" s="1">
-        <v>46296</v>
+        <v>46248</v>
       </c>
       <c r="J35">
-        <v>6000</v>
+        <v>2983.75</v>
       </c>
       <c r="K35" t="s">
-        <v>569</v>
+        <v>263</v>
       </c>
       <c r="L35" t="s">
-        <v>62</v>
-      </c>
-      <c r="M35" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="O35" t="s">
-        <v>570</v>
+        <v>264</v>
       </c>
       <c r="P35" t="s">
-        <v>571</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>572</v>
+        <v>265</v>
       </c>
       <c r="R35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S35" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="T35" t="s">
-        <v>413</v>
+        <v>16</v>
       </c>
       <c r="U35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>577</v>
+        <v>381</v>
       </c>
       <c r="B36" t="s">
-        <v>578</v>
+        <v>382</v>
       </c>
       <c r="C36" t="s">
-        <v>579</v>
+        <v>383</v>
       </c>
       <c r="D36" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E36" t="s">
-        <v>580</v>
+        <v>384</v>
       </c>
       <c r="G36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H36">
-        <v>39807</v>
+        <v>16607</v>
       </c>
       <c r="I36" s="1">
         <v>46296</v>
       </c>
       <c r="J36">
-        <v>1575</v>
+        <v>2965.55</v>
       </c>
       <c r="K36" t="s">
-        <v>581</v>
+        <v>385</v>
       </c>
       <c r="L36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M36" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>582</v>
+        <v>386</v>
       </c>
       <c r="P36" t="s">
-        <v>583</v>
+        <v>387</v>
       </c>
       <c r="Q36" t="s">
-        <v>584</v>
+        <v>388</v>
       </c>
       <c r="R36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T36" t="s">
-        <v>314</v>
+        <v>266</v>
       </c>
       <c r="U36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>585</v>
+        <v>533</v>
       </c>
       <c r="B37" t="s">
-        <v>586</v>
+        <v>534</v>
       </c>
       <c r="C37" t="s">
-        <v>587</v>
+        <v>535</v>
       </c>
       <c r="D37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E37" t="s">
-        <v>588</v>
+        <v>536</v>
       </c>
       <c r="G37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="I37" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="J37">
-        <v>40530</v>
+        <v>2958.63</v>
       </c>
       <c r="K37" t="s">
-        <v>589</v>
+        <v>537</v>
       </c>
       <c r="L37" t="s">
+        <v>61</v>
+      </c>
+      <c r="M37" t="s">
         <v>62</v>
       </c>
-      <c r="M37" t="s">
-        <v>542</v>
-      </c>
       <c r="O37" s="3" t="s">
-        <v>590</v>
+        <v>479</v>
       </c>
       <c r="P37" t="s">
-        <v>591</v>
+        <v>480</v>
       </c>
       <c r="Q37" t="s">
-        <v>592</v>
+        <v>538</v>
       </c>
       <c r="R37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T37" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="U37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>593</v>
+        <v>356</v>
       </c>
       <c r="B38" t="s">
-        <v>594</v>
+        <v>357</v>
       </c>
       <c r="C38" t="s">
-        <v>595</v>
+        <v>358</v>
       </c>
       <c r="D38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E38" t="s">
-        <v>596</v>
+        <v>359</v>
       </c>
       <c r="G38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H38">
-        <v>2307</v>
+        <v>21027</v>
       </c>
       <c r="I38" s="1">
         <v>46296</v>
       </c>
       <c r="J38">
-        <v>17094</v>
+        <v>2918.92</v>
       </c>
       <c r="K38" t="s">
-        <v>597</v>
+        <v>360</v>
       </c>
       <c r="L38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M38" t="s">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="O38" t="s">
-        <v>598</v>
+        <v>361</v>
       </c>
       <c r="P38" t="s">
-        <v>599</v>
+        <v>362</v>
       </c>
       <c r="Q38" t="s">
-        <v>600</v>
+        <v>363</v>
       </c>
       <c r="R38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T38" t="s">
-        <v>31</v>
+        <v>328</v>
       </c>
       <c r="U38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>601</v>
+        <v>299</v>
       </c>
       <c r="B39" t="s">
-        <v>602</v>
+        <v>300</v>
       </c>
       <c r="C39" t="s">
+        <v>301</v>
+      </c>
+      <c r="D39" t="s">
+        <v>58</v>
+      </c>
+      <c r="E39" t="s">
+        <v>302</v>
+      </c>
+      <c r="G39" t="s">
+        <v>59</v>
+      </c>
+      <c r="H39">
+        <v>1006</v>
+      </c>
+      <c r="I39" s="1">
+        <v>46296</v>
+      </c>
+      <c r="J39">
+        <v>28450.799999999999</v>
+      </c>
+      <c r="K39" t="s">
+        <v>296</v>
+      </c>
+      <c r="L39" t="s">
+        <v>61</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="P39" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>303</v>
+      </c>
+      <c r="R39" t="s">
+        <v>63</v>
+      </c>
+      <c r="S39" t="s">
+        <v>117</v>
+      </c>
+      <c r="T39" t="s">
         <v>603</v>
       </c>
-      <c r="D39" t="s">
-        <v>59</v>
-      </c>
-      <c r="E39" t="s">
-        <v>604</v>
-      </c>
-      <c r="G39" t="s">
-        <v>60</v>
-      </c>
-      <c r="H39">
-        <v>2145</v>
-      </c>
-      <c r="I39" s="1">
-        <v>46297</v>
-      </c>
-      <c r="J39">
-        <v>2270</v>
-      </c>
-      <c r="K39" t="s">
-        <v>605</v>
-      </c>
-      <c r="L39" t="s">
-        <v>62</v>
-      </c>
-      <c r="M39" t="s">
-        <v>606</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="P39" t="s">
-        <v>608</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>609</v>
-      </c>
-      <c r="R39" t="s">
-        <v>64</v>
-      </c>
-      <c r="S39" t="s">
-        <v>65</v>
-      </c>
-      <c r="T39" t="s">
-        <v>447</v>
-      </c>
       <c r="U39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="B40" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="C40" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="D40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E40" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="G40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H40">
-        <v>39808</v>
+        <v>4593</v>
       </c>
       <c r="I40" s="1">
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="J40">
-        <v>1575</v>
+        <v>2775.88</v>
       </c>
       <c r="K40" t="s">
-        <v>614</v>
+        <v>575</v>
       </c>
       <c r="L40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M40" t="s">
-        <v>73</v>
+        <v>576</v>
       </c>
       <c r="O40" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="P40" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="Q40" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="R40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T40" t="s">
-        <v>314</v>
+        <v>266</v>
       </c>
       <c r="U40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>616</v>
+        <v>466</v>
       </c>
       <c r="B41" t="s">
-        <v>617</v>
+        <v>467</v>
       </c>
       <c r="C41" t="s">
-        <v>618</v>
+        <v>468</v>
       </c>
       <c r="D41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E41" t="s">
-        <v>619</v>
+        <v>469</v>
       </c>
       <c r="G41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H41">
-        <v>21395</v>
+        <v>131</v>
       </c>
       <c r="I41" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="J41" s="2">
-        <v>2800</v>
+        <v>26584.71</v>
       </c>
       <c r="K41" t="s">
-        <v>620</v>
+        <v>470</v>
       </c>
       <c r="L41" t="s">
-        <v>62</v>
-      </c>
-      <c r="M41" t="s">
-        <v>332</v>
+        <v>61</v>
       </c>
       <c r="O41" t="s">
-        <v>621</v>
+        <v>471</v>
       </c>
       <c r="P41" t="s">
-        <v>622</v>
+        <v>472</v>
       </c>
       <c r="Q41" t="s">
-        <v>623</v>
+        <v>473</v>
       </c>
       <c r="R41" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T41" t="s">
-        <v>3</v>
+        <v>266</v>
       </c>
       <c r="U41" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="B42" t="s">
-        <v>625</v>
+        <v>610</v>
       </c>
       <c r="C42" t="s">
-        <v>626</v>
+        <v>611</v>
       </c>
       <c r="D42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E42" t="s">
-        <v>627</v>
+        <v>612</v>
       </c>
       <c r="G42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H42">
-        <v>131</v>
+        <v>104291</v>
       </c>
       <c r="I42" s="1">
         <v>46297</v>
       </c>
       <c r="J42" s="2">
-        <v>26584.71</v>
+        <v>24858.86</v>
       </c>
       <c r="K42" t="s">
-        <v>628</v>
+        <v>613</v>
       </c>
       <c r="L42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O42" t="s">
-        <v>629</v>
+        <v>490</v>
       </c>
       <c r="P42" t="s">
-        <v>630</v>
+        <v>491</v>
       </c>
       <c r="Q42" t="s">
-        <v>631</v>
+        <v>492</v>
       </c>
       <c r="R42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S42" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T42" t="s">
-        <v>285</v>
+        <v>342</v>
       </c>
       <c r="U42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>632</v>
+        <v>304</v>
       </c>
       <c r="B43" t="s">
-        <v>633</v>
+        <v>305</v>
       </c>
       <c r="C43" t="s">
-        <v>634</v>
+        <v>306</v>
       </c>
       <c r="D43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E43" t="s">
-        <v>635</v>
+        <v>307</v>
       </c>
       <c r="G43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H43">
-        <v>53916126</v>
+        <v>750</v>
       </c>
       <c r="I43" s="1">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="J43" s="2">
-        <v>17069.990000000002</v>
+        <v>22920.95</v>
       </c>
       <c r="K43" t="s">
-        <v>636</v>
+        <v>253</v>
       </c>
       <c r="L43" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M43" t="s">
-        <v>182</v>
+        <v>254</v>
       </c>
       <c r="O43" t="s">
-        <v>637</v>
+        <v>255</v>
       </c>
       <c r="P43" t="s">
-        <v>638</v>
+        <v>256</v>
       </c>
       <c r="Q43" t="s">
-        <v>639</v>
+        <v>257</v>
       </c>
       <c r="R43" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T43" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="U43" t="s">
-        <v>66</v>
+        <v>553</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>640</v>
+        <v>482</v>
       </c>
       <c r="B44" t="s">
-        <v>641</v>
+        <v>483</v>
       </c>
       <c r="C44" t="s">
-        <v>642</v>
+        <v>484</v>
       </c>
       <c r="D44" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E44" t="s">
-        <v>643</v>
+        <v>485</v>
       </c>
       <c r="G44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H44">
-        <v>40</v>
+        <v>176</v>
       </c>
       <c r="I44" s="1">
-        <v>46297</v>
+        <v>46273</v>
       </c>
       <c r="J44" s="2">
-        <v>6686.5</v>
+        <v>22865.14</v>
       </c>
       <c r="K44" t="s">
-        <v>644</v>
+        <v>486</v>
       </c>
       <c r="L44" t="s">
+        <v>61</v>
+      </c>
+      <c r="M44" t="s">
         <v>62</v>
       </c>
-      <c r="M44" t="s">
-        <v>63</v>
-      </c>
       <c r="O44" t="s">
-        <v>645</v>
+        <v>487</v>
       </c>
       <c r="P44" t="s">
-        <v>646</v>
+        <v>488</v>
       </c>
       <c r="Q44" t="s">
-        <v>647</v>
+        <v>489</v>
       </c>
       <c r="R44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S44" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T44" t="s">
-        <v>285</v>
+        <v>12</v>
       </c>
       <c r="U44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>92</v>
+        <v>209</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>210</v>
       </c>
       <c r="C45" t="s">
-        <v>94</v>
+        <v>211</v>
       </c>
       <c r="D45" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E45" t="s">
-        <v>95</v>
+        <v>212</v>
       </c>
       <c r="G45" t="s">
+        <v>59</v>
+      </c>
+      <c r="H45">
+        <v>26491</v>
+      </c>
+      <c r="I45" s="1">
+        <v>46267</v>
+      </c>
+      <c r="J45" s="2">
+        <v>22510.52</v>
+      </c>
+      <c r="K45" t="s">
         <v>60</v>
       </c>
-      <c r="H45">
-        <v>21941</v>
-      </c>
-      <c r="I45" s="1">
-        <v>46247</v>
-      </c>
-      <c r="J45" s="2">
-        <v>7881.75</v>
-      </c>
-      <c r="K45" t="s">
-        <v>96</v>
-      </c>
       <c r="L45" t="s">
+        <v>61</v>
+      </c>
+      <c r="M45" t="s">
         <v>62</v>
       </c>
-      <c r="M45" t="s">
-        <v>97</v>
-      </c>
       <c r="O45" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="P45" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="Q45" t="s">
-        <v>98</v>
+        <v>213</v>
       </c>
       <c r="R45" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T45" t="s">
-        <v>285</v>
+        <v>12</v>
       </c>
       <c r="U45" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>106</v>
+        <v>614</v>
       </c>
       <c r="B46" t="s">
-        <v>107</v>
+        <v>615</v>
       </c>
       <c r="C46" t="s">
-        <v>108</v>
+        <v>616</v>
       </c>
       <c r="D46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E46" t="s">
-        <v>109</v>
+        <v>617</v>
       </c>
       <c r="G46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H46">
-        <v>373798</v>
+        <v>18</v>
       </c>
       <c r="I46" s="1">
-        <v>46195</v>
+        <v>46300</v>
       </c>
       <c r="J46">
-        <v>5136.25</v>
+        <v>22264.6</v>
       </c>
       <c r="K46" t="s">
-        <v>110</v>
+        <v>618</v>
       </c>
       <c r="L46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M46" t="s">
-        <v>67</v>
+        <v>619</v>
       </c>
       <c r="O46" t="s">
-        <v>2</v>
+        <v>620</v>
       </c>
       <c r="P46" t="s">
-        <v>245</v>
+        <v>621</v>
       </c>
       <c r="Q46" t="s">
-        <v>111</v>
+        <v>622</v>
       </c>
       <c r="R46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S46" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T46" t="s">
-        <v>8</v>
+        <v>278</v>
       </c>
       <c r="U46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B47" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C47" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D47" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E47" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H47">
-        <v>97322</v>
+        <v>156553</v>
       </c>
       <c r="I47" s="1">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="J47">
-        <v>1678.6</v>
+        <v>1928</v>
       </c>
       <c r="K47" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="L47" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O47" t="s">
         <v>4</v>
@@ -5459,3582 +5378,3237 @@
         <v>5</v>
       </c>
       <c r="Q47" t="s">
+        <v>116</v>
+      </c>
+      <c r="R47" t="s">
+        <v>63</v>
+      </c>
+      <c r="S47" t="s">
         <v>117</v>
-      </c>
-      <c r="R47" t="s">
-        <v>64</v>
-      </c>
-      <c r="S47" t="s">
-        <v>118</v>
       </c>
       <c r="T47" t="s">
         <v>3</v>
       </c>
       <c r="U47" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>119</v>
+        <v>519</v>
       </c>
       <c r="B48" t="s">
-        <v>120</v>
+        <v>520</v>
       </c>
       <c r="C48" t="s">
-        <v>121</v>
+        <v>521</v>
       </c>
       <c r="D48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E48" t="s">
-        <v>122</v>
+        <v>522</v>
       </c>
       <c r="G48" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H48">
-        <v>156553</v>
+        <v>13018</v>
       </c>
       <c r="I48" s="1">
-        <v>46174</v>
+        <v>46298</v>
       </c>
       <c r="J48">
-        <v>1928</v>
+        <v>18778.25</v>
       </c>
       <c r="K48" t="s">
-        <v>123</v>
+        <v>523</v>
       </c>
       <c r="L48" t="s">
-        <v>62</v>
+        <v>61</v>
+      </c>
+      <c r="M48" t="s">
+        <v>160</v>
       </c>
       <c r="O48" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P48" t="s">
-        <v>5</v>
+        <v>233</v>
       </c>
       <c r="Q48" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="R48" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S48" t="s">
-        <v>118</v>
+        <v>64</v>
       </c>
       <c r="T48" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="U48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>124</v>
+        <v>249</v>
       </c>
       <c r="B49" t="s">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="C49" t="s">
-        <v>126</v>
+        <v>251</v>
       </c>
       <c r="D49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E49" t="s">
-        <v>127</v>
+        <v>252</v>
       </c>
       <c r="G49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H49">
-        <v>12958</v>
+        <v>752</v>
       </c>
       <c r="I49" s="1">
-        <v>46244</v>
+        <v>46294</v>
       </c>
       <c r="J49" s="2">
-        <v>746101.35</v>
+        <v>18357.18</v>
       </c>
       <c r="K49" t="s">
-        <v>128</v>
+        <v>253</v>
       </c>
       <c r="L49" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M49" t="s">
-        <v>129</v>
+        <v>254</v>
       </c>
       <c r="O49" t="s">
-        <v>9</v>
+        <v>255</v>
       </c>
       <c r="P49" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="Q49" t="s">
-        <v>130</v>
+        <v>257</v>
       </c>
       <c r="R49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S49" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T49" t="s">
-        <v>16</v>
+        <v>258</v>
       </c>
       <c r="U49" t="s">
-        <v>66</v>
+        <v>553</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>296</v>
+        <v>623</v>
       </c>
       <c r="B50" t="s">
-        <v>297</v>
+        <v>624</v>
       </c>
       <c r="C50" t="s">
-        <v>298</v>
+        <v>625</v>
       </c>
       <c r="D50" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E50" t="s">
-        <v>299</v>
+        <v>626</v>
       </c>
       <c r="G50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H50">
-        <v>756</v>
+        <v>14735</v>
       </c>
       <c r="I50" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="J50">
-        <v>41919.46</v>
+        <v>1737.06</v>
       </c>
       <c r="K50" t="s">
-        <v>300</v>
+        <v>627</v>
       </c>
       <c r="L50" t="s">
-        <v>62</v>
+        <v>61</v>
+      </c>
+      <c r="M50" t="s">
+        <v>103</v>
       </c>
       <c r="O50" t="s">
-        <v>301</v>
+        <v>628</v>
       </c>
       <c r="P50" t="s">
-        <v>302</v>
+        <v>629</v>
       </c>
       <c r="Q50" t="s">
-        <v>303</v>
+        <v>630</v>
       </c>
       <c r="R50" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S50" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="T50" t="s">
-        <v>304</v>
+        <v>23</v>
       </c>
       <c r="U50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>305</v>
+        <v>111</v>
       </c>
       <c r="B51" t="s">
-        <v>306</v>
+        <v>112</v>
       </c>
       <c r="C51" t="s">
-        <v>307</v>
+        <v>113</v>
       </c>
       <c r="D51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E51" t="s">
-        <v>308</v>
+        <v>114</v>
       </c>
       <c r="G51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H51">
-        <v>571</v>
+        <v>97322</v>
       </c>
       <c r="I51" s="1">
-        <v>46296</v>
+        <v>46143</v>
       </c>
       <c r="J51" s="2">
-        <v>3628</v>
+        <v>1678.6</v>
       </c>
       <c r="K51" t="s">
-        <v>309</v>
+        <v>115</v>
       </c>
       <c r="L51" t="s">
-        <v>62</v>
-      </c>
-      <c r="M51" t="s">
-        <v>310</v>
+        <v>61</v>
       </c>
       <c r="O51" t="s">
-        <v>311</v>
+        <v>4</v>
       </c>
       <c r="P51" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
       <c r="Q51" t="s">
-        <v>313</v>
+        <v>116</v>
       </c>
       <c r="R51" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S51" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="T51" t="s">
-        <v>314</v>
+        <v>3</v>
       </c>
       <c r="U51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>99</v>
+        <v>194</v>
       </c>
       <c r="B52" t="s">
-        <v>100</v>
+        <v>195</v>
       </c>
       <c r="C52" t="s">
-        <v>101</v>
+        <v>196</v>
       </c>
       <c r="D52" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E52" t="s">
-        <v>102</v>
+        <v>197</v>
       </c>
       <c r="G52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H52">
-        <v>5053</v>
+        <v>202</v>
       </c>
       <c r="I52" s="1">
-        <v>46251</v>
+        <v>46189</v>
       </c>
       <c r="J52">
-        <v>719</v>
+        <v>16720</v>
       </c>
       <c r="K52" t="s">
-        <v>103</v>
+        <v>192</v>
       </c>
       <c r="L52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M52" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="O52" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="P52" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="Q52" t="s">
-        <v>105</v>
+        <v>198</v>
       </c>
       <c r="R52" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S52" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T52" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="U52" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>151</v>
+        <v>203</v>
       </c>
       <c r="B53" t="s">
-        <v>152</v>
+        <v>204</v>
       </c>
       <c r="C53" t="s">
-        <v>153</v>
+        <v>205</v>
       </c>
       <c r="D53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E53" t="s">
-        <v>154</v>
+        <v>206</v>
       </c>
       <c r="G53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H53">
-        <v>237</v>
+        <v>2808</v>
       </c>
       <c r="I53" s="1">
-        <v>46282</v>
+        <v>46267</v>
       </c>
       <c r="J53" s="2">
-        <v>35467.589999999997</v>
-      </c>
-      <c r="K53">
-        <v>51990695000137</v>
+        <v>15900</v>
+      </c>
+      <c r="K53" t="s">
+        <v>207</v>
       </c>
       <c r="L53" t="s">
+        <v>61</v>
+      </c>
+      <c r="M53" t="s">
         <v>62</v>
       </c>
       <c r="O53" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="P53" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="Q53" t="s">
-        <v>155</v>
+        <v>208</v>
       </c>
       <c r="R53" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S53" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T53" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="U53" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>156</v>
+        <v>544</v>
       </c>
       <c r="B54" t="s">
-        <v>157</v>
+        <v>545</v>
       </c>
       <c r="C54" t="s">
-        <v>158</v>
+        <v>546</v>
       </c>
       <c r="D54" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E54" t="s">
-        <v>159</v>
+        <v>547</v>
       </c>
       <c r="G54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H54">
-        <v>3841</v>
+        <v>60958</v>
       </c>
       <c r="I54" s="1">
-        <v>46276</v>
+        <v>46296</v>
       </c>
       <c r="J54">
-        <v>1470</v>
+        <v>15.93</v>
       </c>
       <c r="K54" t="s">
+        <v>347</v>
+      </c>
+      <c r="L54" t="s">
+        <v>61</v>
+      </c>
+      <c r="M54" t="s">
         <v>160</v>
       </c>
-      <c r="L54" t="s">
-        <v>62</v>
-      </c>
       <c r="O54" t="s">
-        <v>35</v>
+        <v>348</v>
       </c>
       <c r="P54" t="s">
-        <v>256</v>
+        <v>349</v>
       </c>
       <c r="Q54" t="s">
-        <v>161</v>
+        <v>350</v>
       </c>
       <c r="R54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S54" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T54" t="s">
-        <v>33</v>
+        <v>351</v>
       </c>
       <c r="U54" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B55" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C55" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E55" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H55">
-        <v>32</v>
+        <v>37941</v>
       </c>
       <c r="I55" s="1">
-        <v>46269</v>
+        <v>46120</v>
       </c>
       <c r="J55" s="2">
-        <v>25800</v>
+        <v>1314.09</v>
       </c>
       <c r="K55" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="L55" t="s">
-        <v>62</v>
-      </c>
-      <c r="M55" t="s">
-        <v>142</v>
+        <v>61</v>
       </c>
       <c r="O55" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="P55" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>143</v>
+        <v>5</v>
       </c>
       <c r="R55" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S55" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="T55" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="U55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>144</v>
+        <v>416</v>
       </c>
       <c r="B56" t="s">
-        <v>145</v>
+        <v>417</v>
       </c>
       <c r="C56" t="s">
-        <v>146</v>
+        <v>418</v>
       </c>
       <c r="D56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E56" t="s">
-        <v>147</v>
+        <v>419</v>
       </c>
       <c r="G56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H56">
-        <v>798</v>
+        <v>2041</v>
       </c>
       <c r="I56" s="1">
-        <v>46269</v>
+        <v>46296</v>
       </c>
       <c r="J56" s="2">
-        <v>2890</v>
+        <v>12769.32</v>
       </c>
       <c r="K56" t="s">
-        <v>148</v>
+        <v>420</v>
       </c>
       <c r="L56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M56" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="O56" t="s">
-        <v>26</v>
+        <v>421</v>
       </c>
       <c r="P56" t="s">
-        <v>255</v>
+        <v>422</v>
       </c>
       <c r="Q56" t="s">
-        <v>150</v>
+        <v>423</v>
       </c>
       <c r="R56" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S56" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T56" t="s">
-        <v>20</v>
+        <v>351</v>
       </c>
       <c r="U56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="B57" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="C57" t="s">
+        <v>331</v>
+      </c>
+      <c r="D57" t="s">
+        <v>58</v>
+      </c>
+      <c r="E57" t="s">
+        <v>332</v>
+      </c>
+      <c r="G57" t="s">
+        <v>59</v>
+      </c>
+      <c r="H57">
         <v>342</v>
-      </c>
-      <c r="D57" t="s">
-        <v>59</v>
-      </c>
-      <c r="E57" t="s">
-        <v>343</v>
-      </c>
-      <c r="G57" t="s">
-        <v>60</v>
-      </c>
-      <c r="H57">
-        <v>10017</v>
       </c>
       <c r="I57" s="1">
         <v>46296</v>
       </c>
       <c r="J57" s="2">
-        <v>247890.09</v>
+        <v>1270.83</v>
       </c>
       <c r="K57" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="L57" t="s">
-        <v>62</v>
+        <v>61</v>
+      </c>
+      <c r="M57" t="s">
+        <v>79</v>
       </c>
       <c r="O57" t="s">
-        <v>345</v>
+        <v>289</v>
       </c>
       <c r="P57" t="s">
-        <v>346</v>
+        <v>290</v>
       </c>
       <c r="Q57" t="s">
-        <v>347</v>
+        <v>291</v>
       </c>
       <c r="R57" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S57" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="T57" t="s">
-        <v>304</v>
+        <v>23</v>
       </c>
       <c r="U57" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>348</v>
+        <v>67</v>
       </c>
       <c r="B58" t="s">
-        <v>349</v>
+        <v>68</v>
       </c>
       <c r="C58" t="s">
-        <v>350</v>
+        <v>69</v>
       </c>
       <c r="D58" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E58" t="s">
-        <v>351</v>
+        <v>70</v>
       </c>
       <c r="G58" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H58">
-        <v>1006</v>
+        <v>201</v>
       </c>
       <c r="I58" s="1">
-        <v>46296</v>
+        <v>46253</v>
       </c>
       <c r="J58" s="2">
-        <v>28450.799999999999</v>
+        <v>45439</v>
       </c>
       <c r="K58" t="s">
-        <v>344</v>
+        <v>71</v>
       </c>
       <c r="L58" t="s">
-        <v>62</v>
+        <v>61</v>
+      </c>
+      <c r="M58" t="s">
+        <v>72</v>
       </c>
       <c r="O58" t="s">
-        <v>345</v>
+        <v>21</v>
       </c>
       <c r="P58" t="s">
-        <v>346</v>
+        <v>243</v>
       </c>
       <c r="Q58" t="s">
-        <v>352</v>
+        <v>73</v>
       </c>
       <c r="R58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T58" t="s">
-        <v>285</v>
+        <v>10</v>
       </c>
       <c r="U58" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>131</v>
+        <v>430</v>
       </c>
       <c r="B59" t="s">
-        <v>132</v>
+        <v>431</v>
       </c>
       <c r="C59" t="s">
-        <v>133</v>
+        <v>432</v>
       </c>
       <c r="D59" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E59" t="s">
-        <v>134</v>
+        <v>433</v>
       </c>
       <c r="G59" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H59">
-        <v>37941</v>
+        <v>1246</v>
       </c>
       <c r="I59" s="1">
-        <v>46120</v>
+        <v>46296</v>
       </c>
       <c r="J59" s="2">
-        <v>1314.09</v>
+        <v>41270</v>
       </c>
       <c r="K59" t="s">
-        <v>135</v>
+        <v>434</v>
       </c>
       <c r="L59" t="s">
-        <v>62</v>
+        <v>61</v>
+      </c>
+      <c r="M59" t="s">
+        <v>103</v>
       </c>
       <c r="O59" t="s">
-        <v>4</v>
+        <v>435</v>
       </c>
       <c r="P59" t="s">
-        <v>5</v>
+        <v>436</v>
       </c>
       <c r="Q59" t="s">
-        <v>136</v>
+        <v>437</v>
       </c>
       <c r="R59" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S59" t="s">
-        <v>118</v>
+        <v>64</v>
       </c>
       <c r="T59" t="s">
-        <v>3</v>
+        <v>328</v>
       </c>
       <c r="U59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>362</v>
+        <v>442</v>
       </c>
       <c r="B60" t="s">
-        <v>363</v>
+        <v>443</v>
       </c>
       <c r="C60" t="s">
-        <v>364</v>
+        <v>444</v>
       </c>
       <c r="D60" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E60" t="s">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="G60" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H60">
-        <v>760</v>
+        <v>1</v>
       </c>
       <c r="I60" s="1">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="J60" s="2">
-        <v>500</v>
+        <v>40530</v>
       </c>
       <c r="K60" t="s">
-        <v>261</v>
+        <v>446</v>
       </c>
       <c r="L60" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M60" t="s">
-        <v>84</v>
+        <v>407</v>
       </c>
       <c r="O60" t="s">
-        <v>11</v>
+        <v>447</v>
       </c>
       <c r="P60" t="s">
-        <v>248</v>
+        <v>448</v>
       </c>
       <c r="Q60" t="s">
-        <v>85</v>
+        <v>449</v>
       </c>
       <c r="R60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S60" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T60" t="s">
-        <v>29</v>
+        <v>266</v>
       </c>
       <c r="U60" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>365</v>
+        <v>631</v>
       </c>
       <c r="B61" t="s">
-        <v>366</v>
+        <v>632</v>
       </c>
       <c r="C61" t="s">
-        <v>367</v>
+        <v>633</v>
       </c>
       <c r="D61" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E61" t="s">
-        <v>82</v>
+        <v>634</v>
       </c>
       <c r="G61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H61">
-        <v>759</v>
+        <v>4587</v>
       </c>
       <c r="I61" s="1">
-        <v>46294</v>
+        <v>46301</v>
       </c>
       <c r="J61" s="2">
-        <v>500</v>
+        <v>31518</v>
       </c>
       <c r="K61" t="s">
-        <v>261</v>
+        <v>575</v>
       </c>
       <c r="L61" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M61" t="s">
-        <v>84</v>
+        <v>576</v>
       </c>
       <c r="O61" t="s">
-        <v>11</v>
+        <v>577</v>
       </c>
       <c r="P61" t="s">
-        <v>248</v>
+        <v>578</v>
       </c>
       <c r="Q61" t="s">
-        <v>85</v>
+        <v>635</v>
       </c>
       <c r="R61" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T61" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="U61" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>368</v>
+        <v>636</v>
       </c>
       <c r="B62" t="s">
-        <v>369</v>
+        <v>637</v>
       </c>
       <c r="C62" t="s">
-        <v>370</v>
+        <v>638</v>
       </c>
       <c r="D62" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E62" t="s">
-        <v>82</v>
+        <v>639</v>
       </c>
       <c r="G62" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H62">
-        <v>758</v>
+        <v>801</v>
       </c>
       <c r="I62" s="1">
-        <v>46294</v>
+        <v>46300</v>
       </c>
       <c r="J62" s="2">
-        <v>500</v>
+        <v>30640</v>
       </c>
       <c r="K62" t="s">
-        <v>261</v>
+        <v>640</v>
       </c>
       <c r="L62" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M62" t="s">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="O62" t="s">
-        <v>11</v>
+        <v>641</v>
       </c>
       <c r="P62" t="s">
-        <v>248</v>
+        <v>642</v>
       </c>
       <c r="Q62" t="s">
-        <v>85</v>
+        <v>643</v>
       </c>
       <c r="R62" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S62" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T62" t="s">
-        <v>29</v>
+        <v>644</v>
       </c>
       <c r="U62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>371</v>
+        <v>135</v>
       </c>
       <c r="B63" t="s">
-        <v>372</v>
+        <v>136</v>
       </c>
       <c r="C63" t="s">
-        <v>373</v>
+        <v>137</v>
       </c>
       <c r="D63" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E63" t="s">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="G63" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H63">
-        <v>756</v>
+        <v>32</v>
       </c>
       <c r="I63" s="1">
-        <v>46294</v>
+        <v>46269</v>
       </c>
       <c r="J63" s="2">
-        <v>500</v>
+        <v>25800</v>
       </c>
       <c r="K63" t="s">
-        <v>261</v>
+        <v>139</v>
       </c>
       <c r="L63" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M63" t="s">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="O63" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="P63" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="Q63" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="R63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S63" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T63" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="U63" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>374</v>
+        <v>424</v>
       </c>
       <c r="B64" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C64" t="s">
-        <v>376</v>
+        <v>426</v>
       </c>
       <c r="D64" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E64" t="s">
-        <v>377</v>
+        <v>427</v>
       </c>
       <c r="G64" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H64">
-        <v>750</v>
+        <v>10858</v>
       </c>
       <c r="I64" s="1">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="J64" s="2">
-        <v>22920.95</v>
+        <v>24302</v>
       </c>
       <c r="K64" t="s">
-        <v>272</v>
+        <v>179</v>
       </c>
       <c r="L64" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M64" t="s">
-        <v>273</v>
+        <v>180</v>
       </c>
       <c r="O64" t="s">
-        <v>274</v>
+        <v>33</v>
       </c>
       <c r="P64" t="s">
-        <v>275</v>
+        <v>238</v>
       </c>
       <c r="Q64" t="s">
-        <v>276</v>
+        <v>428</v>
       </c>
       <c r="R64" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T64" t="s">
-        <v>277</v>
+        <v>429</v>
       </c>
       <c r="U64" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>315</v>
+        <v>645</v>
       </c>
       <c r="B65" t="s">
-        <v>316</v>
+        <v>646</v>
       </c>
       <c r="C65" t="s">
-        <v>317</v>
+        <v>647</v>
       </c>
       <c r="D65" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E65" t="s">
-        <v>318</v>
+        <v>648</v>
       </c>
       <c r="G65" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H65">
-        <v>16</v>
+        <v>4588</v>
       </c>
       <c r="I65" s="1">
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="J65" s="2">
-        <v>1700</v>
+        <v>18540</v>
       </c>
       <c r="K65" t="s">
-        <v>319</v>
+        <v>575</v>
       </c>
       <c r="L65" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M65" t="s">
-        <v>320</v>
+        <v>576</v>
       </c>
       <c r="O65" t="s">
-        <v>321</v>
+        <v>577</v>
       </c>
       <c r="P65" t="s">
-        <v>648</v>
+        <v>578</v>
       </c>
       <c r="Q65" t="s">
-        <v>322</v>
+        <v>649</v>
       </c>
       <c r="R65" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S65" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T65" t="s">
-        <v>304</v>
+        <v>20</v>
       </c>
       <c r="U65" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>323</v>
+        <v>450</v>
       </c>
       <c r="B66" t="s">
-        <v>324</v>
+        <v>451</v>
       </c>
       <c r="C66" t="s">
-        <v>325</v>
+        <v>452</v>
       </c>
       <c r="D66" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E66" t="s">
-        <v>174</v>
+        <v>453</v>
       </c>
       <c r="G66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H66">
-        <v>251785</v>
+        <v>2307</v>
       </c>
       <c r="I66" s="1">
         <v>46296</v>
       </c>
       <c r="J66" s="2">
-        <v>69505.789999999994</v>
+        <v>17094</v>
       </c>
       <c r="K66" t="s">
-        <v>326</v>
+        <v>454</v>
       </c>
       <c r="L66" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M66" t="s">
-        <v>162</v>
+        <v>83</v>
       </c>
       <c r="O66" t="s">
-        <v>19</v>
+        <v>455</v>
       </c>
       <c r="P66" t="s">
-        <v>242</v>
+        <v>456</v>
       </c>
       <c r="Q66" t="s">
-        <v>176</v>
+        <v>457</v>
       </c>
       <c r="R66" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S66" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T66" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="U66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>327</v>
+        <v>650</v>
       </c>
       <c r="B67" t="s">
-        <v>328</v>
+        <v>651</v>
       </c>
       <c r="C67" t="s">
-        <v>329</v>
+        <v>652</v>
       </c>
       <c r="D67" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E67" t="s">
-        <v>330</v>
+        <v>653</v>
       </c>
       <c r="G67" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H67">
-        <v>1657</v>
+        <v>4586</v>
       </c>
       <c r="I67" s="1">
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="J67" s="2">
-        <v>9909.09</v>
+        <v>15965</v>
       </c>
       <c r="K67" t="s">
-        <v>331</v>
+        <v>575</v>
       </c>
       <c r="L67" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M67" t="s">
-        <v>332</v>
+        <v>576</v>
       </c>
       <c r="O67" t="s">
-        <v>333</v>
+        <v>577</v>
       </c>
       <c r="P67" t="s">
-        <v>334</v>
+        <v>578</v>
       </c>
       <c r="Q67" t="s">
-        <v>335</v>
+        <v>654</v>
       </c>
       <c r="R67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S67" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T67" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="U67" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>336</v>
+        <v>524</v>
       </c>
       <c r="B68" t="s">
-        <v>337</v>
+        <v>525</v>
       </c>
       <c r="C68" t="s">
-        <v>338</v>
+        <v>526</v>
       </c>
       <c r="D68" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E68" t="s">
-        <v>339</v>
+        <v>527</v>
       </c>
       <c r="G68" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H68">
-        <v>1658</v>
+        <v>20</v>
       </c>
       <c r="I68" s="1">
         <v>46296</v>
       </c>
       <c r="J68">
-        <v>9000</v>
+        <v>11782</v>
       </c>
       <c r="K68" t="s">
-        <v>331</v>
+        <v>528</v>
       </c>
       <c r="L68" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M68" t="s">
-        <v>332</v>
+        <v>277</v>
       </c>
       <c r="O68" t="s">
-        <v>333</v>
+        <v>529</v>
       </c>
       <c r="P68" t="s">
-        <v>334</v>
+        <v>530</v>
       </c>
       <c r="Q68" t="s">
-        <v>335</v>
+        <v>531</v>
       </c>
       <c r="R68" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S68" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T68" t="s">
-        <v>285</v>
+        <v>532</v>
       </c>
       <c r="U68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>201</v>
+        <v>655</v>
       </c>
       <c r="B69" t="s">
-        <v>202</v>
+        <v>656</v>
       </c>
       <c r="C69" t="s">
-        <v>203</v>
+        <v>657</v>
       </c>
       <c r="D69" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E69" t="s">
-        <v>204</v>
+        <v>658</v>
       </c>
       <c r="G69" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H69">
-        <v>176266</v>
+        <v>118</v>
       </c>
       <c r="I69" s="1">
-        <v>46266</v>
+        <v>46300</v>
       </c>
       <c r="J69">
-        <v>270515.57</v>
+        <v>11000</v>
       </c>
       <c r="K69" t="s">
-        <v>205</v>
+        <v>659</v>
       </c>
       <c r="L69" t="s">
-        <v>62</v>
+        <v>61</v>
+      </c>
+      <c r="M69" t="s">
+        <v>187</v>
       </c>
       <c r="O69" t="s">
-        <v>24</v>
+        <v>660</v>
       </c>
       <c r="P69" t="s">
-        <v>249</v>
+        <v>661</v>
       </c>
       <c r="Q69" t="s">
-        <v>206</v>
+        <v>662</v>
       </c>
       <c r="R69" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S69" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T69" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="U69" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>649</v>
+        <v>663</v>
       </c>
       <c r="B70" t="s">
-        <v>650</v>
+        <v>664</v>
       </c>
       <c r="C70" t="s">
-        <v>651</v>
+        <v>665</v>
       </c>
       <c r="D70" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E70" t="s">
-        <v>652</v>
+        <v>666</v>
       </c>
       <c r="G70" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H70">
-        <v>176</v>
+        <v>4589</v>
       </c>
       <c r="I70" s="1">
-        <v>46273</v>
+        <v>46301</v>
       </c>
       <c r="J70">
-        <v>22865.14</v>
+        <v>10000</v>
       </c>
       <c r="K70" t="s">
-        <v>653</v>
+        <v>575</v>
       </c>
       <c r="L70" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M70" t="s">
-        <v>63</v>
+        <v>576</v>
       </c>
       <c r="O70" t="s">
-        <v>654</v>
+        <v>577</v>
       </c>
       <c r="P70" t="s">
-        <v>655</v>
+        <v>578</v>
       </c>
       <c r="Q70" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="R70" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S70" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T70" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="U70" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>177</v>
+        <v>320</v>
       </c>
       <c r="B71" t="s">
-        <v>178</v>
+        <v>321</v>
       </c>
       <c r="C71" t="s">
-        <v>179</v>
+        <v>322</v>
       </c>
       <c r="D71" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E71" t="s">
-        <v>180</v>
+        <v>323</v>
       </c>
       <c r="G71" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H71">
-        <v>10760</v>
+        <v>6025</v>
       </c>
       <c r="I71" s="1">
-        <v>46276</v>
+        <v>46296</v>
       </c>
       <c r="J71" s="2">
-        <v>3770.93</v>
+        <v>9204</v>
       </c>
       <c r="K71" t="s">
-        <v>181</v>
+        <v>324</v>
       </c>
       <c r="L71" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M71" t="s">
-        <v>182</v>
+        <v>83</v>
       </c>
       <c r="O71" t="s">
-        <v>34</v>
+        <v>325</v>
       </c>
       <c r="P71" t="s">
-        <v>246</v>
+        <v>326</v>
       </c>
       <c r="Q71" t="s">
-        <v>183</v>
+        <v>327</v>
       </c>
       <c r="R71" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S71" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T71" t="s">
-        <v>22</v>
+        <v>328</v>
       </c>
       <c r="U71" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>184</v>
+        <v>292</v>
       </c>
       <c r="B72" t="s">
-        <v>185</v>
+        <v>293</v>
       </c>
       <c r="C72" t="s">
-        <v>186</v>
+        <v>294</v>
       </c>
       <c r="D72" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E72" t="s">
-        <v>187</v>
+        <v>295</v>
       </c>
       <c r="G72" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H72">
-        <v>13020</v>
+        <v>1658</v>
       </c>
       <c r="I72" s="1">
-        <v>46268</v>
+        <v>46296</v>
       </c>
       <c r="J72">
-        <v>330986.02</v>
+        <v>9000</v>
       </c>
       <c r="K72" t="s">
-        <v>188</v>
+        <v>287</v>
       </c>
       <c r="L72" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M72" t="s">
-        <v>189</v>
+        <v>288</v>
       </c>
       <c r="O72" t="s">
-        <v>9</v>
+        <v>289</v>
       </c>
       <c r="P72" t="s">
-        <v>241</v>
+        <v>290</v>
       </c>
       <c r="Q72" t="s">
-        <v>130</v>
+        <v>291</v>
       </c>
       <c r="R72" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S72" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="T72" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="U72" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>171</v>
+        <v>308</v>
       </c>
       <c r="B73" t="s">
-        <v>172</v>
+        <v>309</v>
       </c>
       <c r="C73" t="s">
-        <v>173</v>
+        <v>310</v>
       </c>
       <c r="D73" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E73" t="s">
-        <v>174</v>
+        <v>295</v>
       </c>
       <c r="G73" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H73">
-        <v>251216</v>
+        <v>1656</v>
       </c>
       <c r="I73" s="1">
-        <v>46283</v>
+        <v>46296</v>
       </c>
       <c r="J73">
-        <v>69505.789999999994</v>
+        <v>9000</v>
       </c>
       <c r="K73" t="s">
-        <v>175</v>
+        <v>311</v>
       </c>
       <c r="L73" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M73" t="s">
-        <v>162</v>
+        <v>288</v>
       </c>
       <c r="O73" t="s">
-        <v>19</v>
+        <v>289</v>
       </c>
       <c r="P73" t="s">
-        <v>242</v>
+        <v>290</v>
       </c>
       <c r="Q73" t="s">
-        <v>176</v>
+        <v>291</v>
       </c>
       <c r="R73" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S73" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="T73" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="U73" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>378</v>
+        <v>668</v>
       </c>
       <c r="B74" t="s">
-        <v>379</v>
+        <v>669</v>
       </c>
       <c r="C74" t="s">
-        <v>380</v>
+        <v>670</v>
       </c>
       <c r="D74" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E74" t="s">
-        <v>82</v>
+        <v>671</v>
       </c>
       <c r="G74" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H74">
-        <v>766</v>
+        <v>1678</v>
       </c>
       <c r="I74" s="1">
-        <v>46294</v>
+        <v>46301</v>
       </c>
       <c r="J74">
-        <v>500</v>
+        <v>7750</v>
       </c>
       <c r="K74" t="s">
-        <v>261</v>
+        <v>672</v>
       </c>
       <c r="L74" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M74" t="s">
-        <v>84</v>
+        <v>277</v>
       </c>
       <c r="O74" t="s">
-        <v>11</v>
+        <v>673</v>
       </c>
       <c r="P74" t="s">
-        <v>248</v>
+        <v>674</v>
       </c>
       <c r="Q74" t="s">
-        <v>85</v>
+        <v>675</v>
       </c>
       <c r="R74" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S74" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T74" t="s">
-        <v>29</v>
+        <v>266</v>
       </c>
       <c r="U74" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="B75" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="C75" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="D75" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E75" t="s">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="G75" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H75">
-        <v>763</v>
+        <v>31567</v>
       </c>
       <c r="I75" s="1">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="J75">
-        <v>500</v>
+        <v>6144</v>
       </c>
       <c r="K75" t="s">
-        <v>261</v>
+        <v>398</v>
       </c>
       <c r="L75" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M75" t="s">
-        <v>273</v>
+        <v>103</v>
       </c>
       <c r="O75" t="s">
-        <v>11</v>
+        <v>399</v>
       </c>
       <c r="P75" t="s">
-        <v>248</v>
+        <v>400</v>
       </c>
       <c r="Q75" t="s">
-        <v>85</v>
+        <v>401</v>
       </c>
       <c r="R75" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S75" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T75" t="s">
-        <v>29</v>
+        <v>328</v>
       </c>
       <c r="U75" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>384</v>
+        <v>438</v>
       </c>
       <c r="B76" t="s">
-        <v>385</v>
+        <v>439</v>
       </c>
       <c r="C76" t="s">
-        <v>386</v>
+        <v>440</v>
       </c>
       <c r="D76" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E76" t="s">
-        <v>82</v>
+        <v>441</v>
       </c>
       <c r="G76" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H76">
-        <v>765</v>
+        <v>1232</v>
       </c>
       <c r="I76" s="1">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="J76">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="K76" t="s">
-        <v>261</v>
+        <v>434</v>
       </c>
       <c r="L76" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M76" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="O76" t="s">
-        <v>11</v>
+        <v>435</v>
       </c>
       <c r="P76" t="s">
-        <v>248</v>
+        <v>436</v>
       </c>
       <c r="Q76" t="s">
-        <v>85</v>
+        <v>437</v>
       </c>
       <c r="R76" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S76" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T76" t="s">
-        <v>29</v>
+        <v>328</v>
       </c>
       <c r="U76" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>207</v>
+        <v>676</v>
       </c>
       <c r="B77" t="s">
-        <v>208</v>
+        <v>677</v>
       </c>
       <c r="C77" t="s">
-        <v>209</v>
+        <v>678</v>
       </c>
       <c r="D77" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E77" t="s">
-        <v>210</v>
+        <v>679</v>
       </c>
       <c r="G77" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H77">
-        <v>21985</v>
+        <v>7809</v>
       </c>
       <c r="I77" s="1">
-        <v>46262</v>
+        <v>46301</v>
       </c>
       <c r="J77">
-        <v>969.98</v>
+        <v>5824</v>
       </c>
       <c r="K77" t="s">
-        <v>96</v>
+        <v>680</v>
       </c>
       <c r="L77" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M77" t="s">
-        <v>97</v>
+        <v>277</v>
       </c>
       <c r="O77" t="s">
-        <v>17</v>
+        <v>681</v>
       </c>
       <c r="P77" t="s">
-        <v>231</v>
+        <v>682</v>
       </c>
       <c r="Q77" t="s">
-        <v>232</v>
+        <v>683</v>
       </c>
       <c r="R77" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S77" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T77" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="U77" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>657</v>
+        <v>411</v>
       </c>
       <c r="B78" t="s">
-        <v>658</v>
+        <v>412</v>
       </c>
       <c r="C78" t="s">
-        <v>659</v>
+        <v>413</v>
       </c>
       <c r="D78" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E78" t="s">
-        <v>660</v>
+        <v>414</v>
       </c>
       <c r="G78" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H78">
-        <v>17158443</v>
+        <v>2800</v>
       </c>
       <c r="I78" s="1">
-        <v>46290</v>
+        <v>46296</v>
       </c>
       <c r="J78">
-        <v>7704.8</v>
+        <v>5400</v>
       </c>
       <c r="K78" t="s">
-        <v>661</v>
+        <v>406</v>
       </c>
       <c r="L78" t="s">
-        <v>62</v>
+        <v>61</v>
+      </c>
+      <c r="M78" t="s">
+        <v>407</v>
       </c>
       <c r="O78" s="3" t="s">
-        <v>662</v>
+        <v>408</v>
       </c>
       <c r="P78" t="s">
-        <v>663</v>
+        <v>409</v>
       </c>
       <c r="Q78" t="s">
-        <v>664</v>
+        <v>415</v>
       </c>
       <c r="R78" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S78" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T78" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="U78" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>665</v>
+        <v>684</v>
       </c>
       <c r="B79" t="s">
-        <v>666</v>
+        <v>685</v>
       </c>
       <c r="C79" t="s">
-        <v>667</v>
+        <v>686</v>
       </c>
       <c r="D79" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E79" t="s">
-        <v>668</v>
+        <v>687</v>
       </c>
       <c r="G79" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H79">
-        <v>17158451</v>
+        <v>12644</v>
       </c>
       <c r="I79" s="1">
-        <v>46290</v>
+        <v>46300</v>
       </c>
       <c r="J79">
-        <v>198612.03</v>
+        <v>4860</v>
       </c>
       <c r="K79" t="s">
-        <v>661</v>
+        <v>563</v>
       </c>
       <c r="L79" t="s">
-        <v>62</v>
+        <v>61</v>
+      </c>
+      <c r="M79" t="s">
+        <v>277</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>662</v>
+        <v>564</v>
       </c>
       <c r="P79" t="s">
-        <v>663</v>
+        <v>565</v>
       </c>
       <c r="Q79" t="s">
-        <v>669</v>
+        <v>688</v>
       </c>
       <c r="R79" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S79" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T79" t="s">
-        <v>29</v>
+        <v>351</v>
       </c>
       <c r="U79" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>670</v>
+        <v>689</v>
       </c>
       <c r="B80" t="s">
-        <v>671</v>
+        <v>690</v>
       </c>
       <c r="C80" t="s">
-        <v>672</v>
+        <v>691</v>
       </c>
       <c r="D80" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E80" t="s">
-        <v>673</v>
+        <v>692</v>
       </c>
       <c r="G80" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H80">
-        <v>1276715</v>
+        <v>117</v>
       </c>
       <c r="I80" s="1">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="J80">
-        <v>7304.8</v>
+        <v>3531</v>
       </c>
       <c r="K80" t="s">
-        <v>674</v>
+        <v>659</v>
       </c>
       <c r="L80" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M80" t="s">
-        <v>104</v>
+        <v>187</v>
       </c>
       <c r="O80" t="s">
-        <v>675</v>
+        <v>660</v>
       </c>
       <c r="P80" t="s">
-        <v>676</v>
+        <v>661</v>
       </c>
       <c r="Q80" t="s">
-        <v>677</v>
+        <v>693</v>
       </c>
       <c r="R80" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S80" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T80" t="s">
-        <v>447</v>
+        <v>351</v>
       </c>
       <c r="U80" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>678</v>
+        <v>214</v>
       </c>
       <c r="B81" t="s">
-        <v>679</v>
+        <v>215</v>
       </c>
       <c r="C81" t="s">
-        <v>680</v>
+        <v>216</v>
       </c>
       <c r="D81" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E81" t="s">
-        <v>681</v>
+        <v>217</v>
       </c>
       <c r="G81" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H81">
-        <v>2042</v>
+        <v>427</v>
       </c>
       <c r="I81" s="1">
-        <v>46296</v>
+        <v>46281</v>
       </c>
       <c r="J81" s="2">
-        <v>4944.6000000000004</v>
+        <v>3200</v>
       </c>
       <c r="K81" t="s">
-        <v>682</v>
+        <v>218</v>
       </c>
       <c r="L81" t="s">
+        <v>61</v>
+      </c>
+      <c r="M81" t="s">
         <v>62</v>
       </c>
-      <c r="M81" t="s">
-        <v>162</v>
-      </c>
       <c r="O81" t="s">
-        <v>556</v>
+        <v>37</v>
       </c>
       <c r="P81" t="s">
-        <v>557</v>
+        <v>245</v>
       </c>
       <c r="Q81" t="s">
-        <v>683</v>
+        <v>219</v>
       </c>
       <c r="R81" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S81" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T81" t="s">
-        <v>477</v>
+        <v>23</v>
       </c>
       <c r="U81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
       <c r="B82" t="s">
-        <v>685</v>
+        <v>695</v>
       </c>
       <c r="C82" t="s">
-        <v>686</v>
+        <v>696</v>
       </c>
       <c r="D82" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E82" t="s">
-        <v>687</v>
+        <v>697</v>
       </c>
       <c r="G82" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H82">
-        <v>5881</v>
+        <v>2619</v>
       </c>
       <c r="I82" s="1">
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="J82" s="2">
-        <v>7887.75</v>
+        <v>3090</v>
       </c>
       <c r="K82" t="s">
-        <v>688</v>
+        <v>698</v>
       </c>
       <c r="L82" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M82" t="s">
-        <v>104</v>
+        <v>277</v>
       </c>
       <c r="O82" t="s">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="P82" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
       <c r="Q82" t="s">
-        <v>691</v>
+        <v>701</v>
       </c>
       <c r="R82" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S82" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T82" t="s">
-        <v>692</v>
+        <v>266</v>
       </c>
       <c r="U82" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="B83" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="C83" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="D83" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E83" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="G83" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H83">
-        <v>12908</v>
+        <v>798</v>
       </c>
       <c r="I83" s="1">
-        <v>46205</v>
+        <v>46269</v>
       </c>
       <c r="J83" s="2">
-        <v>643664.51</v>
+        <v>2890</v>
       </c>
       <c r="K83" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="L83" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M83" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="O83" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="P83" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="Q83" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="R83" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S83" t="s">
-        <v>118</v>
+        <v>64</v>
       </c>
       <c r="T83" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="U83" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>211</v>
+        <v>458</v>
       </c>
       <c r="B84" t="s">
-        <v>212</v>
+        <v>459</v>
       </c>
       <c r="C84" t="s">
-        <v>213</v>
+        <v>460</v>
       </c>
       <c r="D84" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E84" t="s">
-        <v>214</v>
+        <v>461</v>
       </c>
       <c r="G84" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H84">
-        <v>2808</v>
+        <v>21395</v>
       </c>
       <c r="I84" s="1">
-        <v>46267</v>
+        <v>46296</v>
       </c>
       <c r="J84" s="2">
-        <v>15900</v>
+        <v>2800</v>
       </c>
       <c r="K84" t="s">
-        <v>215</v>
+        <v>462</v>
       </c>
       <c r="L84" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M84" t="s">
-        <v>63</v>
+        <v>288</v>
       </c>
       <c r="O84" t="s">
-        <v>32</v>
+        <v>463</v>
       </c>
       <c r="P84" t="s">
-        <v>251</v>
+        <v>464</v>
       </c>
       <c r="Q84" t="s">
-        <v>216</v>
+        <v>465</v>
       </c>
       <c r="R84" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S84" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T84" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="U84" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>693</v>
+        <v>539</v>
       </c>
       <c r="B85" t="s">
-        <v>694</v>
+        <v>540</v>
       </c>
       <c r="C85" t="s">
-        <v>695</v>
+        <v>541</v>
       </c>
       <c r="D85" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E85" t="s">
-        <v>696</v>
+        <v>542</v>
       </c>
       <c r="G85" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H85">
-        <v>22574</v>
+        <v>21395</v>
       </c>
       <c r="I85" s="1">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="J85">
-        <v>805</v>
+        <v>2800</v>
       </c>
       <c r="K85" t="s">
-        <v>494</v>
+        <v>543</v>
       </c>
       <c r="L85" t="s">
-        <v>62</v>
+        <v>61</v>
+      </c>
+      <c r="M85" t="s">
+        <v>288</v>
       </c>
       <c r="O85" t="s">
-        <v>495</v>
+        <v>463</v>
       </c>
       <c r="P85" t="s">
-        <v>496</v>
+        <v>464</v>
       </c>
       <c r="Q85" t="s">
-        <v>697</v>
+        <v>465</v>
       </c>
       <c r="R85" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S85" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T85" t="s">
-        <v>477</v>
+        <v>3</v>
       </c>
       <c r="U85" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>698</v>
+        <v>154</v>
       </c>
       <c r="B86" t="s">
-        <v>699</v>
+        <v>155</v>
       </c>
       <c r="C86" t="s">
-        <v>700</v>
+        <v>156</v>
       </c>
       <c r="D86" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E86" t="s">
-        <v>701</v>
+        <v>157</v>
       </c>
       <c r="G86" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H86">
-        <v>22575</v>
+        <v>3841</v>
       </c>
       <c r="I86" s="1">
-        <v>46297</v>
+        <v>46276</v>
       </c>
       <c r="J86" s="2">
-        <v>930</v>
+        <v>1470</v>
       </c>
       <c r="K86" t="s">
-        <v>702</v>
+        <v>158</v>
       </c>
       <c r="L86" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O86" t="s">
-        <v>495</v>
+        <v>34</v>
       </c>
       <c r="P86" t="s">
-        <v>496</v>
+        <v>247</v>
       </c>
       <c r="Q86" t="s">
-        <v>703</v>
+        <v>159</v>
       </c>
       <c r="R86" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S86" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T86" t="s">
-        <v>477</v>
+        <v>32</v>
       </c>
       <c r="U86" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>704</v>
+        <v>312</v>
       </c>
       <c r="B87" t="s">
-        <v>705</v>
+        <v>313</v>
       </c>
       <c r="C87" t="s">
-        <v>706</v>
+        <v>314</v>
       </c>
       <c r="D87" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E87" t="s">
-        <v>707</v>
+        <v>315</v>
       </c>
       <c r="G87" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H87">
-        <v>193</v>
+        <v>2564</v>
       </c>
       <c r="I87" s="1">
         <v>46296</v>
       </c>
       <c r="J87">
-        <v>546</v>
+        <v>1300</v>
       </c>
       <c r="K87" t="s">
-        <v>708</v>
+        <v>316</v>
       </c>
       <c r="L87" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M87" t="s">
-        <v>709</v>
+        <v>79</v>
       </c>
       <c r="O87" t="s">
-        <v>710</v>
+        <v>317</v>
       </c>
       <c r="P87" t="s">
-        <v>711</v>
+        <v>318</v>
       </c>
       <c r="Q87" t="s">
-        <v>712</v>
+        <v>319</v>
       </c>
       <c r="R87" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S87" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T87" t="s">
-        <v>285</v>
+        <v>10</v>
       </c>
       <c r="U87" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>713</v>
+        <v>364</v>
       </c>
       <c r="B88" t="s">
-        <v>714</v>
+        <v>365</v>
       </c>
       <c r="C88" t="s">
-        <v>715</v>
+        <v>366</v>
       </c>
       <c r="D88" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E88" t="s">
-        <v>716</v>
+        <v>367</v>
       </c>
       <c r="G88" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H88">
-        <v>13018</v>
+        <v>22573</v>
       </c>
       <c r="I88" s="1">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="J88" s="2">
-        <v>18778.25</v>
+        <v>950</v>
       </c>
       <c r="K88" t="s">
-        <v>717</v>
+        <v>368</v>
       </c>
       <c r="L88" t="s">
-        <v>62</v>
-      </c>
-      <c r="M88" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
       <c r="O88" t="s">
-        <v>9</v>
+        <v>369</v>
       </c>
       <c r="P88" t="s">
-        <v>241</v>
+        <v>370</v>
       </c>
       <c r="Q88" t="s">
-        <v>130</v>
+        <v>371</v>
       </c>
       <c r="R88" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S88" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T88" t="s">
-        <v>16</v>
+        <v>351</v>
       </c>
       <c r="U88" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>168</v>
+        <v>513</v>
       </c>
       <c r="B89" t="s">
-        <v>169</v>
+        <v>514</v>
       </c>
       <c r="C89" t="s">
-        <v>170</v>
+        <v>515</v>
       </c>
       <c r="D89" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E89" t="s">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="G89" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H89">
-        <v>460</v>
+        <v>22575</v>
       </c>
       <c r="I89" s="1">
-        <v>46262</v>
+        <v>46297</v>
       </c>
       <c r="J89">
-        <v>500</v>
+        <v>930</v>
       </c>
       <c r="K89" t="s">
-        <v>83</v>
+        <v>517</v>
       </c>
       <c r="L89" t="s">
-        <v>62</v>
-      </c>
-      <c r="M89" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="O89" t="s">
-        <v>11</v>
+        <v>369</v>
       </c>
       <c r="P89" t="s">
-        <v>248</v>
+        <v>370</v>
       </c>
       <c r="Q89" t="s">
-        <v>85</v>
+        <v>518</v>
       </c>
       <c r="R89" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S89" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T89" t="s">
-        <v>18</v>
+        <v>351</v>
       </c>
       <c r="U89" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>228</v>
+        <v>702</v>
       </c>
       <c r="B90" t="s">
-        <v>229</v>
+        <v>703</v>
       </c>
       <c r="C90" t="s">
-        <v>230</v>
+        <v>704</v>
       </c>
       <c r="D90" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E90" t="s">
-        <v>82</v>
+        <v>705</v>
       </c>
       <c r="G90" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H90">
-        <v>464</v>
+        <v>3656</v>
       </c>
       <c r="I90" s="1">
-        <v>46265</v>
+        <v>46297</v>
       </c>
       <c r="J90">
-        <v>500</v>
+        <v>850</v>
       </c>
       <c r="K90" t="s">
-        <v>83</v>
+        <v>706</v>
       </c>
       <c r="L90" t="s">
-        <v>62</v>
-      </c>
-      <c r="M90" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="O90" t="s">
-        <v>11</v>
+        <v>707</v>
       </c>
       <c r="P90" t="s">
-        <v>248</v>
+        <v>708</v>
       </c>
       <c r="Q90" t="s">
-        <v>85</v>
+        <v>709</v>
       </c>
       <c r="R90" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S90" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T90" t="s">
-        <v>18</v>
+        <v>266</v>
       </c>
       <c r="U90" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>718</v>
+        <v>508</v>
       </c>
       <c r="B91" t="s">
-        <v>719</v>
+        <v>509</v>
       </c>
       <c r="C91" t="s">
-        <v>720</v>
+        <v>510</v>
       </c>
       <c r="D91" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E91" t="s">
-        <v>721</v>
+        <v>511</v>
       </c>
       <c r="G91" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H91">
-        <v>20</v>
+        <v>22574</v>
       </c>
       <c r="I91" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="J91">
-        <v>11782</v>
+        <v>805</v>
       </c>
       <c r="K91" t="s">
-        <v>722</v>
+        <v>368</v>
       </c>
       <c r="L91" t="s">
-        <v>62</v>
-      </c>
-      <c r="M91" t="s">
-        <v>310</v>
+        <v>61</v>
       </c>
       <c r="O91" t="s">
-        <v>723</v>
+        <v>369</v>
       </c>
       <c r="P91" t="s">
-        <v>724</v>
+        <v>370</v>
       </c>
       <c r="Q91" t="s">
-        <v>725</v>
+        <v>512</v>
       </c>
       <c r="R91" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S91" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T91" t="s">
-        <v>726</v>
+        <v>351</v>
       </c>
       <c r="U91" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>727</v>
+        <v>98</v>
       </c>
       <c r="B92" t="s">
-        <v>728</v>
+        <v>99</v>
       </c>
       <c r="C92" t="s">
-        <v>729</v>
+        <v>100</v>
       </c>
       <c r="D92" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E92" t="s">
-        <v>730</v>
+        <v>101</v>
       </c>
       <c r="G92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H92">
-        <v>345</v>
+        <v>5053</v>
       </c>
       <c r="I92" s="1">
-        <v>46296</v>
+        <v>46251</v>
       </c>
       <c r="J92">
-        <v>1200</v>
+        <v>719</v>
       </c>
       <c r="K92" t="s">
-        <v>731</v>
+        <v>102</v>
       </c>
       <c r="L92" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M92" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="O92" t="s">
-        <v>732</v>
+        <v>15</v>
       </c>
       <c r="P92" t="s">
-        <v>733</v>
+        <v>248</v>
       </c>
       <c r="Q92" t="s">
-        <v>734</v>
+        <v>104</v>
       </c>
       <c r="R92" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S92" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T92" t="s">
-        <v>304</v>
+        <v>14</v>
       </c>
       <c r="U92" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>735</v>
+        <v>710</v>
       </c>
       <c r="B93" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="C93" t="s">
-        <v>737</v>
+        <v>712</v>
       </c>
       <c r="D93" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E93" t="s">
-        <v>730</v>
+        <v>81</v>
       </c>
       <c r="G93" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H93">
-        <v>346</v>
+        <v>779</v>
       </c>
       <c r="I93" s="1">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="J93">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="K93" t="s">
-        <v>731</v>
+        <v>82</v>
       </c>
       <c r="L93" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M93" t="s">
+        <v>83</v>
+      </c>
+      <c r="O93" t="s">
+        <v>11</v>
+      </c>
+      <c r="P93" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q93" t="s">
         <v>84</v>
       </c>
-      <c r="O93" t="s">
-        <v>732</v>
-      </c>
-      <c r="P93" t="s">
-        <v>733</v>
-      </c>
-      <c r="Q93" t="s">
-        <v>738</v>
-      </c>
       <c r="R93" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S93" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T93" t="s">
-        <v>304</v>
+        <v>28</v>
       </c>
       <c r="U93" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>217</v>
+        <v>713</v>
       </c>
       <c r="B94" t="s">
-        <v>218</v>
+        <v>714</v>
       </c>
       <c r="C94" t="s">
-        <v>219</v>
+        <v>715</v>
       </c>
       <c r="D94" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E94" t="s">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="G94" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H94">
-        <v>26491</v>
+        <v>790</v>
       </c>
       <c r="I94" s="1">
-        <v>46267</v>
+        <v>46301</v>
       </c>
       <c r="J94">
-        <v>22510.52</v>
+        <v>500</v>
       </c>
       <c r="K94" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="L94" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M94" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="O94" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="P94" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="Q94" t="s">
-        <v>221</v>
+        <v>84</v>
       </c>
       <c r="R94" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S94" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T94" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="U94" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>222</v>
+        <v>166</v>
       </c>
       <c r="B95" t="s">
-        <v>223</v>
+        <v>167</v>
       </c>
       <c r="C95" t="s">
-        <v>224</v>
+        <v>168</v>
       </c>
       <c r="D95" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E95" t="s">
-        <v>225</v>
+        <v>81</v>
       </c>
       <c r="G95" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H95">
-        <v>427</v>
+        <v>460</v>
       </c>
       <c r="I95">
-        <v>46281</v>
+        <v>46262</v>
       </c>
       <c r="J95">
-        <v>3200</v>
+        <v>500</v>
       </c>
       <c r="K95" t="s">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="L95" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M95" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="O95" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="P95" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="Q95" t="s">
-        <v>227</v>
+        <v>84</v>
       </c>
       <c r="R95" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S95" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T95" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="U95" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>739</v>
+        <v>220</v>
       </c>
       <c r="B96" t="s">
-        <v>740</v>
+        <v>221</v>
       </c>
       <c r="C96" t="s">
-        <v>741</v>
+        <v>222</v>
       </c>
       <c r="D96" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E96" t="s">
-        <v>742</v>
+        <v>81</v>
       </c>
       <c r="G96" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H96">
-        <v>39</v>
+        <v>464</v>
       </c>
       <c r="I96">
-        <v>46297</v>
+        <v>46265</v>
       </c>
       <c r="J96">
-        <v>2958.63</v>
+        <v>500</v>
       </c>
       <c r="K96" t="s">
-        <v>743</v>
+        <v>82</v>
       </c>
       <c r="L96" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M96" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="O96" t="s">
-        <v>645</v>
+        <v>11</v>
       </c>
       <c r="P96" t="s">
-        <v>646</v>
+        <v>240</v>
       </c>
       <c r="Q96" t="s">
-        <v>744</v>
+        <v>84</v>
       </c>
       <c r="R96" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S96" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T96" t="s">
-        <v>285</v>
+        <v>18</v>
       </c>
       <c r="U96" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>393</v>
+        <v>716</v>
       </c>
       <c r="B97" t="s">
-        <v>394</v>
+        <v>717</v>
       </c>
       <c r="C97" t="s">
-        <v>395</v>
+        <v>718</v>
       </c>
       <c r="D97" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E97" t="s">
-        <v>339</v>
+        <v>81</v>
       </c>
       <c r="G97" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H97">
-        <v>1656</v>
+        <v>777</v>
       </c>
       <c r="I97">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="J97">
-        <v>9000</v>
+        <v>500</v>
       </c>
       <c r="K97" t="s">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="L97" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M97" t="s">
-        <v>332</v>
+        <v>83</v>
       </c>
       <c r="O97" t="s">
-        <v>333</v>
+        <v>11</v>
       </c>
       <c r="P97" t="s">
-        <v>334</v>
+        <v>240</v>
       </c>
       <c r="Q97" t="s">
-        <v>335</v>
+        <v>84</v>
       </c>
       <c r="R97" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S97" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T97" t="s">
-        <v>285</v>
+        <v>28</v>
       </c>
       <c r="U97" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>397</v>
+        <v>719</v>
       </c>
       <c r="B98" t="s">
-        <v>398</v>
+        <v>720</v>
       </c>
       <c r="C98" t="s">
-        <v>399</v>
+        <v>721</v>
       </c>
       <c r="D98" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E98" t="s">
-        <v>400</v>
+        <v>81</v>
       </c>
       <c r="G98" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H98">
-        <v>2564</v>
+        <v>10280</v>
       </c>
       <c r="I98">
-        <v>46296</v>
+        <v>46149</v>
       </c>
       <c r="J98">
-        <v>1300</v>
+        <v>500</v>
       </c>
       <c r="K98" t="s">
-        <v>401</v>
+        <v>82</v>
       </c>
       <c r="L98" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M98" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="O98" t="s">
-        <v>402</v>
+        <v>11</v>
       </c>
       <c r="P98" t="s">
-        <v>403</v>
+        <v>240</v>
       </c>
       <c r="Q98" t="s">
-        <v>404</v>
+        <v>722</v>
       </c>
       <c r="R98" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S98" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T98" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="U98" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>405</v>
+        <v>723</v>
       </c>
       <c r="B99" t="s">
-        <v>406</v>
+        <v>724</v>
       </c>
       <c r="C99" t="s">
-        <v>407</v>
+        <v>725</v>
       </c>
       <c r="D99" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E99" t="s">
-        <v>408</v>
+        <v>81</v>
       </c>
       <c r="G99" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H99">
-        <v>6025</v>
+        <v>793</v>
       </c>
       <c r="I99">
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="J99">
-        <v>9204</v>
+        <v>500</v>
       </c>
       <c r="K99" t="s">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="L99" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M99" t="s">
+        <v>83</v>
+      </c>
+      <c r="O99" t="s">
+        <v>11</v>
+      </c>
+      <c r="P99" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q99" t="s">
         <v>84</v>
       </c>
-      <c r="O99" t="s">
-        <v>410</v>
-      </c>
-      <c r="P99" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q99" t="s">
-        <v>412</v>
-      </c>
       <c r="R99" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S99" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T99" t="s">
-        <v>413</v>
+        <v>28</v>
       </c>
       <c r="U99" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>414</v>
+        <v>726</v>
       </c>
       <c r="B100" t="s">
-        <v>415</v>
+        <v>727</v>
       </c>
       <c r="C100" t="s">
-        <v>416</v>
+        <v>728</v>
       </c>
       <c r="D100" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E100" t="s">
-        <v>417</v>
+        <v>81</v>
       </c>
       <c r="G100" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H100">
-        <v>10823</v>
+        <v>782</v>
       </c>
       <c r="I100">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="J100">
-        <v>19950</v>
+        <v>500</v>
       </c>
       <c r="K100" t="s">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="L100" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M100" t="s">
-        <v>419</v>
+        <v>83</v>
       </c>
       <c r="O100" t="s">
-        <v>420</v>
+        <v>11</v>
       </c>
       <c r="P100" t="s">
-        <v>745</v>
+        <v>240</v>
       </c>
       <c r="Q100" t="s">
-        <v>421</v>
+        <v>84</v>
       </c>
       <c r="R100" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S100" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T100" t="s">
-        <v>304</v>
+        <v>28</v>
       </c>
       <c r="U100" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>422</v>
+        <v>729</v>
       </c>
       <c r="B101" t="s">
-        <v>423</v>
+        <v>730</v>
       </c>
       <c r="C101" t="s">
-        <v>424</v>
+        <v>731</v>
       </c>
       <c r="D101" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E101" t="s">
-        <v>425</v>
+        <v>732</v>
       </c>
       <c r="G101" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H101">
-        <v>342</v>
+        <v>81452</v>
       </c>
       <c r="I101">
         <v>46296</v>
       </c>
       <c r="J101">
-        <v>1270.83</v>
+        <v>285</v>
       </c>
       <c r="K101" t="s">
-        <v>426</v>
+        <v>563</v>
       </c>
       <c r="L101" t="s">
-        <v>62</v>
-      </c>
-      <c r="M101" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="O101" t="s">
-        <v>333</v>
+        <v>564</v>
       </c>
       <c r="P101" t="s">
-        <v>334</v>
+        <v>565</v>
       </c>
       <c r="Q101" t="s">
-        <v>335</v>
+        <v>733</v>
       </c>
       <c r="R101" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S101" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T101" t="s">
-        <v>285</v>
+        <v>351</v>
       </c>
       <c r="U101" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>387</v>
+        <v>74</v>
       </c>
       <c r="B102" t="s">
-        <v>388</v>
+        <v>75</v>
       </c>
       <c r="C102" t="s">
-        <v>389</v>
+        <v>76</v>
       </c>
       <c r="D102" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E102" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G102" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H102">
-        <v>764</v>
+        <v>157417</v>
       </c>
       <c r="I102">
-        <v>46294</v>
+        <v>46283</v>
       </c>
       <c r="J102">
-        <v>500</v>
+        <v>199</v>
       </c>
       <c r="K102" t="s">
-        <v>261</v>
+        <v>78</v>
       </c>
       <c r="L102" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M102" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="O102" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="P102" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="Q102" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="R102" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S102" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T102" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U102" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
-        <v>390</v>
-      </c>
-      <c r="B103" t="s">
-        <v>391</v>
-      </c>
-      <c r="C103" t="s">
-        <v>392</v>
-      </c>
-      <c r="D103" t="s">
-        <v>59</v>
-      </c>
-      <c r="E103" t="s">
-        <v>82</v>
-      </c>
-      <c r="G103" t="s">
-        <v>60</v>
-      </c>
-      <c r="H103">
-        <v>762</v>
-      </c>
-      <c r="I103">
-        <v>46294</v>
-      </c>
-      <c r="J103">
-        <v>500</v>
-      </c>
-      <c r="K103" t="s">
-        <v>261</v>
-      </c>
-      <c r="L103" t="s">
-        <v>62</v>
-      </c>
-      <c r="M103" t="s">
-        <v>84</v>
-      </c>
-      <c r="O103" t="s">
-        <v>11</v>
-      </c>
-      <c r="P103" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q103" t="s">
-        <v>85</v>
-      </c>
-      <c r="R103" t="s">
-        <v>64</v>
-      </c>
-      <c r="S103" t="s">
-        <v>65</v>
-      </c>
-      <c r="T103" t="s">
-        <v>29</v>
-      </c>
-      <c r="U103" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
-        <v>427</v>
-      </c>
-      <c r="B104" t="s">
-        <v>428</v>
-      </c>
-      <c r="C104" t="s">
-        <v>429</v>
-      </c>
-      <c r="D104" t="s">
-        <v>59</v>
-      </c>
-      <c r="E104" t="s">
-        <v>82</v>
-      </c>
-      <c r="G104" t="s">
-        <v>60</v>
-      </c>
-      <c r="H104">
-        <v>761</v>
-      </c>
-      <c r="I104">
-        <v>46294</v>
-      </c>
-      <c r="J104">
-        <v>500</v>
-      </c>
-      <c r="K104" t="s">
-        <v>261</v>
-      </c>
-      <c r="L104" t="s">
-        <v>62</v>
-      </c>
-      <c r="M104" t="s">
-        <v>84</v>
-      </c>
-      <c r="O104" t="s">
-        <v>11</v>
-      </c>
-      <c r="P104" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q104" t="s">
-        <v>85</v>
-      </c>
-      <c r="R104" t="s">
-        <v>64</v>
-      </c>
-      <c r="S104" t="s">
-        <v>65</v>
-      </c>
-      <c r="T104" t="s">
-        <v>29</v>
-      </c>
-      <c r="U104" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
-        <v>190</v>
-      </c>
-      <c r="B105" t="s">
-        <v>191</v>
-      </c>
-      <c r="C105" t="s">
-        <v>192</v>
-      </c>
-      <c r="D105" t="s">
-        <v>59</v>
-      </c>
-      <c r="E105" t="s">
-        <v>193</v>
-      </c>
-      <c r="G105" t="s">
-        <v>60</v>
-      </c>
-      <c r="H105">
-        <v>203</v>
-      </c>
-      <c r="I105">
-        <v>46189</v>
-      </c>
-      <c r="J105">
-        <v>5280</v>
-      </c>
-      <c r="K105" t="s">
-        <v>194</v>
-      </c>
-      <c r="L105" t="s">
-        <v>62</v>
-      </c>
-      <c r="M105" t="s">
-        <v>84</v>
-      </c>
-      <c r="O105" t="s">
-        <v>7</v>
-      </c>
-      <c r="P105" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q105" t="s">
-        <v>195</v>
-      </c>
-      <c r="R105" t="s">
-        <v>64</v>
-      </c>
-      <c r="S105" t="s">
-        <v>65</v>
-      </c>
-      <c r="T105" t="s">
-        <v>6</v>
-      </c>
-      <c r="U105" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
-        <v>196</v>
-      </c>
-      <c r="B106" t="s">
-        <v>197</v>
-      </c>
-      <c r="C106" t="s">
-        <v>198</v>
-      </c>
-      <c r="D106" t="s">
-        <v>59</v>
-      </c>
-      <c r="E106" t="s">
-        <v>199</v>
-      </c>
-      <c r="G106" t="s">
-        <v>60</v>
-      </c>
-      <c r="H106">
-        <v>202</v>
-      </c>
-      <c r="I106">
-        <v>46189</v>
-      </c>
-      <c r="J106">
-        <v>16720</v>
-      </c>
-      <c r="K106" t="s">
-        <v>194</v>
-      </c>
-      <c r="L106" t="s">
-        <v>62</v>
-      </c>
-      <c r="M106" t="s">
-        <v>84</v>
-      </c>
-      <c r="O106" t="s">
-        <v>7</v>
-      </c>
-      <c r="P106" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q106" t="s">
-        <v>200</v>
-      </c>
-      <c r="R106" t="s">
-        <v>64</v>
-      </c>
-      <c r="S106" t="s">
-        <v>65</v>
-      </c>
-      <c r="T106" t="s">
-        <v>6</v>
-      </c>
-      <c r="U106" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>746</v>
-      </c>
-      <c r="B107" t="s">
-        <v>747</v>
-      </c>
-      <c r="C107" t="s">
-        <v>748</v>
-      </c>
-      <c r="D107" t="s">
-        <v>59</v>
-      </c>
-      <c r="E107" t="s">
-        <v>749</v>
-      </c>
-      <c r="G107" t="s">
-        <v>60</v>
-      </c>
-      <c r="H107">
-        <v>21395</v>
-      </c>
-      <c r="I107">
-        <v>46296</v>
-      </c>
-      <c r="J107">
-        <v>2800</v>
-      </c>
-      <c r="K107" t="s">
-        <v>750</v>
-      </c>
-      <c r="L107" t="s">
-        <v>62</v>
-      </c>
-      <c r="M107" t="s">
-        <v>332</v>
-      </c>
-      <c r="O107" t="s">
-        <v>621</v>
-      </c>
-      <c r="P107" t="s">
-        <v>622</v>
-      </c>
-      <c r="Q107" t="s">
-        <v>623</v>
-      </c>
-      <c r="R107" t="s">
-        <v>64</v>
-      </c>
-      <c r="S107" t="s">
-        <v>65</v>
-      </c>
-      <c r="T107" t="s">
-        <v>3</v>
-      </c>
-      <c r="U107" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>751</v>
-      </c>
-      <c r="B108" t="s">
-        <v>752</v>
-      </c>
-      <c r="C108" t="s">
-        <v>753</v>
-      </c>
-      <c r="D108" t="s">
-        <v>59</v>
-      </c>
-      <c r="E108" t="s">
-        <v>754</v>
-      </c>
-      <c r="G108" t="s">
-        <v>60</v>
-      </c>
-      <c r="H108">
-        <v>60958</v>
-      </c>
-      <c r="I108">
-        <v>46296</v>
-      </c>
-      <c r="J108">
-        <v>15.93</v>
-      </c>
-      <c r="K108" t="s">
-        <v>473</v>
-      </c>
-      <c r="L108" t="s">
-        <v>62</v>
-      </c>
-      <c r="M108" t="s">
-        <v>162</v>
-      </c>
-      <c r="O108" t="s">
-        <v>474</v>
-      </c>
-      <c r="P108" t="s">
-        <v>475</v>
-      </c>
-      <c r="Q108" t="s">
-        <v>476</v>
-      </c>
-      <c r="R108" t="s">
-        <v>64</v>
-      </c>
-      <c r="S108" t="s">
-        <v>65</v>
-      </c>
-      <c r="T108" t="s">
-        <v>477</v>
-      </c>
-      <c r="U108" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/INDUSTRIAL.xlsx
+++ b/INDUSTRIAL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GUDESCHA\Downloads\Dashaboard em HTML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE0AB2E5-8413-4BE3-8B70-D2B82002D662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9001832-045F-4770-890D-A8AE2B977953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{321EB0AA-E4FC-4001-873E-9150905088DA}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{44DC9A11-BE7F-4FE3-A10E-037954EFEE21}"/>
   </bookViews>
   <sheets>
     <sheet name="Client Resolution 9245 novo" sheetId="2" r:id="rId1"/>
@@ -19,8 +19,8 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Client Resolution 9245 novo'!$A$1:$U$73</definedName>
-    <definedName name="ExternalData_1" localSheetId="0">'Client Resolution 9245 novo'!$A$1:$T$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Client Resolution 9245 novo'!$A$1:$U$1</definedName>
+    <definedName name="ExternalData_1" localSheetId="0">'Client Resolution 9245 novo'!$A$1:$T$58</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="458">
   <si>
     <t>Fornecedor</t>
   </si>
@@ -66,195 +66,162 @@
     <t>Nelson Ferreira</t>
   </si>
   <si>
-    <t>B72869</t>
+    <t>B69881</t>
   </si>
   <si>
     <t>null</t>
   </si>
   <si>
-    <t>B69881</t>
-  </si>
-  <si>
-    <t>Glaucilaine Demarchi</t>
-  </si>
-  <si>
     <t>B72612</t>
   </si>
   <si>
-    <t>Thayna1 Rita</t>
+    <t>Joao Candido</t>
   </si>
   <si>
     <t>B71867</t>
   </si>
   <si>
-    <t>Joao Candido</t>
+    <t>Andreia Almeida</t>
   </si>
   <si>
     <t>B73114</t>
   </si>
   <si>
-    <t>Andreia Almeida</t>
+    <t>Francisco Noguti</t>
   </si>
   <si>
     <t>B72877</t>
   </si>
   <si>
-    <t>Francisco Noguti</t>
+    <t>Mauricio Valdivino</t>
   </si>
   <si>
     <t>B72530</t>
   </si>
   <si>
-    <t>Mauricio Valdivino</t>
+    <t>Adriano C Ferrari</t>
   </si>
   <si>
     <t>B61746</t>
   </si>
   <si>
-    <t>Adriano C Ferrari</t>
+    <t>Ana Beatriz Rodrigues</t>
+  </si>
+  <si>
+    <t>B72382</t>
+  </si>
+  <si>
+    <t>Camilla Barros</t>
+  </si>
+  <si>
+    <t>B73359</t>
+  </si>
+  <si>
+    <t>Daniel Menezes</t>
+  </si>
+  <si>
+    <t>B73113</t>
+  </si>
+  <si>
+    <t>Mauricio Santos</t>
+  </si>
+  <si>
+    <t>B73255</t>
+  </si>
+  <si>
+    <t>Geane Lana Garcia Silva</t>
+  </si>
+  <si>
+    <t>B71659</t>
+  </si>
+  <si>
+    <t>Thalles Miranda</t>
+  </si>
+  <si>
+    <t>B72214</t>
+  </si>
+  <si>
+    <t>Paula Carvalho</t>
+  </si>
+  <si>
+    <t>B70582</t>
+  </si>
+  <si>
+    <t>Amanda Lima</t>
+  </si>
+  <si>
+    <t>B73179</t>
+  </si>
+  <si>
+    <t>Allana Fernandes</t>
+  </si>
+  <si>
+    <t>B69098</t>
+  </si>
+  <si>
+    <t>Viviane Silva</t>
+  </si>
+  <si>
+    <t>B73051</t>
+  </si>
+  <si>
+    <t>Thais Piantoni</t>
+  </si>
+  <si>
+    <t>B72593</t>
+  </si>
+  <si>
+    <t>Jessica de Carvalho</t>
+  </si>
+  <si>
+    <t>B67827</t>
+  </si>
+  <si>
+    <t>B72179</t>
+  </si>
+  <si>
+    <t>B72711</t>
+  </si>
+  <si>
+    <t>DIALOG DESENVOLVIMENTO E LICENCIAMENTO DE SOFTWARE, TECNOLOGI</t>
+  </si>
+  <si>
+    <t>B73232</t>
+  </si>
+  <si>
+    <t>B71225</t>
+  </si>
+  <si>
+    <t>B66381</t>
+  </si>
+  <si>
+    <t>B73214</t>
+  </si>
+  <si>
+    <t>B66385</t>
+  </si>
+  <si>
+    <t>B73360</t>
+  </si>
+  <si>
+    <t>B72039</t>
   </si>
   <si>
     <t>B73029</t>
   </si>
   <si>
-    <t>Ana Beatriz Rodrigues</t>
-  </si>
-  <si>
-    <t>B73208</t>
-  </si>
-  <si>
-    <t>Camilla Barros</t>
-  </si>
-  <si>
-    <t>B71473</t>
-  </si>
-  <si>
-    <t>Daniel Menezes</t>
-  </si>
-  <si>
-    <t>B72854</t>
-  </si>
-  <si>
-    <t>Rafaela Alves</t>
-  </si>
-  <si>
-    <t>B67827</t>
-  </si>
-  <si>
-    <t>Mauricio Santos</t>
-  </si>
-  <si>
-    <t>B72382</t>
-  </si>
-  <si>
-    <t>Geane Lana Garcia Silva</t>
-  </si>
-  <si>
-    <t>B73359</t>
-  </si>
-  <si>
-    <t>Thalles Miranda</t>
-  </si>
-  <si>
-    <t>B73113</t>
-  </si>
-  <si>
-    <t>Paula Carvalho</t>
-  </si>
-  <si>
-    <t>B66385</t>
-  </si>
-  <si>
-    <t>Amanda Lima</t>
-  </si>
-  <si>
-    <t>B73291</t>
-  </si>
-  <si>
-    <t>Rafael Lucena</t>
-  </si>
-  <si>
-    <t>B71726</t>
-  </si>
-  <si>
-    <t>Jessica de Carvalho</t>
-  </si>
-  <si>
-    <t>B73255</t>
-  </si>
-  <si>
-    <t>Allana Fernandes</t>
-  </si>
-  <si>
-    <t>B71659</t>
-  </si>
-  <si>
-    <t>B73138</t>
-  </si>
-  <si>
-    <t>B73280</t>
-  </si>
-  <si>
-    <t>B72298</t>
-  </si>
-  <si>
-    <t>B70582</t>
-  </si>
-  <si>
-    <t>B73179</t>
-  </si>
-  <si>
-    <t>B73214</t>
-  </si>
-  <si>
-    <t>B72040</t>
-  </si>
-  <si>
-    <t>B71225</t>
-  </si>
-  <si>
-    <t>B73051</t>
-  </si>
-  <si>
-    <t>B72593</t>
-  </si>
-  <si>
-    <t>B73360</t>
-  </si>
-  <si>
-    <t>B72039</t>
-  </si>
-  <si>
-    <t>B69098</t>
-  </si>
-  <si>
-    <t>B72216</t>
-  </si>
-  <si>
-    <t>B71339</t>
-  </si>
-  <si>
-    <t>B72214</t>
-  </si>
-  <si>
-    <t>B73232</t>
-  </si>
-  <si>
-    <t>DIALOG DESENVOLVIMENTO E LICENCIAMENTO DE SOFTWARE, TECNOLOGI</t>
-  </si>
-  <si>
     <t>31861323000527</t>
   </si>
   <si>
+    <t>STOCCO ESCULTURAS LTDA ME</t>
+  </si>
+  <si>
+    <t>36380366000180</t>
+  </si>
+  <si>
     <t>ROBSON GODOI SOLUCOES EMPRESARIAIS EIRELI</t>
   </si>
   <si>
-    <t>36380366000180</t>
-  </si>
-  <si>
-    <t>STOCCO ESCULTURAS LTDA ME</t>
-  </si>
-  <si>
     <t>ASV Ref Id</t>
   </si>
   <si>
@@ -354,28 +321,820 @@
     <t>Aprovar serviço</t>
   </si>
   <si>
-    <t>SKFAPE202610051212050958</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85855742PO</t>
-  </si>
-  <si>
-    <t>2026-10-05 12:12:06.077</t>
-  </si>
-  <si>
-    <t>2784.07</t>
-  </si>
-  <si>
-    <t>06999230000192&amp;18/10/2026</t>
+    <t>SKFAPE202610231825570463</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85873407PO</t>
+  </si>
+  <si>
+    <t>2026-10-23 18:25:57.597</t>
+  </si>
+  <si>
+    <t>109446.07</t>
+  </si>
+  <si>
+    <t>116618,08</t>
+  </si>
+  <si>
+    <t>49928567000111&amp;NA</t>
+  </si>
+  <si>
+    <t>17.16</t>
+  </si>
+  <si>
+    <t>EP1801283</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051214530968</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855754PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:14:53.583</t>
+  </si>
+  <si>
+    <t>5400.00</t>
+  </si>
+  <si>
+    <t>19660635000143&amp;NA</t>
+  </si>
+  <si>
+    <t>17.02</t>
+  </si>
+  <si>
+    <t>EP1802978</t>
+  </si>
+  <si>
+    <t>SKFAPE202606221512250742</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85764388PO</t>
+  </si>
+  <si>
+    <t>2026-06-22 15:12:25.693</t>
+  </si>
+  <si>
+    <t>1928.00</t>
+  </si>
+  <si>
+    <t>1928,00</t>
+  </si>
+  <si>
+    <t>31861323000527&amp;01/07/2026&amp;</t>
+  </si>
+  <si>
+    <t>EP1737982</t>
+  </si>
+  <si>
+    <t>ReAssigned</t>
+  </si>
+  <si>
+    <t>SKFAPE202610192015080470</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85868677PO</t>
+  </si>
+  <si>
+    <t>2026-10-19 20:15:08.553</t>
+  </si>
+  <si>
+    <t>892.40</t>
+  </si>
+  <si>
+    <t>892,40</t>
+  </si>
+  <si>
+    <t>00845661000703&amp;13/01/2027</t>
+  </si>
+  <si>
+    <t>EP1804973</t>
+  </si>
+  <si>
+    <t>SKFAPE202610192015280471</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85868678PO</t>
+  </si>
+  <si>
+    <t>2026-10-19 20:15:28.977</t>
+  </si>
+  <si>
+    <t>446.20</t>
+  </si>
+  <si>
+    <t>446,20</t>
+  </si>
+  <si>
+    <t>EP1761513</t>
+  </si>
+  <si>
+    <t>SKFAPE202610151914270417</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85866314PO</t>
+  </si>
+  <si>
+    <t>2026-10-15 19:14:27.67</t>
+  </si>
+  <si>
+    <t>1105.00</t>
+  </si>
+  <si>
+    <t>04911895000177&amp;NA</t>
+  </si>
+  <si>
+    <t>17.06</t>
+  </si>
+  <si>
+    <t>EP1778402</t>
+  </si>
+  <si>
+    <t>SKFAPE202610231211350370</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85873074PO</t>
+  </si>
+  <si>
+    <t>2026-10-23 12:11:35.327</t>
+  </si>
+  <si>
+    <t>5063.99</t>
+  </si>
+  <si>
+    <t>5063,99</t>
+  </si>
+  <si>
+    <t>03857930001479&amp;31/01/2027</t>
+  </si>
+  <si>
+    <t>EP1808148</t>
+  </si>
+  <si>
+    <t>SKFAPE202610231211560371</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85873077PO</t>
+  </si>
+  <si>
+    <t>2026-10-23 12:11:56.34</t>
+  </si>
+  <si>
+    <t>3826.44</t>
+  </si>
+  <si>
+    <t>3826,44</t>
+  </si>
+  <si>
+    <t>SKFAPE202610231212160372</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85873080PO</t>
+  </si>
+  <si>
+    <t>2026-10-23 12:12:16.587</t>
+  </si>
+  <si>
+    <t>2023.24</t>
+  </si>
+  <si>
+    <t>2023,24</t>
+  </si>
+  <si>
+    <t>SKFAPE202610231212500373</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85873083PO</t>
+  </si>
+  <si>
+    <t>2026-10-23 12:12:50.947</t>
+  </si>
+  <si>
+    <t>112849.88</t>
+  </si>
+  <si>
+    <t>112849,88</t>
+  </si>
+  <si>
+    <t>SKFAPE202610191857290457</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85868640PO</t>
+  </si>
+  <si>
+    <t>2026-10-19 18:57:29.333</t>
+  </si>
+  <si>
+    <t>3500.00</t>
+  </si>
+  <si>
+    <t>08998192000189&amp;NA</t>
+  </si>
+  <si>
+    <t>40.01</t>
+  </si>
+  <si>
+    <t>EP1808670</t>
+  </si>
+  <si>
+    <t>SKFAPE202606172025160726</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85761153PO</t>
+  </si>
+  <si>
+    <t>2026-06-17 20:25:16.883</t>
+  </si>
+  <si>
+    <t>5280.00</t>
+  </si>
+  <si>
+    <t>5280,00</t>
+  </si>
+  <si>
+    <t>13182443000273&amp;NA&amp;</t>
   </si>
   <si>
     <t>17.01</t>
   </si>
   <si>
-    <t>EP1802943</t>
-  </si>
-  <si>
-    <t>ReAssigned</t>
+    <t>P120097</t>
+  </si>
+  <si>
+    <t>SKFAPE202606172025360727</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85761154PO</t>
+  </si>
+  <si>
+    <t>2026-06-17 20:25:36.37</t>
+  </si>
+  <si>
+    <t>16720.00</t>
+  </si>
+  <si>
+    <t>16720,00</t>
+  </si>
+  <si>
+    <t>P116642</t>
+  </si>
+  <si>
+    <t>SKFAPE202606221231260718</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85764188PO</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:31:27.107</t>
+  </si>
+  <si>
+    <t>4897.41</t>
+  </si>
+  <si>
+    <t>5136,25</t>
+  </si>
+  <si>
+    <t>00973749000891&amp;NA&amp;</t>
+  </si>
+  <si>
+    <t>07.10</t>
+  </si>
+  <si>
+    <t>EP1760114</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051224340104</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855793PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:24:35.023</t>
+  </si>
+  <si>
+    <t>8521.46</t>
+  </si>
+  <si>
+    <t>8521,46</t>
+  </si>
+  <si>
+    <t>62173620009306&amp;NA&amp;</t>
+  </si>
+  <si>
+    <t>Pedido não informado</t>
+  </si>
+  <si>
+    <t>SKFAPE202610051225190107</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85855796PO</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:25:19.22</t>
+  </si>
+  <si>
+    <t>26584.71</t>
+  </si>
+  <si>
+    <t>26584,71</t>
+  </si>
+  <si>
+    <t>12237752000150&amp;21/08/2026&amp;5005</t>
+  </si>
+  <si>
+    <t>EP1780835</t>
+  </si>
+  <si>
+    <t>SKFAPE202610151913060413</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85866310PO</t>
+  </si>
+  <si>
+    <t>2026-10-15 19:13:06.693</t>
+  </si>
+  <si>
+    <t>511.93</t>
+  </si>
+  <si>
+    <t>511,93</t>
+  </si>
+  <si>
+    <t>15168902000109&amp;10/11/2026</t>
+  </si>
+  <si>
+    <t>SKFAPE202609011505250264</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85826472PO</t>
+  </si>
+  <si>
+    <t>2026-09-01 15:05:25.78</t>
+  </si>
+  <si>
+    <t>469.25</t>
+  </si>
+  <si>
+    <t>09059224000224&amp;NA</t>
+  </si>
+  <si>
+    <t>EP1734627</t>
+  </si>
+  <si>
+    <t>SKFAPE202609011506050266</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85826475PO</t>
+  </si>
+  <si>
+    <t>2026-09-01 15:06:05.7</t>
+  </si>
+  <si>
+    <t>SKFAPE202610211930330536</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85871120PO</t>
+  </si>
+  <si>
+    <t>2026-10-21 19:30:33.72</t>
+  </si>
+  <si>
+    <t>50714.50</t>
+  </si>
+  <si>
+    <t>50714,50</t>
+  </si>
+  <si>
+    <t>EP1670931</t>
+  </si>
+  <si>
+    <t>SKFAPE202607201424280391</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85788978PO</t>
+  </si>
+  <si>
+    <t>2026-07-20 14:24:28.657</t>
+  </si>
+  <si>
+    <t>560.28</t>
+  </si>
+  <si>
+    <t>560,28</t>
+  </si>
+  <si>
+    <t>03774819006054&amp;20/10/2026</t>
+  </si>
+  <si>
+    <t>17.09</t>
+  </si>
+  <si>
+    <t>EP1753582</t>
+  </si>
+  <si>
+    <t>SKFAPE202610101358530193</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85861394PO</t>
+  </si>
+  <si>
+    <t>2026-10-10 13:58:53.877</t>
+  </si>
+  <si>
+    <t>4482.20</t>
+  </si>
+  <si>
+    <t>4482,20</t>
+  </si>
+  <si>
+    <t>36380366000180&amp;09/12/2026&amp;9001</t>
+  </si>
+  <si>
+    <t>EP1701877</t>
+  </si>
+  <si>
+    <t>SKFAPE202610231825170461</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85873405PO</t>
+  </si>
+  <si>
+    <t>2026-10-23 18:25:17.2</t>
+  </si>
+  <si>
+    <t>121317.75</t>
+  </si>
+  <si>
+    <t>121317,75</t>
+  </si>
+  <si>
+    <t>43637214000186&amp;21/10/2026</t>
+  </si>
+  <si>
+    <t>EP1755433</t>
+  </si>
+  <si>
+    <t>SKFAPE202610151928240419</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85866329PO</t>
+  </si>
+  <si>
+    <t>2026-10-15 19:28:24.923</t>
+  </si>
+  <si>
+    <t>8103.84</t>
+  </si>
+  <si>
+    <t>8103,84</t>
+  </si>
+  <si>
+    <t>15168902000109&amp;06/11/2026</t>
+  </si>
+  <si>
+    <t>SKFAPE202610151928450420</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85866330PO</t>
+  </si>
+  <si>
+    <t>2026-10-15 19:28:45.337</t>
+  </si>
+  <si>
+    <t>8726.94</t>
+  </si>
+  <si>
+    <t>8726,94</t>
+  </si>
+  <si>
+    <t>SKFAPE202610201301370696</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85869352PO</t>
+  </si>
+  <si>
+    <t>2026-10-20 13:01:37.207</t>
+  </si>
+  <si>
+    <t>18573.30</t>
+  </si>
+  <si>
+    <t>18573,30</t>
+  </si>
+  <si>
+    <t>08640510001700&amp;NA</t>
+  </si>
+  <si>
+    <t>11.04</t>
+  </si>
+  <si>
+    <t>EP1811895</t>
+  </si>
+  <si>
+    <t>SKFAPE202610201302580697</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85869353PO</t>
+  </si>
+  <si>
+    <t>2026-10-20 13:02:58.557</t>
+  </si>
+  <si>
+    <t>87.25</t>
+  </si>
+  <si>
+    <t>87,25</t>
+  </si>
+  <si>
+    <t>EP1811894</t>
+  </si>
+  <si>
+    <t>SKFAPE202610201303460700</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85869356PO</t>
+  </si>
+  <si>
+    <t>2026-10-20 13:03:47.033</t>
+  </si>
+  <si>
+    <t>7038.75</t>
+  </si>
+  <si>
+    <t>13182443000273&amp;NA</t>
+  </si>
+  <si>
+    <t>P113724</t>
+  </si>
+  <si>
+    <t>SKFAPE202610201304130702</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85869358PO</t>
+  </si>
+  <si>
+    <t>2026-10-20 13:04:14.007</t>
+  </si>
+  <si>
+    <t>176.46</t>
+  </si>
+  <si>
+    <t>176,46</t>
+  </si>
+  <si>
+    <t>48109110000112&amp;14/12/2026</t>
+  </si>
+  <si>
+    <t>EP1813328</t>
+  </si>
+  <si>
+    <t>SKFAPE202610201305370706</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85869362PO</t>
+  </si>
+  <si>
+    <t>2026-10-20 13:05:37.407</t>
+  </si>
+  <si>
+    <t>33474.02</t>
+  </si>
+  <si>
+    <t>33474,02</t>
+  </si>
+  <si>
+    <t>08640510001700&amp;18/11/2026</t>
+  </si>
+  <si>
+    <t>SKFAPE202610201549110805</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85869598PO</t>
+  </si>
+  <si>
+    <t>2026-10-20 15:49:11.407</t>
+  </si>
+  <si>
+    <t>9325.00</t>
+  </si>
+  <si>
+    <t>36532863000157&amp;25/12/2026</t>
+  </si>
+  <si>
+    <t>08.02</t>
+  </si>
+  <si>
+    <t>EP1761510</t>
+  </si>
+  <si>
+    <t>SKFAPE202610211347290438</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85870792PO</t>
+  </si>
+  <si>
+    <t>2026-10-21 13:47:29.277</t>
+  </si>
+  <si>
+    <t>20357.22</t>
+  </si>
+  <si>
+    <t>12017507000137&amp;19/11/2026&amp;</t>
+  </si>
+  <si>
+    <t>EP1814004</t>
+  </si>
+  <si>
+    <t>SKFAPE202610211347490439</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85870793PO</t>
+  </si>
+  <si>
+    <t>2026-10-21 13:47:49.433</t>
+  </si>
+  <si>
+    <t>3654.25</t>
+  </si>
+  <si>
+    <t>3654,25</t>
+  </si>
+  <si>
+    <t>11314113000188&amp;18/11/2026&amp;5005</t>
+  </si>
+  <si>
+    <t>EP1802975</t>
+  </si>
+  <si>
+    <t>SKFAPE202610231825370462</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85873406PO</t>
+  </si>
+  <si>
+    <t>2026-10-23 18:25:37.477</t>
+  </si>
+  <si>
+    <t>1360.00</t>
+  </si>
+  <si>
+    <t>20549570000142&amp;21/12/2026</t>
+  </si>
+  <si>
+    <t>EP1814433</t>
+  </si>
+  <si>
+    <t>SKFAPE202608121232060524</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85810235PO</t>
+  </si>
+  <si>
+    <t>2026-08-12 12:32:06.887</t>
+  </si>
+  <si>
+    <t>700216.08</t>
+  </si>
+  <si>
+    <t>746101,35</t>
+  </si>
+  <si>
+    <t>02833315000579&amp;09/10/2026&amp;9123</t>
+  </si>
+  <si>
+    <t>01.01</t>
+  </si>
+  <si>
+    <t>EP1759012</t>
+  </si>
+  <si>
+    <t>SKFAPE202609091247220128</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85833497PO</t>
+  </si>
+  <si>
+    <t>2026-09-09 12:47:22.8</t>
+  </si>
+  <si>
+    <t>330986.02</t>
+  </si>
+  <si>
+    <t>330986,02</t>
+  </si>
+  <si>
+    <t>02833315000579&amp;02/11/2026&amp;9123</t>
+  </si>
+  <si>
+    <t>01.03</t>
+  </si>
+  <si>
+    <t>SKFAPE202610142005120967</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85865283PO</t>
+  </si>
+  <si>
+    <t>2026-10-14 20:05:12.743</t>
+  </si>
+  <si>
+    <t>20412.48</t>
+  </si>
+  <si>
+    <t>21750,11</t>
+  </si>
+  <si>
+    <t>02833315000579&amp;05/12/2026&amp;9123</t>
+  </si>
+  <si>
+    <t>01.07</t>
+  </si>
+  <si>
+    <t>SKFAPE202610141219000664</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85864647PO</t>
+  </si>
+  <si>
+    <t>2026-10-14 12:19:00.777</t>
+  </si>
+  <si>
+    <t>580.00</t>
+  </si>
+  <si>
+    <t>20549570000142&amp;NA&amp;5810</t>
+  </si>
+  <si>
+    <t>26.01</t>
+  </si>
+  <si>
+    <t>EP1672893</t>
+  </si>
+  <si>
+    <t>SKFAPE202609041641030888</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85830580PO</t>
+  </si>
+  <si>
+    <t>2026-09-04 16:41:03.5</t>
+  </si>
+  <si>
+    <t>2625.57</t>
+  </si>
+  <si>
+    <t>18694139000148&amp;NA</t>
+  </si>
+  <si>
+    <t>17.10</t>
+  </si>
+  <si>
+    <t>EP1759004</t>
+  </si>
+  <si>
+    <t>SKFAPE202608311931510712</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85825337PO</t>
+  </si>
+  <si>
+    <t>2026-08-31 19:31:51.463</t>
+  </si>
+  <si>
+    <t>910.33</t>
+  </si>
+  <si>
+    <t>969,98</t>
+  </si>
+  <si>
+    <t>07589942000104&amp;NA</t>
+  </si>
+  <si>
+    <t>33.01</t>
+  </si>
+  <si>
+    <t>EP1762183</t>
+  </si>
+  <si>
+    <t>SKFAPE202609041348390846</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85830427PO</t>
+  </si>
+  <si>
+    <t>2026-09-04 13:48:39.54</t>
+  </si>
+  <si>
+    <t>270515.57</t>
+  </si>
+  <si>
+    <t>270515,57</t>
+  </si>
+  <si>
+    <t>03519007000102&amp;30/11/2026</t>
+  </si>
+  <si>
+    <t>EP1457750</t>
   </si>
   <si>
     <t>SKFAPE202609041641230889</t>
@@ -399,6 +1158,192 @@
     <t>EP1786734</t>
   </si>
   <si>
+    <t>SKFAPE202610142003510963</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85865279PO</t>
+  </si>
+  <si>
+    <t>2026-10-14 20:03:51.403</t>
+  </si>
+  <si>
+    <t>572291.44</t>
+  </si>
+  <si>
+    <t>609793,75</t>
+  </si>
+  <si>
+    <t>02833315000579&amp;01/12/2026&amp;9123</t>
+  </si>
+  <si>
+    <t>SKFAPE202610142003160962</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85865277PO</t>
+  </si>
+  <si>
+    <t>2026-10-14 20:03:16.17</t>
+  </si>
+  <si>
+    <t>195781.06</t>
+  </si>
+  <si>
+    <t>195781,06</t>
+  </si>
+  <si>
+    <t>SKFAPE202606221512160740</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85764386PO</t>
+  </si>
+  <si>
+    <t>2026-06-22 15:12:17.017</t>
+  </si>
+  <si>
+    <t>1314.09</t>
+  </si>
+  <si>
+    <t>1314,09</t>
+  </si>
+  <si>
+    <t>31861323000527&amp;08/05/2026&amp;</t>
+  </si>
+  <si>
+    <t>SKFAPE202606221512210741</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85764387PO</t>
+  </si>
+  <si>
+    <t>2026-06-22 15:12:21.343</t>
+  </si>
+  <si>
+    <t>1678.60</t>
+  </si>
+  <si>
+    <t>1678,60</t>
+  </si>
+  <si>
+    <t>31861323000527&amp;01/06/2026&amp;</t>
+  </si>
+  <si>
+    <t>SKFAPE202610142007450976</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85865292PO</t>
+  </si>
+  <si>
+    <t>2026-10-14 20:07:46.28</t>
+  </si>
+  <si>
+    <t>10366.20</t>
+  </si>
+  <si>
+    <t>10366,20</t>
+  </si>
+  <si>
+    <t>33449007000144&amp;NA&amp;9001</t>
+  </si>
+  <si>
+    <t>17.05</t>
+  </si>
+  <si>
+    <t>EP1796483</t>
+  </si>
+  <si>
+    <t>SKFAPE202610211347540440</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85870794PO</t>
+  </si>
+  <si>
+    <t>2026-10-21 13:47:54.88</t>
+  </si>
+  <si>
+    <t>38635.44</t>
+  </si>
+  <si>
+    <t>41167,23</t>
+  </si>
+  <si>
+    <t>58069360000120&amp;19/12/2026&amp;9105</t>
+  </si>
+  <si>
+    <t>EP1778552</t>
+  </si>
+  <si>
+    <t>SKFAPE202610101357540190</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85861391PO</t>
+  </si>
+  <si>
+    <t>2026-10-10 13:57:54.667</t>
+  </si>
+  <si>
+    <t>16758.10</t>
+  </si>
+  <si>
+    <t>02633186000141&amp;07/01/2026&amp;</t>
+  </si>
+  <si>
+    <t>EP1662798</t>
+  </si>
+  <si>
+    <t>SKFAPE202608171932270470</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85813366PO</t>
+  </si>
+  <si>
+    <t>2026-08-17 19:32:28.06</t>
+  </si>
+  <si>
+    <t>719.00</t>
+  </si>
+  <si>
+    <t>21071712000171&amp;NA&amp;7506</t>
+  </si>
+  <si>
+    <t>01.05</t>
+  </si>
+  <si>
+    <t>EP1660441</t>
+  </si>
+  <si>
+    <t>SKFAPE202610061246560471</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85856949PO</t>
+  </si>
+  <si>
+    <t>2026-10-06 12:46:56.177</t>
+  </si>
+  <si>
+    <t>4860.00</t>
+  </si>
+  <si>
+    <t>07312805000110&amp;04/11/2026</t>
+  </si>
+  <si>
+    <t>14.01</t>
+  </si>
+  <si>
+    <t>EP1798662</t>
+  </si>
+  <si>
+    <t>SKFAPE202610081331370300</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9245L85859507PO</t>
+  </si>
+  <si>
+    <t>2026-10-08 13:31:38.03</t>
+  </si>
+  <si>
+    <t>EP1802976</t>
+  </si>
+  <si>
     <t>SKFAPE202609111730160780</t>
   </si>
   <si>
@@ -411,6 +1356,9 @@
     <t>3770.93</t>
   </si>
   <si>
+    <t>3770,93</t>
+  </si>
+  <si>
     <t>34010457000107&amp;NA</t>
   </si>
   <si>
@@ -420,832 +1368,22 @@
     <t>EP1795564</t>
   </si>
   <si>
-    <t>SKFAPE202610051214530968</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85855754PO</t>
-  </si>
-  <si>
-    <t>2026-10-05 12:14:53.583</t>
-  </si>
-  <si>
-    <t>5400.00</t>
-  </si>
-  <si>
-    <t>19660635000143&amp;NA</t>
-  </si>
-  <si>
-    <t>17.02</t>
-  </si>
-  <si>
-    <t>EP1802978</t>
-  </si>
-  <si>
-    <t>SKFAPE202610081331370300</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85859507PO</t>
-  </si>
-  <si>
-    <t>2026-10-08 13:31:38.03</t>
-  </si>
-  <si>
-    <t>3500.00</t>
-  </si>
-  <si>
-    <t>04911895000177&amp;NA</t>
-  </si>
-  <si>
-    <t>17.06</t>
-  </si>
-  <si>
-    <t>EP1802976</t>
-  </si>
-  <si>
-    <t>SKFAPE202606221512250742</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85764388PO</t>
-  </si>
-  <si>
-    <t>2026-06-22 15:12:25.693</t>
-  </si>
-  <si>
-    <t>1928.00</t>
-  </si>
-  <si>
-    <t>31861323000527&amp;01/07/2026&amp;</t>
-  </si>
-  <si>
-    <t>EP1737982</t>
-  </si>
-  <si>
-    <t>SKFAPE202610192015080470</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85868677PO</t>
-  </si>
-  <si>
-    <t>2026-10-19 20:15:08.553</t>
-  </si>
-  <si>
-    <t>892.40</t>
-  </si>
-  <si>
-    <t>00845661000703&amp;13/01/2027</t>
-  </si>
-  <si>
-    <t>EP1804973</t>
-  </si>
-  <si>
-    <t>SKFAPE202610192015280471</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85868678PO</t>
-  </si>
-  <si>
-    <t>2026-10-19 20:15:28.977</t>
-  </si>
-  <si>
-    <t>446.20</t>
-  </si>
-  <si>
-    <t>EP1761513</t>
-  </si>
-  <si>
-    <t>SKFAPE202610151914270417</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85866314PO</t>
-  </si>
-  <si>
-    <t>2026-10-15 19:14:27.67</t>
-  </si>
-  <si>
-    <t>1105.00</t>
-  </si>
-  <si>
-    <t>EP1778402</t>
-  </si>
-  <si>
-    <t>SKFAPE202610211930330536</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85871120PO</t>
-  </si>
-  <si>
-    <t>2026-10-21 19:30:33.72</t>
-  </si>
-  <si>
-    <t>50714.50</t>
-  </si>
-  <si>
-    <t>15168902000109&amp;10/11/2026</t>
-  </si>
-  <si>
-    <t>EP1670931</t>
-  </si>
-  <si>
-    <t>SKFAPE202607201424280391</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85788978PO</t>
-  </si>
-  <si>
-    <t>2026-07-20 14:24:28.657</t>
-  </si>
-  <si>
-    <t>560.28</t>
-  </si>
-  <si>
-    <t>03774819006054&amp;20/10/2026</t>
-  </si>
-  <si>
-    <t>17.09</t>
-  </si>
-  <si>
-    <t>EP1753582</t>
-  </si>
-  <si>
-    <t>SKFAPE202610061248240477</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85856955PO</t>
-  </si>
-  <si>
-    <t>2026-10-06 12:48:24.367</t>
-  </si>
-  <si>
-    <t>11000.00</t>
-  </si>
-  <si>
-    <t>31980223000196&amp;NA</t>
-  </si>
-  <si>
-    <t>01.03</t>
-  </si>
-  <si>
-    <t>EP1786099</t>
-  </si>
-  <si>
-    <t>SKFAPE202610081330430298</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85859505PO</t>
-  </si>
-  <si>
-    <t>2026-10-08 13:30:43.32</t>
-  </si>
-  <si>
-    <t>231.47</t>
-  </si>
-  <si>
-    <t>03774819006054&amp;08/01/2027</t>
-  </si>
-  <si>
-    <t>EP1806333</t>
-  </si>
-  <si>
-    <t>SKFAPE202610081857480367</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85859769PO</t>
-  </si>
-  <si>
-    <t>2026-10-08 18:57:48.803</t>
-  </si>
-  <si>
-    <t>5591.92</t>
-  </si>
-  <si>
-    <t>01382559000196&amp;NA</t>
-  </si>
-  <si>
-    <t>14.01</t>
-  </si>
-  <si>
-    <t>EP1735732</t>
-  </si>
-  <si>
-    <t>SKFAPE202610081858280369</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85859771PO</t>
-  </si>
-  <si>
-    <t>2026-10-08 18:58:28.937</t>
-  </si>
-  <si>
-    <t>532.66</t>
-  </si>
-  <si>
-    <t>EP1805805</t>
-  </si>
-  <si>
-    <t>SKFAPE202610141215260651</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85864634PO</t>
-  </si>
-  <si>
-    <t>2026-10-14 12:15:26.22</t>
-  </si>
-  <si>
-    <t>952.33</t>
-  </si>
-  <si>
-    <t>03774819006054&amp;NA&amp;8024</t>
-  </si>
-  <si>
-    <t>EP1807061</t>
-  </si>
-  <si>
-    <t>SKFAPE202610101358530193</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85861394PO</t>
-  </si>
-  <si>
-    <t>2026-10-10 13:58:53.877</t>
-  </si>
-  <si>
-    <t>4482.20</t>
-  </si>
-  <si>
-    <t>36380366000180&amp;09/12/2026&amp;9001</t>
-  </si>
-  <si>
-    <t>EP1701877</t>
-  </si>
-  <si>
-    <t>SKFAPM202610221714200900</t>
-  </si>
-  <si>
-    <t>2026-10-22 17:14:55.713</t>
-  </si>
-  <si>
-    <t>22865.14</t>
-  </si>
-  <si>
-    <t>176&amp;01</t>
-  </si>
-  <si>
-    <t>41420915000133&amp;NA</t>
-  </si>
-  <si>
-    <t>EP1702648</t>
-  </si>
-  <si>
-    <t>SKFAPE202610201303190698</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85869354PO</t>
-  </si>
-  <si>
-    <t>2026-10-20 13:03:19.737</t>
-  </si>
-  <si>
-    <t>513009.00</t>
-  </si>
-  <si>
-    <t>08640510001700&amp;NA</t>
-  </si>
-  <si>
-    <t>11.04</t>
-  </si>
-  <si>
-    <t>EP1698688</t>
-  </si>
-  <si>
-    <t>SKFAPE202610201303260699</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85869355PO</t>
-  </si>
-  <si>
-    <t>2026-10-20 13:03:26.553</t>
-  </si>
-  <si>
-    <t>82634.96</t>
-  </si>
-  <si>
-    <t>SKFAPE202610201303530701</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85869357PO</t>
-  </si>
-  <si>
-    <t>2026-10-20 13:03:53.733</t>
-  </si>
-  <si>
-    <t>5000.00</t>
-  </si>
-  <si>
-    <t>14166914000131&amp;NA</t>
-  </si>
-  <si>
-    <t>EP1674864</t>
-  </si>
-  <si>
-    <t>SKFAPE202610201304340703</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85869359PO</t>
-  </si>
-  <si>
-    <t>2026-10-20 13:04:34.4</t>
-  </si>
-  <si>
-    <t>72500.00</t>
-  </si>
-  <si>
-    <t>EP1677398</t>
-  </si>
-  <si>
-    <t>SKFAPE202610201304550704</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85869360PO</t>
-  </si>
-  <si>
-    <t>2026-10-20 13:04:55.887</t>
-  </si>
-  <si>
-    <t>227050.00</t>
-  </si>
-  <si>
-    <t>SKFAPE202608171932270470</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85813366PO</t>
-  </si>
-  <si>
-    <t>2026-08-17 19:32:28.06</t>
-  </si>
-  <si>
-    <t>719.00</t>
-  </si>
-  <si>
-    <t>21071712000171&amp;NA&amp;7506</t>
-  </si>
-  <si>
-    <t>01.05</t>
-  </si>
-  <si>
-    <t>EP1660441</t>
-  </si>
-  <si>
-    <t>SKFAPE202606172025160726</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85761153PO</t>
-  </si>
-  <si>
-    <t>2026-06-17 20:25:16.883</t>
-  </si>
-  <si>
-    <t>5280.00</t>
-  </si>
-  <si>
-    <t>13182443000273&amp;NA&amp;</t>
-  </si>
-  <si>
-    <t>P120097</t>
-  </si>
-  <si>
-    <t>SKFAPE202606172025360727</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85761154PO</t>
-  </si>
-  <si>
-    <t>2026-06-17 20:25:36.37</t>
-  </si>
-  <si>
-    <t>16720.00</t>
-  </si>
-  <si>
-    <t>P116642</t>
-  </si>
-  <si>
-    <t>SKFAPE202606221231260718</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85764188PO</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:31:27.107</t>
-  </si>
-  <si>
-    <t>4897.41</t>
-  </si>
-  <si>
-    <t>00973749000891&amp;NA&amp;</t>
-  </si>
-  <si>
-    <t>07.10</t>
-  </si>
-  <si>
-    <t>EP1760114</t>
-  </si>
-  <si>
-    <t>SKFAPE202610051224340104</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85855793PO</t>
-  </si>
-  <si>
-    <t>2026-10-05 12:24:35.023</t>
-  </si>
-  <si>
-    <t>8521.46</t>
-  </si>
-  <si>
-    <t>62173620009306&amp;NA&amp;</t>
-  </si>
-  <si>
-    <t>Pedido não informado</t>
-  </si>
-  <si>
-    <t>SKFAPE202610051225190107</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85855796PO</t>
-  </si>
-  <si>
-    <t>2026-10-05 12:25:19.22</t>
-  </si>
-  <si>
-    <t>26584.71</t>
-  </si>
-  <si>
-    <t>12237752000150&amp;21/08/2026&amp;5005</t>
-  </si>
-  <si>
-    <t>EP1780835</t>
-  </si>
-  <si>
-    <t>SKFAPE202610151913060413</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85866310PO</t>
-  </si>
-  <si>
-    <t>2026-10-15 19:13:06.693</t>
-  </si>
-  <si>
-    <t>511.93</t>
-  </si>
-  <si>
-    <t>SKFAPE202609011505250264</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85826472PO</t>
-  </si>
-  <si>
-    <t>2026-09-01 15:05:25.78</t>
-  </si>
-  <si>
-    <t>469.25</t>
-  </si>
-  <si>
-    <t>09059224000224&amp;NA</t>
-  </si>
-  <si>
-    <t>EP1734627</t>
-  </si>
-  <si>
-    <t>SKFAPE202609011506050266</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85826475PO</t>
-  </si>
-  <si>
-    <t>2026-09-01 15:06:05.7</t>
-  </si>
-  <si>
-    <t>SKFAPE202606221512160740</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85764386PO</t>
-  </si>
-  <si>
-    <t>2026-06-22 15:12:17.017</t>
-  </si>
-  <si>
-    <t>1314.09</t>
-  </si>
-  <si>
-    <t>31861323000527&amp;08/05/2026&amp;</t>
-  </si>
-  <si>
-    <t>SKFAPE202606221512210741</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85764387PO</t>
-  </si>
-  <si>
-    <t>2026-06-22 15:12:21.343</t>
-  </si>
-  <si>
-    <t>1678.60</t>
-  </si>
-  <si>
-    <t>31861323000527&amp;01/06/2026&amp;</t>
-  </si>
-  <si>
-    <t>SKFAPE202610101357540190</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85861391PO</t>
-  </si>
-  <si>
-    <t>2026-10-10 13:57:54.667</t>
-  </si>
-  <si>
-    <t>16758.10</t>
-  </si>
-  <si>
-    <t>02633186000141&amp;07/01/2026&amp;</t>
-  </si>
-  <si>
-    <t>EP1662798</t>
-  </si>
-  <si>
-    <t>SKFAPE202610142007450976</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85865292PO</t>
-  </si>
-  <si>
-    <t>2026-10-14 20:07:46.28</t>
-  </si>
-  <si>
-    <t>10366.20</t>
-  </si>
-  <si>
-    <t>33449007000144&amp;NA&amp;9001</t>
-  </si>
-  <si>
-    <t>17.05</t>
-  </si>
-  <si>
-    <t>EP1796483</t>
-  </si>
-  <si>
-    <t>SKFAPE202610211347540440</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85870794PO</t>
-  </si>
-  <si>
-    <t>2026-10-21 13:47:54.88</t>
-  </si>
-  <si>
-    <t>38635.44</t>
-  </si>
-  <si>
-    <t>58069360000120&amp;19/12/2026&amp;9105</t>
-  </si>
-  <si>
-    <t>01.07</t>
-  </si>
-  <si>
-    <t>EP1778552</t>
-  </si>
-  <si>
-    <t>SKFAPE202610151928240419</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85866329PO</t>
-  </si>
-  <si>
-    <t>2026-10-15 19:28:24.923</t>
-  </si>
-  <si>
-    <t>8103.84</t>
-  </si>
-  <si>
-    <t>15168902000109&amp;06/11/2026</t>
-  </si>
-  <si>
-    <t>SKFAPE202610151928450420</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85866330PO</t>
-  </si>
-  <si>
-    <t>2026-10-15 19:28:45.337</t>
-  </si>
-  <si>
-    <t>8726.94</t>
-  </si>
-  <si>
-    <t>SKFAPE202610201301370696</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85869352PO</t>
-  </si>
-  <si>
-    <t>2026-10-20 13:01:37.207</t>
-  </si>
-  <si>
-    <t>18573.30</t>
-  </si>
-  <si>
-    <t>EP1811895</t>
-  </si>
-  <si>
-    <t>SKFAPE202610201302580697</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85869353PO</t>
-  </si>
-  <si>
-    <t>2026-10-20 13:02:58.557</t>
-  </si>
-  <si>
-    <t>87.25</t>
-  </si>
-  <si>
-    <t>EP1811894</t>
-  </si>
-  <si>
-    <t>SKFAPE202610201303460700</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85869356PO</t>
-  </si>
-  <si>
-    <t>2026-10-20 13:03:47.033</t>
-  </si>
-  <si>
-    <t>7038.75</t>
-  </si>
-  <si>
-    <t>13182443000273&amp;NA</t>
-  </si>
-  <si>
-    <t>P113724</t>
-  </si>
-  <si>
-    <t>SKFAPE202610201304130702</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85869358PO</t>
-  </si>
-  <si>
-    <t>2026-10-20 13:04:14.007</t>
-  </si>
-  <si>
-    <t>176.46</t>
-  </si>
-  <si>
-    <t>48109110000112&amp;14/12/2026</t>
-  </si>
-  <si>
-    <t>EP1813328</t>
-  </si>
-  <si>
-    <t>SKFAPE202610201305370706</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85869362PO</t>
-  </si>
-  <si>
-    <t>2026-10-20 13:05:37.407</t>
-  </si>
-  <si>
-    <t>33474.02</t>
-  </si>
-  <si>
-    <t>08640510001700&amp;18/11/2026</t>
-  </si>
-  <si>
-    <t>SKFAPE202610201549110805</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85869598PO</t>
-  </si>
-  <si>
-    <t>2026-10-20 15:49:11.407</t>
-  </si>
-  <si>
-    <t>9325.00</t>
-  </si>
-  <si>
-    <t>36532863000157&amp;25/12/2026</t>
-  </si>
-  <si>
-    <t>08.02</t>
-  </si>
-  <si>
-    <t>EP1761510</t>
-  </si>
-  <si>
-    <t>SKFAPE202610211347290438</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85870792PO</t>
-  </si>
-  <si>
-    <t>2026-10-21 13:47:29.277</t>
-  </si>
-  <si>
-    <t>20357.22</t>
-  </si>
-  <si>
-    <t>12017507000137&amp;19/11/2026&amp;</t>
-  </si>
-  <si>
-    <t>EP1814004</t>
-  </si>
-  <si>
-    <t>SKFAPE202610211347490439</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85870793PO</t>
-  </si>
-  <si>
-    <t>2026-10-21 13:47:49.433</t>
-  </si>
-  <si>
-    <t>3654.25</t>
-  </si>
-  <si>
-    <t>11314113000188&amp;18/11/2026&amp;5005</t>
-  </si>
-  <si>
-    <t>EP1802975</t>
-  </si>
-  <si>
-    <t>SKFAPE202610221930530921</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85872264PO</t>
-  </si>
-  <si>
-    <t>2026-10-22 19:30:54.103</t>
-  </si>
-  <si>
-    <t>98605.09</t>
-  </si>
-  <si>
-    <t>41985210000163&amp;NA</t>
-  </si>
-  <si>
-    <t>EP113866</t>
-  </si>
-  <si>
-    <t>SKFAPE202610221931140922</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85872265PO</t>
-  </si>
-  <si>
-    <t>2026-10-22 19:31:14.397</t>
-  </si>
-  <si>
-    <t>7272.72</t>
-  </si>
-  <si>
-    <t>EP113867</t>
-  </si>
-  <si>
-    <t>SKFAPE202608201921570301</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85816866PO</t>
-  </si>
-  <si>
-    <t>2026-08-20 19:21:57.383</t>
-  </si>
-  <si>
-    <t>42644.50</t>
-  </si>
-  <si>
-    <t>05524572003028&amp;NA</t>
-  </si>
-  <si>
-    <t>EP1708355</t>
-  </si>
-  <si>
-    <t>SKFAPE202610021138480653</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85854476PO</t>
-  </si>
-  <si>
-    <t>2026-10-02 11:38:48.363</t>
-  </si>
-  <si>
-    <t>1300.00</t>
-  </si>
-  <si>
-    <t>33975507000110&amp;NA&amp;7503</t>
-  </si>
-  <si>
-    <t>EP1724232</t>
+    <t>SKFAPM202610061112520439</t>
+  </si>
+  <si>
+    <t>2026-10-06 11:14:16.867</t>
+  </si>
+  <si>
+    <t>605254.44</t>
+  </si>
+  <si>
+    <t>13024&amp;01</t>
+  </si>
+  <si>
+    <t>605254,44</t>
+  </si>
+  <si>
+    <t>02833315000579&amp;07/11/2026</t>
   </si>
   <si>
     <t>SKFAPE202607061306410616</t>
@@ -1260,45 +1398,12 @@
     <t>604079.15</t>
   </si>
   <si>
+    <t>643664,51</t>
+  </si>
+  <si>
     <t>02833315000579&amp;31/08/2026&amp;9123</t>
   </si>
   <si>
-    <t>01.01</t>
-  </si>
-  <si>
-    <t>EP1759012</t>
-  </si>
-  <si>
-    <t>SKFAPE202608121232060524</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85810235PO</t>
-  </si>
-  <si>
-    <t>2026-08-12 12:32:06.887</t>
-  </si>
-  <si>
-    <t>700216.08</t>
-  </si>
-  <si>
-    <t>02833315000579&amp;09/10/2026&amp;9123</t>
-  </si>
-  <si>
-    <t>SKFAPE202609091247220128</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85833497PO</t>
-  </si>
-  <si>
-    <t>2026-09-09 12:47:22.8</t>
-  </si>
-  <si>
-    <t>330986.02</t>
-  </si>
-  <si>
-    <t>02833315000579&amp;02/11/2026&amp;9123</t>
-  </si>
-  <si>
     <t>SKFAPE202610051219210984</t>
   </si>
   <si>
@@ -1311,280 +1416,10 @@
     <t>17623.41</t>
   </si>
   <si>
+    <t>18778,25</t>
+  </si>
+  <si>
     <t>02833315000579&amp;02/11/2026</t>
-  </si>
-  <si>
-    <t>SKFAPM202610061112520439</t>
-  </si>
-  <si>
-    <t>2026-10-06 11:14:16.867</t>
-  </si>
-  <si>
-    <t>605254.44</t>
-  </si>
-  <si>
-    <t>13024&amp;01</t>
-  </si>
-  <si>
-    <t>02833315000579&amp;07/11/2026</t>
-  </si>
-  <si>
-    <t>SKFAPE202610142003160962</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85865277PO</t>
-  </si>
-  <si>
-    <t>2026-10-14 20:03:16.17</t>
-  </si>
-  <si>
-    <t>195781.06</t>
-  </si>
-  <si>
-    <t>02833315000579&amp;01/12/2026&amp;9123</t>
-  </si>
-  <si>
-    <t>SKFAPE202610142003510963</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85865279PO</t>
-  </si>
-  <si>
-    <t>2026-10-14 20:03:51.403</t>
-  </si>
-  <si>
-    <t>572291.44</t>
-  </si>
-  <si>
-    <t>SKFAPE202610142005120967</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85865283PO</t>
-  </si>
-  <si>
-    <t>2026-10-14 20:05:12.743</t>
-  </si>
-  <si>
-    <t>20412.48</t>
-  </si>
-  <si>
-    <t>02833315000579&amp;05/12/2026&amp;9123</t>
-  </si>
-  <si>
-    <t>SKFAPE202610221930180920</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85872263PO</t>
-  </si>
-  <si>
-    <t>2026-10-22 19:30:18.91</t>
-  </si>
-  <si>
-    <t>1850.00</t>
-  </si>
-  <si>
-    <t>53337275000181&amp;08/12/2026</t>
-  </si>
-  <si>
-    <t>EP1804906</t>
-  </si>
-  <si>
-    <t>SKFAPE202610141219000664</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85864647PO</t>
-  </si>
-  <si>
-    <t>2026-10-14 12:19:00.777</t>
-  </si>
-  <si>
-    <t>580.00</t>
-  </si>
-  <si>
-    <t>20549570000142&amp;NA&amp;5810</t>
-  </si>
-  <si>
-    <t>26.01</t>
-  </si>
-  <si>
-    <t>EP1672893</t>
-  </si>
-  <si>
-    <t>SKFAPE202609041641030888</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85830580PO</t>
-  </si>
-  <si>
-    <t>2026-09-04 16:41:03.5</t>
-  </si>
-  <si>
-    <t>2625.57</t>
-  </si>
-  <si>
-    <t>18694139000148&amp;NA</t>
-  </si>
-  <si>
-    <t>17.10</t>
-  </si>
-  <si>
-    <t>EP1759004</t>
-  </si>
-  <si>
-    <t>SKFAPE202609161729000364</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85839322PO</t>
-  </si>
-  <si>
-    <t>2026-09-16 17:29:00.427</t>
-  </si>
-  <si>
-    <t>3200.00</t>
-  </si>
-  <si>
-    <t>27261174000164&amp;16/11/2026&amp;9012</t>
-  </si>
-  <si>
-    <t>EP1795426</t>
-  </si>
-  <si>
-    <t>SKFAPE202610141218190662</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85864645PO</t>
-  </si>
-  <si>
-    <t>2026-10-14 12:18:20.04</t>
-  </si>
-  <si>
-    <t>2563.58</t>
-  </si>
-  <si>
-    <t>07100026000150&amp;12/01/2027&amp;9012</t>
-  </si>
-  <si>
-    <t>07.09</t>
-  </si>
-  <si>
-    <t>EP1802621</t>
-  </si>
-  <si>
-    <t>SKFAPE202610141219200665</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85864648PO</t>
-  </si>
-  <si>
-    <t>2026-10-14 12:19:20.347</t>
-  </si>
-  <si>
-    <t>7051.50</t>
-  </si>
-  <si>
-    <t>SKFAPE202610061246560471</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85856949PO</t>
-  </si>
-  <si>
-    <t>2026-10-06 12:46:56.177</t>
-  </si>
-  <si>
-    <t>4860.00</t>
-  </si>
-  <si>
-    <t>07312805000110&amp;04/11/2026</t>
-  </si>
-  <si>
-    <t>EP1798662</t>
-  </si>
-  <si>
-    <t>SKFAPE202610191857290457</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85868640PO</t>
-  </si>
-  <si>
-    <t>2026-10-19 18:57:29.333</t>
-  </si>
-  <si>
-    <t>08998192000189&amp;NA</t>
-  </si>
-  <si>
-    <t>40.01</t>
-  </si>
-  <si>
-    <t>EP1808670</t>
-  </si>
-  <si>
-    <t>SKFAPE202608132035580770</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85811409PO</t>
-  </si>
-  <si>
-    <t>2026-08-13 20:35:59.063</t>
-  </si>
-  <si>
-    <t>7397.02</t>
-  </si>
-  <si>
-    <t>07589942000104&amp;NA</t>
-  </si>
-  <si>
-    <t>33.01</t>
-  </si>
-  <si>
-    <t>EP1799203</t>
-  </si>
-  <si>
-    <t>SKFAPE202608311931510712</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85825337PO</t>
-  </si>
-  <si>
-    <t>2026-08-31 19:31:51.463</t>
-  </si>
-  <si>
-    <t>910.33</t>
-  </si>
-  <si>
-    <t>EP1762183</t>
-  </si>
-  <si>
-    <t>SKFAPE202609041348390846</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85830427PO</t>
-  </si>
-  <si>
-    <t>2026-09-04 13:48:39.54</t>
-  </si>
-  <si>
-    <t>270515.57</t>
-  </si>
-  <si>
-    <t>03519007000102&amp;30/11/2026</t>
-  </si>
-  <si>
-    <t>EP1457750</t>
-  </si>
-  <si>
-    <t>SKFAPE202610141532190864</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9245L85864988PO</t>
-  </si>
-  <si>
-    <t>2026-10-14 15:32:19.17</t>
-  </si>
-  <si>
-    <t>1910.89</t>
-  </si>
-  <si>
-    <t>07589942000104&amp;NA&amp;5000</t>
   </si>
 </sst>
 </file>
@@ -20604,8 +20439,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45B7138B-8E59-4319-B533-11F3B8B533CE}">
-  <dimension ref="A1:U73"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36A19D23-42E6-41C5-AC0B-ECE14204C2C9}">
+  <dimension ref="A1:U58"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.81640625" bestFit="1" customWidth="1"/>
@@ -20632,87 +20467,87 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L1" t="s">
         <v>69</v>
       </c>
-      <c r="B1" t="s">
+      <c r="M1" t="s">
         <v>70</v>
       </c>
-      <c r="C1" t="s">
+      <c r="N1" t="s">
         <v>71</v>
       </c>
-      <c r="D1" t="s">
+      <c r="O1" t="s">
         <v>72</v>
-      </c>
-      <c r="E1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J1" t="s">
-        <v>78</v>
-      </c>
-      <c r="K1" t="s">
-        <v>79</v>
-      </c>
-      <c r="L1" t="s">
-        <v>80</v>
-      </c>
-      <c r="M1" t="s">
-        <v>81</v>
-      </c>
-      <c r="N1" t="s">
-        <v>82</v>
-      </c>
-      <c r="O1" t="s">
-        <v>83</v>
       </c>
       <c r="P1" t="s">
         <v>0</v>
       </c>
       <c r="Q1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="R1" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="S1" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="T1" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="U1" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H2">
         <v>157417</v>
@@ -20724,1387 +20559,1374 @@
         <v>199</v>
       </c>
       <c r="K2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="L2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M2" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="O2" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="P2" t="str">
         <f>_xlfn.XLOOKUP(O2,[1]BASE!N:N,[1]BASE!O:O)</f>
         <v>0FFICE TOTAL SP</v>
       </c>
       <c r="Q2" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="R2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S2" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="U2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="G3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H3">
-        <v>16607</v>
+        <v>109568</v>
       </c>
       <c r="I3" s="1">
-        <v>46296</v>
-      </c>
-      <c r="J3">
-        <v>2965.55</v>
+        <v>46289</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="K3" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="L3" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M3" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="O3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="P3" t="str">
         <f>_xlfn.XLOOKUP(O3,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>FAIR SERVICES - SERV TECNICOS</v>
+        <v>DELOITTE TOUCHE TOHMATSU AUDIT</v>
       </c>
       <c r="Q3" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="R3" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S3" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="T3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="U3" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="G4" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H4">
+        <v>2800</v>
+      </c>
+      <c r="I4" s="1">
+        <v>46296</v>
+      </c>
+      <c r="J4" s="2">
+        <v>5400</v>
+      </c>
+      <c r="K4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L4" t="s">
+        <v>85</v>
+      </c>
+      <c r="M4" t="s">
+        <v>104</v>
+      </c>
+      <c r="O4" t="s">
         <v>32</v>
-      </c>
-      <c r="I4" s="1">
-        <v>46269</v>
-      </c>
-      <c r="J4" s="2">
-        <v>25800</v>
-      </c>
-      <c r="K4" t="s">
-        <v>114</v>
-      </c>
-      <c r="L4" t="s">
-        <v>96</v>
-      </c>
-      <c r="M4" t="s">
-        <v>115</v>
-      </c>
-      <c r="O4" t="s">
-        <v>34</v>
       </c>
       <c r="P4" t="str">
         <f>_xlfn.XLOOKUP(O4,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>LUBRAC SYSTEM LTDA</v>
+        <v>DKT SER ESP DE AP ADM LTDA ME</v>
       </c>
       <c r="Q4" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="R4" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S4" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="U4" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="G5" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H5">
-        <v>10760</v>
+        <v>156553</v>
       </c>
       <c r="I5" s="1">
-        <v>46276</v>
-      </c>
-      <c r="J5">
-        <v>3770.93</v>
+        <v>46174</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="K5" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="L5" t="s">
-        <v>96</v>
-      </c>
-      <c r="M5" t="s">
-        <v>122</v>
-      </c>
-      <c r="O5" t="s">
-        <v>36</v>
+        <v>85</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="P5" t="str">
         <f>_xlfn.XLOOKUP(O5,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>LOBBY TEC PROD PERSO LTDA</v>
+        <v>CULLIGAN BRASIL LTDA</v>
       </c>
       <c r="Q5" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="R5" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S5" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="T5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="U5" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C6" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G6" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H6">
-        <v>2800</v>
+        <v>159034</v>
       </c>
       <c r="I6" s="1">
-        <v>46296</v>
-      </c>
-      <c r="J6" s="2">
-        <v>5400</v>
+        <v>46305</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="K6" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="L6" t="s">
-        <v>96</v>
-      </c>
-      <c r="M6" t="s">
-        <v>129</v>
+        <v>85</v>
       </c>
       <c r="O6" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="P6" t="str">
         <f>_xlfn.XLOOKUP(O6,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>DKT SER ESP DE AP ADM LTDA ME</v>
+        <v>0FFICE TOTAL SP</v>
       </c>
       <c r="Q6" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="R6" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="U6" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C7" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="G7" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H7">
-        <v>4604</v>
+        <v>159035</v>
       </c>
       <c r="I7" s="1">
-        <v>46302</v>
-      </c>
-      <c r="J7" s="2">
-        <v>3500</v>
+        <v>46305</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="K7" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="L7" t="s">
-        <v>96</v>
-      </c>
-      <c r="M7" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="O7" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="P7" t="str">
         <f>_xlfn.XLOOKUP(O7,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>MAPA COMUNIC E ASSESSORIA LTDA</v>
+        <v>0FFICE TOTAL SP</v>
       </c>
       <c r="Q7" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="R7" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S7" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="U7" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C8" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G8" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H8">
-        <v>156553</v>
+        <v>4623</v>
       </c>
       <c r="I8" s="1">
-        <v>46174</v>
-      </c>
-      <c r="J8">
-        <v>1928</v>
+        <v>46310</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1105</v>
       </c>
       <c r="K8" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="L8" t="s">
-        <v>96</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>65</v>
+        <v>85</v>
+      </c>
+      <c r="M8" t="s">
+        <v>132</v>
+      </c>
+      <c r="O8" t="s">
+        <v>8</v>
       </c>
       <c r="P8" t="str">
         <f>_xlfn.XLOOKUP(O8,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>CULLIGAN BRASIL LTDA</v>
+        <v>MAPA COMUNIC E ASSESSORIA LTDA</v>
       </c>
       <c r="Q8" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="R8" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S8" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="T8" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="U8" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C9" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E9" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="G9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H9">
-        <v>159034</v>
+        <v>769</v>
       </c>
       <c r="I9" s="1">
-        <v>46305</v>
-      </c>
-      <c r="J9">
-        <v>892.4</v>
+        <v>46318</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="K9" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="L9" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="O9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P9" t="str">
         <f>_xlfn.XLOOKUP(O9,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>0FFICE TOTAL SP</v>
+        <v>INTECOM SER DE LOGISTICA LTDA</v>
       </c>
       <c r="Q9" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="R9" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S9" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U9" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C10" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="G10" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H10">
-        <v>159035</v>
+        <v>771</v>
       </c>
       <c r="I10" s="1">
-        <v>46305</v>
-      </c>
-      <c r="J10">
-        <v>446.2</v>
+        <v>46318</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="K10" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="L10" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="O10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P10" t="str">
         <f>_xlfn.XLOOKUP(O10,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>0FFICE TOTAL SP</v>
+        <v>INTECOM SER DE LOGISTICA LTDA</v>
       </c>
       <c r="Q10" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="R10" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S10" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U10" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C11" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="G11" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H11">
-        <v>4623</v>
+        <v>770</v>
       </c>
       <c r="I11" s="1">
-        <v>46310</v>
-      </c>
-      <c r="J11" s="2">
-        <v>1105</v>
+        <v>46318</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="K11" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="L11" t="s">
-        <v>96</v>
-      </c>
-      <c r="M11" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="O11" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="P11" t="str">
         <f>_xlfn.XLOOKUP(O11,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>MAPA COMUNIC E ASSESSORIA LTDA</v>
+        <v>INTECOM SER DE LOGISTICA LTDA</v>
       </c>
       <c r="Q11" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="R11" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S11" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T11" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="U11" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C12" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="G12" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H12">
-        <v>1696740</v>
+        <v>768</v>
       </c>
       <c r="I12" s="1">
-        <v>46315</v>
-      </c>
-      <c r="J12">
-        <v>50714.5</v>
+        <v>46318</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="K12" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="L12" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="O12" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="P12" t="str">
         <f>_xlfn.XLOOKUP(O12,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>ASSOCIACAO DELTA EMP PARK</v>
+        <v>INTECOM SER DE LOGISTICA LTDA</v>
       </c>
       <c r="Q12" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="R12" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S12" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="U12" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C13" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="G13" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H13">
-        <v>143685</v>
+        <v>2970</v>
       </c>
       <c r="I13" s="1">
-        <v>46220</v>
-      </c>
-      <c r="J13">
-        <v>560.28</v>
+        <v>46304</v>
+      </c>
+      <c r="J13" s="2">
+        <v>3500</v>
       </c>
       <c r="K13" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M13" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="O13" t="s">
-        <v>14</v>
-      </c>
-      <c r="P13" t="str">
-        <f>_xlfn.XLOOKUP(O13,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>SERVICO NACIONAL APRENDI INDUS</v>
+        <v>46</v>
+      </c>
+      <c r="P13" t="s">
+        <v>55</v>
       </c>
       <c r="Q13" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="R13" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S13" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T13" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="U13" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="C14" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D14" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E14" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="G14" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H14">
-        <v>118</v>
+        <v>203</v>
       </c>
       <c r="I14" s="1">
-        <v>46300</v>
-      </c>
-      <c r="J14" s="2">
-        <v>11000</v>
+        <v>46189</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="K14" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M14" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="O14" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="P14" t="str">
         <f>_xlfn.XLOOKUP(O14,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>EDIEL SIQUEIRA DE ANDRADE JUNI</v>
+        <v>FASTENAL B</v>
       </c>
       <c r="Q14" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="R14" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S14" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T14" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U14" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="G15" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H15">
-        <v>144527</v>
+        <v>202</v>
       </c>
       <c r="I15" s="1">
-        <v>46303</v>
-      </c>
-      <c r="J15">
-        <v>231.47</v>
+        <v>46189</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>175</v>
       </c>
       <c r="K15" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="O15" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P15" t="str">
         <f>_xlfn.XLOOKUP(O15,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>SERVICO NACIO APRENDI INDUS</v>
+        <v>FASTENAL B</v>
       </c>
       <c r="Q15" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="R15" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S15" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="T15" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U15" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C16" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E16" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="G16" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H16">
-        <v>18870</v>
+        <v>373798</v>
       </c>
       <c r="I16" s="1">
-        <v>46303</v>
-      </c>
-      <c r="J16">
-        <v>5864.62</v>
+        <v>46195</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="K16" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="L16" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M16" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="O16" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="P16" t="str">
         <f>_xlfn.XLOOKUP(O16,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>PENSALAB EQUI IND S.A.</v>
+        <v>TOP SERVICE SERVICOS E SIS LTD</v>
       </c>
       <c r="Q16" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="R16" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S16" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T16" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U16" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C17" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="G17" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H17">
-        <v>144528</v>
+        <v>1588429</v>
       </c>
       <c r="I17" s="1">
-        <v>46303</v>
-      </c>
-      <c r="J17">
-        <v>532.66</v>
+        <v>46295</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>189</v>
       </c>
       <c r="K17" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="L17" t="s">
-        <v>96</v>
-      </c>
-      <c r="M17" t="s">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="O17" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="P17" t="str">
         <f>_xlfn.XLOOKUP(O17,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>SERVICO NACIO APRENDI INDUS</v>
+        <v>SERASA S.A.</v>
       </c>
       <c r="Q17" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="R17" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S17" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="T17" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="U17" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G18" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H18">
-        <v>144564</v>
+        <v>131</v>
       </c>
       <c r="I18" s="1">
-        <v>46308</v>
-      </c>
-      <c r="J18">
-        <v>952.33</v>
+        <v>46297</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="K18" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="L18" t="s">
-        <v>96</v>
-      </c>
-      <c r="M18" t="s">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="O18" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="P18" t="str">
         <f>_xlfn.XLOOKUP(O18,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>SERVICO NACIO APRENDI INDUS</v>
+        <v>RODL &amp; PARTNER CONSUL LTDA</v>
       </c>
       <c r="Q18" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="R18" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S18" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T18" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="U18" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>199</v>
+      </c>
+      <c r="B19" t="s">
+        <v>200</v>
+      </c>
+      <c r="C19" t="s">
+        <v>201</v>
+      </c>
+      <c r="D19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" t="s">
+        <v>202</v>
+      </c>
+      <c r="G19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H19">
+        <v>1693866</v>
+      </c>
+      <c r="I19" s="1">
+        <v>46310</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="K19" t="s">
         <v>204</v>
       </c>
-      <c r="B19" t="s">
-        <v>205</v>
-      </c>
-      <c r="C19" t="s">
-        <v>206</v>
-      </c>
-      <c r="D19" t="s">
-        <v>92</v>
-      </c>
-      <c r="E19" t="s">
-        <v>207</v>
-      </c>
-      <c r="G19" t="s">
-        <v>94</v>
-      </c>
-      <c r="H19">
-        <v>10622</v>
-      </c>
-      <c r="I19" s="1">
-        <v>46304</v>
-      </c>
-      <c r="J19">
-        <v>4482.2</v>
-      </c>
-      <c r="K19" t="s">
-        <v>208</v>
-      </c>
       <c r="L19" t="s">
-        <v>96</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="P19" t="s">
-        <v>64</v>
+        <v>85</v>
+      </c>
+      <c r="O19" t="s">
+        <v>34</v>
+      </c>
+      <c r="P19" t="str">
+        <f>_xlfn.XLOOKUP(O19,[1]BASE!N:N,[1]BASE!O:O)</f>
+        <v>ASSOCIACAO DELTA EMP PARK</v>
       </c>
       <c r="Q19" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="R19" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S19" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="U19" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C20" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="G20" t="s">
-        <v>94</v>
-      </c>
-      <c r="H20" t="s">
-        <v>213</v>
+        <v>83</v>
+      </c>
+      <c r="H20">
+        <v>464</v>
       </c>
       <c r="I20" s="1">
-        <v>46273</v>
-      </c>
-      <c r="J20">
-        <v>22865.14</v>
+        <v>46265</v>
+      </c>
+      <c r="J20" s="2">
+        <v>500</v>
       </c>
       <c r="K20" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="L20" t="s">
-        <v>96</v>
+        <v>85</v>
+      </c>
+      <c r="M20" t="s">
+        <v>169</v>
       </c>
       <c r="O20" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="P20" t="str">
         <f>_xlfn.XLOOKUP(O20,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>QUATRO PONTO ZERO - RH LT</v>
+        <v>RAZAC INTERNATIONAL TRADE LTDA</v>
       </c>
       <c r="Q20" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="R20" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S20" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T20" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="U20" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C21" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="G21" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H21">
-        <v>99</v>
+        <v>460</v>
       </c>
       <c r="I21" s="1">
-        <v>46314</v>
+        <v>46262</v>
       </c>
       <c r="J21" s="2">
-        <v>513009</v>
+        <v>500</v>
       </c>
       <c r="K21" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M21" t="s">
-        <v>221</v>
+        <v>169</v>
       </c>
       <c r="O21" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="P21" t="str">
         <f>_xlfn.XLOOKUP(O21,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>TECADI OPERADOR LOGISTICO LTDA</v>
+        <v>RAZAC INTERNATIONAL TRADE LTDA</v>
       </c>
       <c r="Q21" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="R21" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S21" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T21" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="U21" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C22" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="G22" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H22">
-        <v>100</v>
+        <v>1696740</v>
       </c>
       <c r="I22" s="1">
-        <v>46314</v>
-      </c>
-      <c r="J22">
-        <v>82634.960000000006</v>
+        <v>46315</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>218</v>
       </c>
       <c r="K22" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="L22" t="s">
-        <v>96</v>
-      </c>
-      <c r="M22" t="s">
-        <v>221</v>
+        <v>85</v>
       </c>
       <c r="O22" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="P22" t="str">
         <f>_xlfn.XLOOKUP(O22,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>TECADI OPERADOR LOGISTICO LTDA</v>
+        <v>ASSOCIACAO DELTA EMP PARK</v>
       </c>
       <c r="Q22" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="R22" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S22" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T22" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="U22" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C23" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="G23" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H23">
-        <v>4768</v>
+        <v>143685</v>
       </c>
       <c r="I23" s="1">
-        <v>46314</v>
-      </c>
-      <c r="J23" s="2">
-        <v>5000</v>
+        <v>46220</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="K23" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="L23" t="s">
-        <v>96</v>
+        <v>85</v>
+      </c>
+      <c r="M23" t="s">
+        <v>226</v>
       </c>
       <c r="O23" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="P23" t="str">
         <f>_xlfn.XLOOKUP(O23,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>DAGNONI E KENIG ADM DE BENS LT</v>
+        <v>SERVICO NACIONAL APRENDI INDUS</v>
       </c>
       <c r="Q23" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="R23" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S23" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T23" t="s">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="U23" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>228</v>
+      </c>
+      <c r="B24" t="s">
+        <v>229</v>
+      </c>
+      <c r="C24" t="s">
+        <v>230</v>
+      </c>
+      <c r="D24" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" t="s">
+        <v>231</v>
+      </c>
+      <c r="G24" t="s">
+        <v>83</v>
+      </c>
+      <c r="H24">
+        <v>10622</v>
+      </c>
+      <c r="I24" s="1">
+        <v>46304</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="K24" t="s">
         <v>233</v>
       </c>
-      <c r="B24" t="s">
+      <c r="L24" t="s">
+        <v>85</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="P24" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q24" t="s">
         <v>234</v>
       </c>
-      <c r="C24" t="s">
-        <v>235</v>
-      </c>
-      <c r="D24" t="s">
-        <v>92</v>
-      </c>
-      <c r="E24" t="s">
-        <v>236</v>
-      </c>
-      <c r="G24" t="s">
-        <v>94</v>
-      </c>
-      <c r="H24">
-        <v>4770</v>
-      </c>
-      <c r="I24" s="1">
-        <v>46314</v>
-      </c>
-      <c r="J24" s="2">
-        <v>72500</v>
-      </c>
-      <c r="K24" t="s">
-        <v>231</v>
-      </c>
-      <c r="L24" t="s">
-        <v>96</v>
-      </c>
-      <c r="O24" t="s">
-        <v>53</v>
-      </c>
-      <c r="P24" t="str">
-        <f>_xlfn.XLOOKUP(O24,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>DAGNONI E KENIG ADM DE BENS LT</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>237</v>
-      </c>
       <c r="R24" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S24" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T24" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="U24" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>235</v>
+      </c>
+      <c r="B25" t="s">
+        <v>236</v>
+      </c>
+      <c r="C25" t="s">
+        <v>237</v>
+      </c>
+      <c r="D25" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" t="s">
         <v>238</v>
       </c>
-      <c r="B25" t="s">
+      <c r="G25" t="s">
+        <v>83</v>
+      </c>
+      <c r="H25">
+        <v>1852839</v>
+      </c>
+      <c r="I25" s="1">
+        <v>46302</v>
+      </c>
+      <c r="J25" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C25" t="s">
+      <c r="K25" t="s">
         <v>240</v>
       </c>
-      <c r="D25" t="s">
-        <v>92</v>
-      </c>
-      <c r="E25" t="s">
-        <v>241</v>
-      </c>
-      <c r="G25" t="s">
-        <v>94</v>
-      </c>
-      <c r="H25">
-        <v>4769</v>
-      </c>
-      <c r="I25" s="1">
-        <v>46314</v>
-      </c>
-      <c r="J25" s="2">
-        <v>227050</v>
-      </c>
-      <c r="K25" t="s">
-        <v>231</v>
-      </c>
       <c r="L25" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="O25" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="P25" t="str">
         <f>_xlfn.XLOOKUP(O25,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>DAGNONI E KENIG ADM DE BENS LT</v>
+        <v>COPASTUR VIAGENS E TURISMO LTD</v>
       </c>
       <c r="Q25" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="R25" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S25" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T25" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="U25" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.35">
@@ -22118,233 +21940,227 @@
         <v>244</v>
       </c>
       <c r="D26" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E26" t="s">
         <v>245</v>
       </c>
       <c r="G26" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H26">
-        <v>5053</v>
+        <v>1693929</v>
       </c>
       <c r="I26" s="1">
-        <v>46251</v>
-      </c>
-      <c r="J26" s="2">
-        <v>719</v>
+        <v>46310</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>246</v>
       </c>
       <c r="K26" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L26" t="s">
-        <v>96</v>
-      </c>
-      <c r="M26" t="s">
-        <v>247</v>
+        <v>85</v>
       </c>
       <c r="O26" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="P26" t="str">
         <f>_xlfn.XLOOKUP(O26,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>SPEED IO SERV ESPECIALI LTDA</v>
+        <v>ASSOCIACAO DELTA EMP PARK</v>
       </c>
       <c r="Q26" t="s">
-        <v>248</v>
+        <v>191</v>
       </c>
       <c r="R26" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S26" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T26" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="U26" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>248</v>
+      </c>
+      <c r="B27" t="s">
         <v>249</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>250</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" t="s">
         <v>251</v>
       </c>
-      <c r="D27" t="s">
-        <v>92</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="G27" t="s">
+        <v>83</v>
+      </c>
+      <c r="H27">
+        <v>1693882</v>
+      </c>
+      <c r="I27" s="1">
+        <v>46310</v>
+      </c>
+      <c r="J27" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="G27" t="s">
-        <v>94</v>
-      </c>
-      <c r="H27">
-        <v>203</v>
-      </c>
-      <c r="I27" s="1">
-        <v>46189</v>
-      </c>
-      <c r="J27">
-        <v>5280</v>
-      </c>
       <c r="K27" t="s">
-        <v>253</v>
+        <v>204</v>
       </c>
       <c r="L27" t="s">
-        <v>96</v>
-      </c>
-      <c r="M27" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="O27" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="P27" t="str">
         <f>_xlfn.XLOOKUP(O27,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>FASTENAL B</v>
+        <v>ASSOCIACAO DELTA EMP PARK</v>
       </c>
       <c r="Q27" t="s">
-        <v>254</v>
+        <v>191</v>
       </c>
       <c r="R27" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S27" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T27" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="U27" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>253</v>
+      </c>
+      <c r="B28" t="s">
+        <v>254</v>
+      </c>
+      <c r="C28" t="s">
         <v>255</v>
       </c>
-      <c r="B28" t="s">
+      <c r="D28" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" t="s">
         <v>256</v>
       </c>
-      <c r="C28" t="s">
+      <c r="G28" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28">
+        <v>97</v>
+      </c>
+      <c r="I28" s="1">
+        <v>46314</v>
+      </c>
+      <c r="J28" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D28" t="s">
-        <v>92</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="K28" t="s">
         <v>258</v>
       </c>
-      <c r="G28" t="s">
-        <v>94</v>
-      </c>
-      <c r="H28">
-        <v>202</v>
-      </c>
-      <c r="I28" s="1">
-        <v>46189</v>
-      </c>
-      <c r="J28">
-        <v>16720</v>
-      </c>
-      <c r="K28" t="s">
-        <v>253</v>
-      </c>
       <c r="L28" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M28" t="s">
-        <v>107</v>
+        <v>259</v>
       </c>
       <c r="O28" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="P28" t="str">
         <f>_xlfn.XLOOKUP(O28,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>FASTENAL B</v>
+        <v>TECADI OPERADOR LOGISTICO LTDA</v>
       </c>
       <c r="Q28" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="R28" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S28" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T28" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="U28" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C29" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D29" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E29" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G29" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H29">
-        <v>373798</v>
+        <v>98</v>
       </c>
       <c r="I29" s="1">
-        <v>46195</v>
-      </c>
-      <c r="J29">
-        <v>5136.25</v>
+        <v>46314</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>265</v>
       </c>
       <c r="K29" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="L29" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M29" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="O29" t="s">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="P29" t="str">
         <f>_xlfn.XLOOKUP(O29,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>TOP SERVICE SERVICOS E SIS LTD</v>
+        <v>TECADI OPERADOR LOGISTICO LTDA</v>
       </c>
       <c r="Q29" t="s">
         <v>266</v>
       </c>
       <c r="R29" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S29" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="U29" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.35">
@@ -22358,50 +22174,53 @@
         <v>269</v>
       </c>
       <c r="D30" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E30" t="s">
         <v>270</v>
       </c>
       <c r="G30" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H30">
-        <v>1588429</v>
+        <v>218</v>
       </c>
       <c r="I30" s="1">
-        <v>46295</v>
-      </c>
-      <c r="J30">
-        <v>8521.4599999999991</v>
+        <v>46314</v>
+      </c>
+      <c r="J30" s="2">
+        <v>7500</v>
       </c>
       <c r="K30" t="s">
         <v>271</v>
       </c>
       <c r="L30" t="s">
-        <v>96</v>
+        <v>85</v>
+      </c>
+      <c r="M30" t="s">
+        <v>169</v>
       </c>
       <c r="O30" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="P30" t="str">
         <f>_xlfn.XLOOKUP(O30,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>SERASA S.A.</v>
+        <v>FASTENAL B</v>
       </c>
       <c r="Q30" t="s">
         <v>272</v>
       </c>
       <c r="R30" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S30" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T30" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="U30" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.35">
@@ -22415,2544 +22234,1655 @@
         <v>275</v>
       </c>
       <c r="D31" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E31" t="s">
         <v>276</v>
       </c>
       <c r="G31" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H31">
-        <v>131</v>
+        <v>4254</v>
       </c>
       <c r="I31" s="1">
-        <v>46297</v>
-      </c>
-      <c r="J31">
-        <v>26584.71</v>
+        <v>46308</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>277</v>
       </c>
       <c r="K31" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L31" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="O31" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="P31" t="str">
         <f>_xlfn.XLOOKUP(O31,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>RODL &amp; PARTNER CONSUL LTDA</v>
+        <v>TOZZINI FREIRE TEIXEIRA E SILV</v>
       </c>
       <c r="Q31" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="R31" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S31" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T31" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="U31" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B32" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C32" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D32" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E32" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G32" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H32">
-        <v>1693866</v>
+        <v>1132026</v>
       </c>
       <c r="I32" s="1">
-        <v>46310</v>
-      </c>
-      <c r="J32">
-        <v>511.93</v>
+        <v>46314</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>284</v>
       </c>
       <c r="K32" t="s">
-        <v>164</v>
+        <v>285</v>
       </c>
       <c r="L32" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="O32" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="P32" t="str">
         <f>_xlfn.XLOOKUP(O32,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>ASSOCIACAO DELTA EMP PARK</v>
+        <v>TECADI OPERADOR LOGISTICO LTDA</v>
       </c>
       <c r="Q32" t="s">
-        <v>272</v>
+        <v>191</v>
       </c>
       <c r="R32" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S32" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T32" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="U32" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B33" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C33" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D33" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E33" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G33" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H33">
-        <v>464</v>
+        <v>312</v>
       </c>
       <c r="I33" s="1">
-        <v>46265</v>
+        <v>46315</v>
       </c>
       <c r="J33" s="2">
-        <v>500</v>
+        <v>9325</v>
       </c>
       <c r="K33" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L33" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M33" t="s">
-        <v>107</v>
+        <v>291</v>
       </c>
       <c r="O33" t="s">
-        <v>12</v>
-      </c>
-      <c r="P33" t="str">
-        <f>_xlfn.XLOOKUP(O33,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>RAZAC INTERNATIONAL TRADE LTDA</v>
+        <v>51</v>
+      </c>
+      <c r="P33" t="s">
+        <v>57</v>
       </c>
       <c r="Q33" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="R33" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S33" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T33" t="s">
         <v>19</v>
       </c>
       <c r="U33" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C34" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D34" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E34" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="G34" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H34">
-        <v>460</v>
+        <v>795</v>
       </c>
       <c r="I34" s="1">
-        <v>46262</v>
+        <v>46315</v>
       </c>
       <c r="J34" s="2">
-        <v>500</v>
+        <v>21350</v>
       </c>
       <c r="K34" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="L34" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M34" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="O34" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="P34" t="str">
         <f>_xlfn.XLOOKUP(O34,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>RAZAC INTERNATIONAL TRADE LTDA</v>
+        <v>RODOLFO DA SILVA MAIA</v>
       </c>
       <c r="Q34" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="R34" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S34" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T34" t="s">
         <v>19</v>
       </c>
       <c r="U34" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C35" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D35" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E35" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="G35" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H35">
-        <v>37941</v>
+        <v>42</v>
       </c>
       <c r="I35" s="1">
-        <v>46120</v>
-      </c>
-      <c r="J35">
-        <v>1314.09</v>
+        <v>46315</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>303</v>
       </c>
       <c r="K35" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="L35" t="s">
-        <v>96</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>65</v>
+        <v>85</v>
+      </c>
+      <c r="M35" t="s">
+        <v>291</v>
+      </c>
+      <c r="O35" t="s">
+        <v>36</v>
       </c>
       <c r="P35" t="str">
         <f>_xlfn.XLOOKUP(O35,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>CULLIGAN BRASIL LTDA</v>
+        <v>BP DOS SANTOS</v>
       </c>
       <c r="Q35" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="R35" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S35" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="T35" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="U35" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="B36" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="C36" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="D36" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E36" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="G36" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H36">
-        <v>97322</v>
+        <v>3770</v>
       </c>
       <c r="I36" s="1">
-        <v>46143</v>
-      </c>
-      <c r="J36">
-        <v>1678.6</v>
+        <v>46317</v>
+      </c>
+      <c r="J36" s="2">
+        <v>1360</v>
       </c>
       <c r="K36" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="L36" t="s">
-        <v>96</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>65</v>
+        <v>85</v>
+      </c>
+      <c r="O36" t="s">
+        <v>26</v>
       </c>
       <c r="P36" t="str">
         <f>_xlfn.XLOOKUP(O36,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>CULLIGAN BRASIL LTDA</v>
+        <v>TO INDO EXPRESS EIRELI</v>
       </c>
       <c r="Q36" t="s">
-        <v>143</v>
+        <v>311</v>
       </c>
       <c r="R36" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S36" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="T36" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="U36" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B37" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="C37" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="D37" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E37" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="G37" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H37">
-        <v>27641</v>
+        <v>12958</v>
       </c>
       <c r="I37" s="1">
-        <v>46304</v>
-      </c>
-      <c r="J37" s="2">
-        <v>20600</v>
+        <v>46244</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>316</v>
       </c>
       <c r="K37" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="L37" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M37" t="s">
-        <v>265</v>
+        <v>318</v>
       </c>
       <c r="O37" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="P37" t="str">
         <f>_xlfn.XLOOKUP(O37,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>LANCER SERVIÇOS GERAIS LTDA</v>
+        <v>ENTERPRISE SERV BR S DE TEC LT</v>
       </c>
       <c r="Q37" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="R37" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S37" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T37" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="U37" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B38" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C38" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="D38" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E38" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="G38" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H38">
-        <v>9019040</v>
+        <v>13020</v>
       </c>
       <c r="I38" s="1">
-        <v>46309</v>
-      </c>
-      <c r="J38">
-        <v>10366.200000000001</v>
+        <v>46268</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>324</v>
       </c>
       <c r="K38" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="L38" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M38" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="O38" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="P38" t="str">
         <f>_xlfn.XLOOKUP(O38,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>EMPRESA BRAS DE BENE E PAG LTD</v>
+        <v>ENTERPRISE SERV BR S DE TEC LT</v>
       </c>
       <c r="Q38" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="R38" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S38" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T38" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="U38" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B39" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="C39" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D39" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E39" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="G39" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H39">
-        <v>252715</v>
+        <v>13078</v>
       </c>
       <c r="I39" s="1">
-        <v>46315</v>
-      </c>
-      <c r="J39">
-        <v>41167.230000000003</v>
+        <v>46307</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="K39" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="L39" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M39" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="O39" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="P39" t="str">
         <f>_xlfn.XLOOKUP(O39,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>STEFANINI CONSULTORIA INFO LTD</v>
+        <v>ENTERPRISE SERV BR S DE TEC LT</v>
       </c>
       <c r="Q39" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="R39" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S39" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T39" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="U39" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B40" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="C40" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="D40" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E40" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="G40" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H40">
-        <v>1693929</v>
+        <v>1153</v>
       </c>
       <c r="I40" s="1">
-        <v>46310</v>
-      </c>
-      <c r="J40">
-        <v>8103.84</v>
+        <v>46308</v>
+      </c>
+      <c r="J40" s="2">
+        <v>580</v>
       </c>
       <c r="K40" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="L40" t="s">
-        <v>96</v>
+        <v>85</v>
+      </c>
+      <c r="M40" t="s">
+        <v>339</v>
       </c>
       <c r="O40" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="P40" t="str">
         <f>_xlfn.XLOOKUP(O40,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>ASSOCIACAO DELTA EMP PARK</v>
+        <v>TO INDO EXPRESS EIRELI</v>
       </c>
       <c r="Q40" t="s">
-        <v>272</v>
+        <v>340</v>
       </c>
       <c r="R40" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S40" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T40" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="U40" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="B41" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="C41" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="D41" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E41" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="G41" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H41">
-        <v>1693882</v>
+        <v>798</v>
       </c>
       <c r="I41" s="1">
-        <v>46310</v>
-      </c>
-      <c r="J41">
-        <v>8726.94</v>
+        <v>46269</v>
+      </c>
+      <c r="J41" s="2">
+        <v>2890</v>
       </c>
       <c r="K41" t="s">
-        <v>164</v>
+        <v>345</v>
       </c>
       <c r="L41" t="s">
-        <v>96</v>
+        <v>85</v>
+      </c>
+      <c r="M41" t="s">
+        <v>346</v>
       </c>
       <c r="O41" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="P41" t="str">
         <f>_xlfn.XLOOKUP(O41,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>ASSOCIACAO DELTA EMP PARK</v>
+        <v>HASS ASSES MARK E EVENTOS LTDA</v>
       </c>
       <c r="Q41" t="s">
-        <v>272</v>
+        <v>347</v>
       </c>
       <c r="R41" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S41" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T41" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="U41" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="B42" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="C42" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="D42" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E42" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="G42" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H42">
-        <v>97</v>
+        <v>21985</v>
       </c>
       <c r="I42" s="1">
-        <v>46314</v>
-      </c>
-      <c r="J42">
-        <v>18573.3</v>
+        <v>46262</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>352</v>
       </c>
       <c r="K42" t="s">
-        <v>220</v>
+        <v>353</v>
       </c>
       <c r="L42" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M42" t="s">
-        <v>221</v>
+        <v>354</v>
       </c>
       <c r="O42" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="P42" t="str">
         <f>_xlfn.XLOOKUP(O42,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>TECADI OPERADOR LOGISTICO LTDA</v>
+        <v>RAZAC SERVICES CONSUL EM COM E</v>
       </c>
       <c r="Q42" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="R42" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S42" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="T42" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="U42" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="B43" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="C43" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="D43" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E43" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="G43" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H43">
-        <v>98</v>
+        <v>176266</v>
       </c>
       <c r="I43" s="1">
-        <v>46314</v>
-      </c>
-      <c r="J43">
-        <v>87.25</v>
+        <v>46266</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>360</v>
       </c>
       <c r="K43" t="s">
-        <v>220</v>
+        <v>361</v>
       </c>
       <c r="L43" t="s">
-        <v>96</v>
-      </c>
-      <c r="M43" t="s">
-        <v>221</v>
+        <v>85</v>
       </c>
       <c r="O43" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="P43" t="str">
         <f>_xlfn.XLOOKUP(O43,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>TECADI OPERADOR LOGISTICO LTDA</v>
+        <v>ILS CARGO TRANSPORTES INTERNAC</v>
       </c>
       <c r="Q43" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="R43" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S43" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T43" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="U43" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="B44" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="C44" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="D44" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E44" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="G44" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H44">
-        <v>218</v>
+        <v>32</v>
       </c>
       <c r="I44" s="1">
-        <v>46314</v>
+        <v>46269</v>
       </c>
       <c r="J44" s="2">
-        <v>7500</v>
+        <v>25800</v>
       </c>
       <c r="K44" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="L44" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M44" t="s">
-        <v>107</v>
+        <v>368</v>
       </c>
       <c r="O44" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="P44" t="str">
         <f>_xlfn.XLOOKUP(O44,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>FASTENAL B</v>
+        <v>LUBRAC SYSTEM LTDA</v>
       </c>
       <c r="Q44" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="R44" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S44" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T44" t="s">
         <v>23</v>
       </c>
       <c r="U44" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="B45" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="C45" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="D45" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E45" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="G45" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H45">
-        <v>4254</v>
+        <v>13074</v>
       </c>
       <c r="I45" s="1">
-        <v>46308</v>
-      </c>
-      <c r="J45">
-        <v>176.46</v>
+        <v>46307</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>374</v>
       </c>
       <c r="K45" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
       <c r="L45" t="s">
-        <v>96</v>
+        <v>85</v>
+      </c>
+      <c r="M45" t="s">
+        <v>318</v>
       </c>
       <c r="O45" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="P45" t="str">
         <f>_xlfn.XLOOKUP(O45,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>TOZZINI FREIRE TEIXEIRA E SILV</v>
+        <v>ENTERPRISE SERV BR S DE TEC LT</v>
       </c>
       <c r="Q45" t="s">
-        <v>352</v>
+        <v>319</v>
       </c>
       <c r="R45" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S45" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T45" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="U45" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="B46" t="s">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="C46" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="D46" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E46" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="G46" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H46">
-        <v>1132026</v>
+        <v>13073</v>
       </c>
       <c r="I46" s="1">
-        <v>46314</v>
-      </c>
-      <c r="J46">
-        <v>33474.019999999997</v>
+        <v>46307</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>380</v>
       </c>
       <c r="K46" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="L46" t="s">
-        <v>96</v>
+        <v>85</v>
+      </c>
+      <c r="M46" t="s">
+        <v>326</v>
       </c>
       <c r="O46" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="P46" t="str">
         <f>_xlfn.XLOOKUP(O46,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>TECADI OPERADOR LOGISTICO LTDA</v>
+        <v>ENTERPRISE SERV BR S DE TEC LT</v>
       </c>
       <c r="Q46" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
       <c r="R46" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S46" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T46" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="U46" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="B47" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="C47" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="D47" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E47" t="s">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="G47" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H47">
-        <v>312</v>
+        <v>37941</v>
       </c>
       <c r="I47" s="1">
-        <v>46315</v>
-      </c>
-      <c r="J47" s="2">
-        <v>9325</v>
+        <v>46120</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>385</v>
       </c>
       <c r="K47" t="s">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="L47" t="s">
-        <v>96</v>
-      </c>
-      <c r="M47" t="s">
-        <v>363</v>
-      </c>
-      <c r="O47" t="s">
-        <v>57</v>
-      </c>
-      <c r="P47" t="s">
-        <v>66</v>
+        <v>85</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P47" t="str">
+        <f>_xlfn.XLOOKUP(O47,[1]BASE!N:N,[1]BASE!O:O)</f>
+        <v>CULLIGAN BRASIL LTDA</v>
       </c>
       <c r="Q47" t="s">
-        <v>364</v>
+        <v>191</v>
       </c>
       <c r="R47" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S47" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="T47" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="U47" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="B48" t="s">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="C48" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="D48" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E48" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="G48" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H48">
-        <v>795</v>
+        <v>97322</v>
       </c>
       <c r="I48" s="1">
-        <v>46315</v>
-      </c>
-      <c r="J48" s="2">
-        <v>21350</v>
+        <v>46143</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>391</v>
       </c>
       <c r="K48" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="L48" t="s">
-        <v>96</v>
-      </c>
-      <c r="M48" t="s">
-        <v>129</v>
-      </c>
-      <c r="O48" t="s">
-        <v>58</v>
+        <v>85</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="P48" t="str">
         <f>_xlfn.XLOOKUP(O48,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>RODOLFO DA SILVA MAIA</v>
+        <v>CULLIGAN BRASIL LTDA</v>
       </c>
       <c r="Q48" t="s">
-        <v>370</v>
+        <v>112</v>
       </c>
       <c r="R48" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S48" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="T48" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="U48" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="B49" t="s">
-        <v>372</v>
+        <v>394</v>
       </c>
       <c r="C49" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="D49" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E49" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="G49" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H49">
-        <v>42</v>
+        <v>9019040</v>
       </c>
       <c r="I49" s="1">
-        <v>46315</v>
-      </c>
-      <c r="J49">
-        <v>3654.25</v>
+        <v>46309</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>397</v>
       </c>
       <c r="K49" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="L49" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M49" t="s">
-        <v>363</v>
+        <v>399</v>
       </c>
       <c r="O49" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="P49" t="str">
         <f>_xlfn.XLOOKUP(O49,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>BP DOS SANTOS</v>
+        <v>EMPRESA BRAS DE BENE E PAG LTD</v>
       </c>
       <c r="Q49" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="R49" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S49" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T49" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="U49" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>377</v>
+        <v>401</v>
       </c>
       <c r="B50" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="C50" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="D50" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E50" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="G50" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H50">
-        <v>2600000000196</v>
+        <v>252715</v>
       </c>
       <c r="I50" s="1">
-        <v>46313</v>
-      </c>
-      <c r="J50">
-        <v>98605.09</v>
+        <v>46315</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>405</v>
       </c>
       <c r="K50" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="L50" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M50" t="s">
-        <v>191</v>
+        <v>333</v>
       </c>
       <c r="O50" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="P50" t="str">
         <f>_xlfn.XLOOKUP(O50,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>MAXILUBE SERV PROD LUBR LTDA</v>
+        <v>STEFANINI CONSULTORIA INFO LTD</v>
       </c>
       <c r="Q50" t="s">
-        <v>382</v>
+        <v>407</v>
       </c>
       <c r="R50" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S50" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T50" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="U50" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="B51" t="s">
-        <v>384</v>
+        <v>409</v>
       </c>
       <c r="C51" t="s">
-        <v>385</v>
+        <v>410</v>
       </c>
       <c r="D51" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E51" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="G51" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H51">
-        <v>2600000000197</v>
+        <v>27641</v>
       </c>
       <c r="I51" s="1">
-        <v>46313</v>
-      </c>
-      <c r="J51">
-        <v>7272.72</v>
+        <v>46304</v>
+      </c>
+      <c r="J51" s="2">
+        <v>20600</v>
       </c>
       <c r="K51" t="s">
-        <v>381</v>
+        <v>412</v>
       </c>
       <c r="L51" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M51" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="O51" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="P51" t="str">
         <f>_xlfn.XLOOKUP(O51,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>MAXILUBE SERV PROD LUBR LTDA</v>
+        <v>LANCER SERVIÇOS GERAIS LTDA</v>
       </c>
       <c r="Q51" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="R51" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S51" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T51" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="U51" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="B52" t="s">
-        <v>389</v>
+        <v>415</v>
       </c>
       <c r="C52" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="D52" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E52" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="G52" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H52">
-        <v>201</v>
+        <v>5053</v>
       </c>
       <c r="I52" s="1">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="J52" s="2">
-        <v>45439</v>
+        <v>719</v>
       </c>
       <c r="K52" t="s">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="L52" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M52" t="s">
-        <v>171</v>
+        <v>419</v>
       </c>
       <c r="O52" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="P52" t="str">
         <f>_xlfn.XLOOKUP(O52,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>ICONIC LUBRIFICANTES S.A</v>
+        <v>SPEED IO SERV ESPECIALI LTDA</v>
       </c>
       <c r="Q52" t="s">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="R52" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S52" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T52" t="s">
         <v>11</v>
       </c>
       <c r="U52" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="B53" t="s">
-        <v>395</v>
+        <v>422</v>
       </c>
       <c r="C53" t="s">
-        <v>396</v>
+        <v>423</v>
       </c>
       <c r="D53" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E53" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="G53" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H53">
-        <v>2564</v>
+        <v>12644</v>
       </c>
       <c r="I53" s="1">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="J53" s="2">
-        <v>1300</v>
+        <v>4860</v>
       </c>
       <c r="K53" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="L53" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M53" t="s">
-        <v>97</v>
+        <v>426</v>
       </c>
       <c r="O53" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P53" t="str">
         <f>_xlfn.XLOOKUP(O53,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>CTLOC LOCAÇÃO DE CONTAINERS</v>
+        <v>DHARMACOM TELECOMUNICACOES LTD</v>
       </c>
       <c r="Q53" t="s">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="R53" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S53" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T53" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="U53" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>400</v>
+        <v>428</v>
       </c>
       <c r="B54" t="s">
-        <v>401</v>
+        <v>429</v>
       </c>
       <c r="C54" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="D54" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E54" t="s">
-        <v>403</v>
+        <v>159</v>
       </c>
       <c r="G54" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H54">
-        <v>12908</v>
+        <v>4604</v>
       </c>
       <c r="I54" s="1">
-        <v>46205</v>
-      </c>
-      <c r="J54">
-        <v>643664.51</v>
+        <v>46302</v>
+      </c>
+      <c r="J54" s="2">
+        <v>3500</v>
       </c>
       <c r="K54" t="s">
-        <v>404</v>
+        <v>131</v>
       </c>
       <c r="L54" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M54" t="s">
-        <v>405</v>
+        <v>132</v>
       </c>
       <c r="O54" t="s">
         <v>8</v>
       </c>
       <c r="P54" t="str">
         <f>_xlfn.XLOOKUP(O54,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>ENTERPRISE SERV BR S DE TEC LT</v>
+        <v>MAPA COMUNIC E ASSESSORIA LTDA</v>
       </c>
       <c r="Q54" t="s">
-        <v>406</v>
+        <v>431</v>
       </c>
       <c r="R54" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S54" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="T54" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="U54" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>407</v>
+        <v>432</v>
       </c>
       <c r="B55" t="s">
-        <v>408</v>
+        <v>433</v>
       </c>
       <c r="C55" t="s">
-        <v>409</v>
+        <v>434</v>
       </c>
       <c r="D55" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E55" t="s">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="G55" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H55">
-        <v>12958</v>
+        <v>10760</v>
       </c>
       <c r="I55" s="1">
-        <v>46244</v>
-      </c>
-      <c r="J55">
-        <v>746101.35</v>
+        <v>46276</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>436</v>
       </c>
       <c r="K55" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="L55" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M55" t="s">
-        <v>405</v>
+        <v>438</v>
       </c>
       <c r="O55" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="P55" t="str">
         <f>_xlfn.XLOOKUP(O55,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>ENTERPRISE SERV BR S DE TEC LT</v>
+        <v>LOBBY TEC PROD PERSO LTDA</v>
       </c>
       <c r="Q55" t="s">
-        <v>406</v>
+        <v>439</v>
       </c>
       <c r="R55" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S55" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T55" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="U55" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>412</v>
+        <v>440</v>
       </c>
       <c r="B56" t="s">
-        <v>413</v>
+        <v>440</v>
       </c>
       <c r="C56" t="s">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="D56" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E56" t="s">
-        <v>415</v>
+        <v>442</v>
       </c>
       <c r="G56" t="s">
-        <v>94</v>
-      </c>
-      <c r="H56">
-        <v>13020</v>
+        <v>83</v>
+      </c>
+      <c r="H56" t="s">
+        <v>443</v>
       </c>
       <c r="I56" s="1">
-        <v>46268</v>
-      </c>
-      <c r="J56">
-        <v>330986.02</v>
+        <v>46273</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>444</v>
       </c>
       <c r="K56" t="s">
-        <v>416</v>
+        <v>445</v>
       </c>
       <c r="L56" t="s">
-        <v>96</v>
-      </c>
-      <c r="M56" t="s">
-        <v>178</v>
+        <v>85</v>
       </c>
       <c r="O56" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P56" t="str">
         <f>_xlfn.XLOOKUP(O56,[1]BASE!N:N,[1]BASE!O:O)</f>
         <v>ENTERPRISE SERV BR S DE TEC LT</v>
       </c>
       <c r="Q56" t="s">
-        <v>406</v>
+        <v>319</v>
       </c>
       <c r="R56" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S56" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T56" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="U56" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>417</v>
+        <v>446</v>
       </c>
       <c r="B57" t="s">
-        <v>418</v>
+        <v>447</v>
       </c>
       <c r="C57" t="s">
-        <v>419</v>
+        <v>448</v>
       </c>
       <c r="D57" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E57" t="s">
-        <v>420</v>
+        <v>449</v>
       </c>
       <c r="G57" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H57">
-        <v>13018</v>
+        <v>12908</v>
       </c>
       <c r="I57" s="1">
-        <v>46298</v>
-      </c>
-      <c r="J57">
-        <v>18778.25</v>
+        <v>46205</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>450</v>
       </c>
       <c r="K57" t="s">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="L57" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M57" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="O57" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P57" t="str">
         <f>_xlfn.XLOOKUP(O57,[1]BASE!N:N,[1]BASE!O:O)</f>
         <v>ENTERPRISE SERV BR S DE TEC LT</v>
       </c>
       <c r="Q57" t="s">
-        <v>406</v>
+        <v>319</v>
       </c>
       <c r="R57" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S57" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="T57" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="U57" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="B58" t="s">
-        <v>422</v>
+        <v>453</v>
       </c>
       <c r="C58" t="s">
-        <v>423</v>
+        <v>454</v>
       </c>
       <c r="D58" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E58" t="s">
-        <v>424</v>
+        <v>455</v>
       </c>
       <c r="G58" t="s">
-        <v>94</v>
-      </c>
-      <c r="H58" t="s">
-        <v>425</v>
+        <v>83</v>
+      </c>
+      <c r="H58">
+        <v>13018</v>
       </c>
       <c r="I58" s="1">
-        <v>46273</v>
-      </c>
-      <c r="J58">
-        <v>605254.43999999994</v>
+        <v>46298</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>456</v>
       </c>
       <c r="K58" t="s">
-        <v>426</v>
+        <v>457</v>
       </c>
       <c r="L58" t="s">
-        <v>96</v>
+        <v>85</v>
+      </c>
+      <c r="M58" t="s">
+        <v>333</v>
       </c>
       <c r="O58" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P58" t="str">
         <f>_xlfn.XLOOKUP(O58,[1]BASE!N:N,[1]BASE!O:O)</f>
         <v>ENTERPRISE SERV BR S DE TEC LT</v>
       </c>
       <c r="Q58" t="s">
-        <v>406</v>
+        <v>319</v>
       </c>
       <c r="R58" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S58" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T58" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="U58" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>427</v>
-      </c>
-      <c r="B59" t="s">
-        <v>428</v>
-      </c>
-      <c r="C59" t="s">
-        <v>429</v>
-      </c>
-      <c r="D59" t="s">
-        <v>92</v>
-      </c>
-      <c r="E59" t="s">
-        <v>430</v>
-      </c>
-      <c r="G59" t="s">
-        <v>94</v>
-      </c>
-      <c r="H59">
-        <v>13073</v>
-      </c>
-      <c r="I59" s="1">
-        <v>46307</v>
-      </c>
-      <c r="J59">
-        <v>195781.06</v>
-      </c>
-      <c r="K59" t="s">
-        <v>431</v>
-      </c>
-      <c r="L59" t="s">
-        <v>96</v>
-      </c>
-      <c r="M59" t="s">
-        <v>178</v>
-      </c>
-      <c r="O59" t="s">
-        <v>8</v>
-      </c>
-      <c r="P59" t="str">
-        <f>_xlfn.XLOOKUP(O59,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>ENTERPRISE SERV BR S DE TEC LT</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>406</v>
-      </c>
-      <c r="R59" t="s">
-        <v>99</v>
-      </c>
-      <c r="S59" t="s">
-        <v>100</v>
-      </c>
-      <c r="T59" t="s">
-        <v>17</v>
-      </c>
-      <c r="U59" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>432</v>
-      </c>
-      <c r="B60" t="s">
-        <v>433</v>
-      </c>
-      <c r="C60" t="s">
-        <v>434</v>
-      </c>
-      <c r="D60" t="s">
-        <v>92</v>
-      </c>
-      <c r="E60" t="s">
-        <v>435</v>
-      </c>
-      <c r="G60" t="s">
-        <v>94</v>
-      </c>
-      <c r="H60">
-        <v>13074</v>
-      </c>
-      <c r="I60" s="1">
-        <v>46307</v>
-      </c>
-      <c r="J60">
-        <v>609793.75</v>
-      </c>
-      <c r="K60" t="s">
-        <v>431</v>
-      </c>
-      <c r="L60" t="s">
-        <v>96</v>
-      </c>
-      <c r="M60" t="s">
-        <v>405</v>
-      </c>
-      <c r="O60" t="s">
-        <v>8</v>
-      </c>
-      <c r="P60" t="str">
-        <f>_xlfn.XLOOKUP(O60,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>ENTERPRISE SERV BR S DE TEC LT</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>406</v>
-      </c>
-      <c r="R60" t="s">
-        <v>99</v>
-      </c>
-      <c r="S60" t="s">
-        <v>100</v>
-      </c>
-      <c r="T60" t="s">
-        <v>17</v>
-      </c>
-      <c r="U60" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>436</v>
-      </c>
-      <c r="B61" t="s">
-        <v>437</v>
-      </c>
-      <c r="C61" t="s">
-        <v>438</v>
-      </c>
-      <c r="D61" t="s">
-        <v>92</v>
-      </c>
-      <c r="E61" t="s">
-        <v>439</v>
-      </c>
-      <c r="G61" t="s">
-        <v>94</v>
-      </c>
-      <c r="H61">
-        <v>13078</v>
-      </c>
-      <c r="I61" s="1">
-        <v>46307</v>
-      </c>
-      <c r="J61">
-        <v>21750.11</v>
-      </c>
-      <c r="K61" t="s">
-        <v>440</v>
-      </c>
-      <c r="L61" t="s">
-        <v>96</v>
-      </c>
-      <c r="M61" t="s">
-        <v>320</v>
-      </c>
-      <c r="O61" t="s">
-        <v>8</v>
-      </c>
-      <c r="P61" t="str">
-        <f>_xlfn.XLOOKUP(O61,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>ENTERPRISE SERV BR S DE TEC LT</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>406</v>
-      </c>
-      <c r="R61" t="s">
-        <v>99</v>
-      </c>
-      <c r="S61" t="s">
-        <v>100</v>
-      </c>
-      <c r="T61" t="s">
-        <v>17</v>
-      </c>
-      <c r="U61" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>441</v>
-      </c>
-      <c r="B62" t="s">
-        <v>442</v>
-      </c>
-      <c r="C62" t="s">
-        <v>443</v>
-      </c>
-      <c r="D62" t="s">
-        <v>92</v>
-      </c>
-      <c r="E62" t="s">
-        <v>444</v>
-      </c>
-      <c r="G62" t="s">
-        <v>94</v>
-      </c>
-      <c r="H62">
-        <v>3679</v>
-      </c>
-      <c r="I62" s="1">
-        <v>46317</v>
-      </c>
-      <c r="J62" s="2">
-        <v>1850</v>
-      </c>
-      <c r="K62" t="s">
-        <v>445</v>
-      </c>
-      <c r="L62" t="s">
-        <v>96</v>
-      </c>
-      <c r="M62" t="s">
-        <v>191</v>
-      </c>
-      <c r="O62" t="s">
-        <v>60</v>
-      </c>
-      <c r="P62" t="str">
-        <f>_xlfn.XLOOKUP(O62,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>FEMAG INDUSTRIA E COMERCIO LTD</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>446</v>
-      </c>
-      <c r="R62" t="s">
-        <v>99</v>
-      </c>
-      <c r="S62" t="s">
-        <v>100</v>
-      </c>
-      <c r="T62" t="s">
-        <v>9</v>
-      </c>
-      <c r="U62" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>447</v>
-      </c>
-      <c r="B63" t="s">
-        <v>448</v>
-      </c>
-      <c r="C63" t="s">
-        <v>449</v>
-      </c>
-      <c r="D63" t="s">
-        <v>92</v>
-      </c>
-      <c r="E63" t="s">
-        <v>450</v>
-      </c>
-      <c r="G63" t="s">
-        <v>94</v>
-      </c>
-      <c r="H63">
-        <v>1153</v>
-      </c>
-      <c r="I63" s="1">
-        <v>46308</v>
-      </c>
-      <c r="J63" s="2">
-        <v>580</v>
-      </c>
-      <c r="K63" t="s">
-        <v>451</v>
-      </c>
-      <c r="L63" t="s">
-        <v>96</v>
-      </c>
-      <c r="M63" t="s">
-        <v>452</v>
-      </c>
-      <c r="O63" t="s">
-        <v>44</v>
-      </c>
-      <c r="P63" t="str">
-        <f>_xlfn.XLOOKUP(O63,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>TO INDO EXPRESS EIRELI</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>453</v>
-      </c>
-      <c r="R63" t="s">
-        <v>99</v>
-      </c>
-      <c r="S63" t="s">
-        <v>100</v>
-      </c>
-      <c r="T63" t="s">
-        <v>33</v>
-      </c>
-      <c r="U63" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>454</v>
-      </c>
-      <c r="B64" t="s">
-        <v>455</v>
-      </c>
-      <c r="C64" t="s">
-        <v>456</v>
-      </c>
-      <c r="D64" t="s">
-        <v>92</v>
-      </c>
-      <c r="E64" t="s">
-        <v>457</v>
-      </c>
-      <c r="G64" t="s">
-        <v>94</v>
-      </c>
-      <c r="H64">
-        <v>798</v>
-      </c>
-      <c r="I64" s="1">
-        <v>46269</v>
-      </c>
-      <c r="J64" s="2">
-        <v>2890</v>
-      </c>
-      <c r="K64" t="s">
-        <v>458</v>
-      </c>
-      <c r="L64" t="s">
-        <v>96</v>
-      </c>
-      <c r="M64" t="s">
-        <v>459</v>
-      </c>
-      <c r="O64" t="s">
-        <v>32</v>
-      </c>
-      <c r="P64" t="str">
-        <f>_xlfn.XLOOKUP(O64,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>HASS ASSES MARK E EVENTOS LTDA</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>460</v>
-      </c>
-      <c r="R64" t="s">
-        <v>99</v>
-      </c>
-      <c r="S64" t="s">
-        <v>100</v>
-      </c>
-      <c r="T64" t="s">
-        <v>25</v>
-      </c>
-      <c r="U64" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>461</v>
-      </c>
-      <c r="B65" t="s">
-        <v>462</v>
-      </c>
-      <c r="C65" t="s">
-        <v>463</v>
-      </c>
-      <c r="D65" t="s">
-        <v>92</v>
-      </c>
-      <c r="E65" t="s">
-        <v>464</v>
-      </c>
-      <c r="G65" t="s">
-        <v>94</v>
-      </c>
-      <c r="H65">
-        <v>427</v>
-      </c>
-      <c r="I65" s="1">
-        <v>46281</v>
-      </c>
-      <c r="J65" s="2">
-        <v>3200</v>
-      </c>
-      <c r="K65" t="s">
-        <v>465</v>
-      </c>
-      <c r="L65" t="s">
-        <v>96</v>
-      </c>
-      <c r="M65" t="s">
-        <v>363</v>
-      </c>
-      <c r="O65" t="s">
-        <v>48</v>
-      </c>
-      <c r="P65" t="str">
-        <f>_xlfn.XLOOKUP(O65,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>SUPORTE EPI SEGURANCA TRA</v>
-      </c>
-      <c r="Q65" t="s">
-        <v>466</v>
-      </c>
-      <c r="R65" t="s">
-        <v>99</v>
-      </c>
-      <c r="S65" t="s">
-        <v>100</v>
-      </c>
-      <c r="T65" t="s">
-        <v>29</v>
-      </c>
-      <c r="U65" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>467</v>
-      </c>
-      <c r="B66" t="s">
-        <v>468</v>
-      </c>
-      <c r="C66" t="s">
-        <v>469</v>
-      </c>
-      <c r="D66" t="s">
-        <v>92</v>
-      </c>
-      <c r="E66" t="s">
-        <v>470</v>
-      </c>
-      <c r="G66" t="s">
-        <v>94</v>
-      </c>
-      <c r="H66">
-        <v>1662</v>
-      </c>
-      <c r="I66" s="1">
-        <v>46307</v>
-      </c>
-      <c r="J66">
-        <v>2869.14</v>
-      </c>
-      <c r="K66" t="s">
-        <v>471</v>
-      </c>
-      <c r="L66" t="s">
-        <v>96</v>
-      </c>
-      <c r="M66" t="s">
-        <v>472</v>
-      </c>
-      <c r="O66" t="s">
-        <v>61</v>
-      </c>
-      <c r="P66" t="str">
-        <f>_xlfn.XLOOKUP(O66,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>RFR COM E RECI DE RESIDUOS LTD</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>473</v>
-      </c>
-      <c r="R66" t="s">
-        <v>99</v>
-      </c>
-      <c r="S66" t="s">
-        <v>109</v>
-      </c>
-      <c r="T66" t="s">
-        <v>29</v>
-      </c>
-      <c r="U66" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>474</v>
-      </c>
-      <c r="B67" t="s">
-        <v>475</v>
-      </c>
-      <c r="C67" t="s">
-        <v>476</v>
-      </c>
-      <c r="D67" t="s">
-        <v>92</v>
-      </c>
-      <c r="E67" t="s">
-        <v>477</v>
-      </c>
-      <c r="G67" t="s">
-        <v>94</v>
-      </c>
-      <c r="H67">
-        <v>1661</v>
-      </c>
-      <c r="I67" s="1">
-        <v>46307</v>
-      </c>
-      <c r="J67" s="2">
-        <v>9000</v>
-      </c>
-      <c r="K67" t="s">
-        <v>471</v>
-      </c>
-      <c r="L67" t="s">
-        <v>96</v>
-      </c>
-      <c r="M67" t="s">
-        <v>472</v>
-      </c>
-      <c r="O67" t="s">
-        <v>61</v>
-      </c>
-      <c r="P67" t="str">
-        <f>_xlfn.XLOOKUP(O67,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>RFR COM E RECI DE RESIDUOS LTD</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>473</v>
-      </c>
-      <c r="R67" t="s">
-        <v>99</v>
-      </c>
-      <c r="S67" t="s">
-        <v>109</v>
-      </c>
-      <c r="T67" t="s">
-        <v>29</v>
-      </c>
-      <c r="U67" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>478</v>
-      </c>
-      <c r="B68" t="s">
-        <v>479</v>
-      </c>
-      <c r="C68" t="s">
-        <v>480</v>
-      </c>
-      <c r="D68" t="s">
-        <v>92</v>
-      </c>
-      <c r="E68" t="s">
-        <v>481</v>
-      </c>
-      <c r="G68" t="s">
-        <v>94</v>
-      </c>
-      <c r="H68">
-        <v>12644</v>
-      </c>
-      <c r="I68" s="1">
-        <v>46300</v>
-      </c>
-      <c r="J68" s="2">
-        <v>4860</v>
-      </c>
-      <c r="K68" t="s">
-        <v>482</v>
-      </c>
-      <c r="L68" t="s">
-        <v>96</v>
-      </c>
-      <c r="M68" t="s">
-        <v>191</v>
-      </c>
-      <c r="O68" t="s">
-        <v>62</v>
-      </c>
-      <c r="P68" t="str">
-        <f>_xlfn.XLOOKUP(O68,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>DHARMACOM TELECOMUNICACOES LTD</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>483</v>
-      </c>
-      <c r="R68" t="s">
-        <v>99</v>
-      </c>
-      <c r="S68" t="s">
-        <v>100</v>
-      </c>
-      <c r="T68" t="s">
-        <v>43</v>
-      </c>
-      <c r="U68" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>484</v>
-      </c>
-      <c r="B69" t="s">
-        <v>485</v>
-      </c>
-      <c r="C69" t="s">
-        <v>486</v>
-      </c>
-      <c r="D69" t="s">
-        <v>92</v>
-      </c>
-      <c r="E69" t="s">
-        <v>134</v>
-      </c>
-      <c r="G69" t="s">
-        <v>94</v>
-      </c>
-      <c r="H69">
-        <v>2970</v>
-      </c>
-      <c r="I69" s="1">
-        <v>46304</v>
-      </c>
-      <c r="J69" s="2">
-        <v>3500</v>
-      </c>
-      <c r="K69" t="s">
-        <v>487</v>
-      </c>
-      <c r="L69" t="s">
-        <v>96</v>
-      </c>
-      <c r="M69" t="s">
-        <v>488</v>
-      </c>
-      <c r="O69" t="s">
-        <v>63</v>
-      </c>
-      <c r="P69" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>489</v>
-      </c>
-      <c r="R69" t="s">
-        <v>99</v>
-      </c>
-      <c r="S69" t="s">
-        <v>100</v>
-      </c>
-      <c r="T69" t="s">
-        <v>45</v>
-      </c>
-      <c r="U69" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>490</v>
-      </c>
-      <c r="B70" t="s">
-        <v>491</v>
-      </c>
-      <c r="C70" t="s">
-        <v>492</v>
-      </c>
-      <c r="D70" t="s">
-        <v>92</v>
-      </c>
-      <c r="E70" t="s">
-        <v>493</v>
-      </c>
-      <c r="G70" t="s">
-        <v>94</v>
-      </c>
-      <c r="H70">
-        <v>21941</v>
-      </c>
-      <c r="I70" s="1">
-        <v>46247</v>
-      </c>
-      <c r="J70">
-        <v>7881.75</v>
-      </c>
-      <c r="K70" t="s">
-        <v>494</v>
-      </c>
-      <c r="L70" t="s">
-        <v>96</v>
-      </c>
-      <c r="M70" t="s">
-        <v>495</v>
-      </c>
-      <c r="O70" t="s">
-        <v>18</v>
-      </c>
-      <c r="P70" t="str">
-        <f>_xlfn.XLOOKUP(O70,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>RAZAC SERVICES CONSUL EM COM E</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>496</v>
-      </c>
-      <c r="R70" t="s">
-        <v>99</v>
-      </c>
-      <c r="S70" t="s">
-        <v>109</v>
-      </c>
-      <c r="T70" t="s">
-        <v>31</v>
-      </c>
-      <c r="U70" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>497</v>
-      </c>
-      <c r="B71" t="s">
-        <v>498</v>
-      </c>
-      <c r="C71" t="s">
-        <v>499</v>
-      </c>
-      <c r="D71" t="s">
-        <v>92</v>
-      </c>
-      <c r="E71" t="s">
-        <v>500</v>
-      </c>
-      <c r="G71" t="s">
-        <v>94</v>
-      </c>
-      <c r="H71">
-        <v>21985</v>
-      </c>
-      <c r="I71" s="1">
-        <v>46262</v>
-      </c>
-      <c r="J71">
-        <v>969.98</v>
-      </c>
-      <c r="K71" t="s">
-        <v>494</v>
-      </c>
-      <c r="L71" t="s">
-        <v>96</v>
-      </c>
-      <c r="M71" t="s">
-        <v>495</v>
-      </c>
-      <c r="O71" t="s">
-        <v>18</v>
-      </c>
-      <c r="P71" t="str">
-        <f>_xlfn.XLOOKUP(O71,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>RAZAC SERVICES CONSUL EM COM E</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>501</v>
-      </c>
-      <c r="R71" t="s">
-        <v>99</v>
-      </c>
-      <c r="S71" t="s">
-        <v>109</v>
-      </c>
-      <c r="T71" t="s">
-        <v>31</v>
-      </c>
-      <c r="U71" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>502</v>
-      </c>
-      <c r="B72" t="s">
-        <v>503</v>
-      </c>
-      <c r="C72" t="s">
-        <v>504</v>
-      </c>
-      <c r="D72" t="s">
-        <v>92</v>
-      </c>
-      <c r="E72" t="s">
-        <v>505</v>
-      </c>
-      <c r="G72" t="s">
-        <v>94</v>
-      </c>
-      <c r="H72">
-        <v>176266</v>
-      </c>
-      <c r="I72" s="1">
-        <v>46266</v>
-      </c>
-      <c r="J72">
-        <v>270515.57</v>
-      </c>
-      <c r="K72" t="s">
-        <v>506</v>
-      </c>
-      <c r="L72" t="s">
-        <v>96</v>
-      </c>
-      <c r="O72" t="s">
-        <v>30</v>
-      </c>
-      <c r="P72" t="str">
-        <f>_xlfn.XLOOKUP(O72,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>ILS CARGO TRANSPORTES INTERNAC</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>507</v>
-      </c>
-      <c r="R72" t="s">
-        <v>99</v>
-      </c>
-      <c r="S72" t="s">
-        <v>100</v>
-      </c>
-      <c r="T72" t="s">
-        <v>31</v>
-      </c>
-      <c r="U72" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>508</v>
-      </c>
-      <c r="B73" t="s">
-        <v>509</v>
-      </c>
-      <c r="C73" t="s">
-        <v>510</v>
-      </c>
-      <c r="D73" t="s">
-        <v>92</v>
-      </c>
-      <c r="E73" t="s">
-        <v>511</v>
-      </c>
-      <c r="G73" t="s">
-        <v>94</v>
-      </c>
-      <c r="H73">
-        <v>22168</v>
-      </c>
-      <c r="I73" s="1">
-        <v>46309</v>
-      </c>
-      <c r="J73">
-        <v>2036.1</v>
-      </c>
-      <c r="K73" t="s">
-        <v>512</v>
-      </c>
-      <c r="L73" t="s">
-        <v>96</v>
-      </c>
-      <c r="M73" t="s">
-        <v>495</v>
-      </c>
-      <c r="O73" t="s">
-        <v>18</v>
-      </c>
-      <c r="P73" t="str">
-        <f>_xlfn.XLOOKUP(O73,[1]BASE!N:N,[1]BASE!O:O)</f>
-        <v>RAZAC SERVICES CONSUL EM COM E</v>
-      </c>
-      <c r="Q73" t="s">
-        <v>496</v>
-      </c>
-      <c r="R73" t="s">
-        <v>99</v>
-      </c>
-      <c r="S73" t="s">
-        <v>109</v>
-      </c>
-      <c r="T73" t="s">
-        <v>31</v>
-      </c>
-      <c r="U73" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:U1" xr:uid="{13EBA7BE-CA8E-4BCB-B20F-18622FF64A60}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
